--- a/grupos/2APM - Estadisticos 20222.xlsx
+++ b/grupos/2APM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="174">
   <si>
     <t>Materia</t>
   </si>
@@ -1051,7 +1051,7 @@
         <v>9</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F4">
         <v>-1</v>
@@ -1114,7 +1114,7 @@
         <v>9</v>
       </c>
       <c r="Z4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA4">
         <v>-1</v>
@@ -1140,7 +1140,7 @@
         <v>8</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F5">
         <v>-1</v>
@@ -1203,7 +1203,7 @@
         <v>8</v>
       </c>
       <c r="Z5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA5">
         <v>-1</v>
@@ -1229,7 +1229,7 @@
         <v>7</v>
       </c>
       <c r="E6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F6">
         <v>-1</v>
@@ -1292,7 +1292,7 @@
         <v>7</v>
       </c>
       <c r="Z6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA6">
         <v>-1</v>
@@ -1318,7 +1318,7 @@
         <v>8</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F7">
         <v>-1</v>
@@ -1381,7 +1381,7 @@
         <v>8</v>
       </c>
       <c r="Z7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA7">
         <v>-1</v>
@@ -1407,7 +1407,7 @@
         <v>8</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F8">
         <v>-1</v>
@@ -1470,7 +1470,7 @@
         <v>8</v>
       </c>
       <c r="Z8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA8">
         <v>-1</v>
@@ -1496,7 +1496,7 @@
         <v>5</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="F9">
         <v>-1</v>
@@ -1559,7 +1559,7 @@
         <v>5</v>
       </c>
       <c r="Z9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA9">
         <v>-1</v>
@@ -1585,7 +1585,7 @@
         <v>9</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F10">
         <v>-1</v>
@@ -1648,7 +1648,7 @@
         <v>9</v>
       </c>
       <c r="Z10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA10">
         <v>-1</v>
@@ -1674,7 +1674,7 @@
         <v>8</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F11">
         <v>-1</v>
@@ -1737,7 +1737,7 @@
         <v>8</v>
       </c>
       <c r="Z11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA11">
         <v>-1</v>
@@ -1763,7 +1763,7 @@
         <v>6</v>
       </c>
       <c r="E12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F12">
         <v>-1</v>
@@ -1826,7 +1826,7 @@
         <v>6</v>
       </c>
       <c r="Z12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA12">
         <v>-1</v>
@@ -1852,7 +1852,7 @@
         <v>5</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F13">
         <v>-1</v>
@@ -1915,7 +1915,7 @@
         <v>5</v>
       </c>
       <c r="Z13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA13">
         <v>-1</v>
@@ -1941,7 +1941,7 @@
         <v>6</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F14">
         <v>-1</v>
@@ -2004,7 +2004,7 @@
         <v>6</v>
       </c>
       <c r="Z14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA14">
         <v>-1</v>
@@ -2030,7 +2030,7 @@
         <v>8</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F15">
         <v>-1</v>
@@ -2093,7 +2093,7 @@
         <v>8</v>
       </c>
       <c r="Z15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA15">
         <v>-1</v>
@@ -2119,7 +2119,7 @@
         <v>7</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F16">
         <v>-1</v>
@@ -2182,7 +2182,7 @@
         <v>7</v>
       </c>
       <c r="Z16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA16">
         <v>-1</v>
@@ -2208,7 +2208,7 @@
         <v>7</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F17">
         <v>-1</v>
@@ -2271,7 +2271,7 @@
         <v>7</v>
       </c>
       <c r="Z17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA17">
         <v>-1</v>
@@ -2297,7 +2297,7 @@
         <v>7</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F18">
         <v>-1</v>
@@ -2360,7 +2360,7 @@
         <v>7</v>
       </c>
       <c r="Z18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA18">
         <v>-1</v>
@@ -2386,7 +2386,7 @@
         <v>7</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F19">
         <v>-1</v>
@@ -2449,7 +2449,7 @@
         <v>7</v>
       </c>
       <c r="Z19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA19">
         <v>-1</v>
@@ -2475,7 +2475,7 @@
         <v>6</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="F20">
         <v>-1</v>
@@ -2538,7 +2538,7 @@
         <v>6</v>
       </c>
       <c r="Z20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA20">
         <v>-1</v>
@@ -2564,7 +2564,7 @@
         <v>7</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F21">
         <v>-1</v>
@@ -2627,7 +2627,7 @@
         <v>7</v>
       </c>
       <c r="Z21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA21">
         <v>-1</v>
@@ -2653,7 +2653,7 @@
         <v>6</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F22">
         <v>-1</v>
@@ -2716,7 +2716,7 @@
         <v>6</v>
       </c>
       <c r="Z22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA22">
         <v>-1</v>
@@ -2742,7 +2742,7 @@
         <v>7</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F23">
         <v>-1</v>
@@ -2805,7 +2805,7 @@
         <v>7</v>
       </c>
       <c r="Z23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA23">
         <v>-1</v>
@@ -2831,7 +2831,7 @@
         <v>7</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F24">
         <v>-1</v>
@@ -2894,7 +2894,7 @@
         <v>7</v>
       </c>
       <c r="Z24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA24">
         <v>-1</v>
@@ -2920,7 +2920,7 @@
         <v>7</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F25">
         <v>-1</v>
@@ -2983,7 +2983,7 @@
         <v>7</v>
       </c>
       <c r="Z25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA25">
         <v>-1</v>
@@ -3009,7 +3009,7 @@
         <v>8</v>
       </c>
       <c r="E26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F26">
         <v>-1</v>
@@ -3072,7 +3072,7 @@
         <v>8</v>
       </c>
       <c r="Z26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA26">
         <v>-1</v>
@@ -3098,7 +3098,7 @@
         <v>8</v>
       </c>
       <c r="E27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F27">
         <v>-1</v>
@@ -3161,7 +3161,7 @@
         <v>8</v>
       </c>
       <c r="Z27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA27">
         <v>-1</v>
@@ -3187,7 +3187,7 @@
         <v>8</v>
       </c>
       <c r="E28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F28">
         <v>-1</v>
@@ -3250,7 +3250,7 @@
         <v>8</v>
       </c>
       <c r="Z28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA28">
         <v>-1</v>
@@ -3276,7 +3276,7 @@
         <v>8</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F29">
         <v>-1</v>
@@ -3339,7 +3339,7 @@
         <v>8</v>
       </c>
       <c r="Z29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA29">
         <v>-1</v>
@@ -3365,7 +3365,7 @@
         <v>9</v>
       </c>
       <c r="E30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F30">
         <v>-1</v>
@@ -3428,7 +3428,7 @@
         <v>9</v>
       </c>
       <c r="Z30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA30">
         <v>-1</v>
@@ -3454,7 +3454,7 @@
         <v>9</v>
       </c>
       <c r="E31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F31">
         <v>-1</v>
@@ -3517,7 +3517,7 @@
         <v>9</v>
       </c>
       <c r="Z31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA31">
         <v>-1</v>
@@ -3543,7 +3543,7 @@
         <v>9</v>
       </c>
       <c r="E32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F32">
         <v>-1</v>
@@ -3606,7 +3606,7 @@
         <v>9</v>
       </c>
       <c r="Z32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA32">
         <v>-1</v>
@@ -3632,7 +3632,7 @@
         <v>7</v>
       </c>
       <c r="E33">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F33">
         <v>-1</v>
@@ -3695,7 +3695,7 @@
         <v>7</v>
       </c>
       <c r="Z33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA33">
         <v>-1</v>
@@ -3721,7 +3721,7 @@
         <v>7</v>
       </c>
       <c r="E34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F34">
         <v>-1</v>
@@ -3784,7 +3784,7 @@
         <v>7</v>
       </c>
       <c r="Z34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA34">
         <v>-1</v>
@@ -3810,7 +3810,7 @@
         <v>8</v>
       </c>
       <c r="E35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F35">
         <v>-1</v>
@@ -3873,7 +3873,7 @@
         <v>8</v>
       </c>
       <c r="Z35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA35">
         <v>-1</v>
@@ -3899,7 +3899,7 @@
         <v>8</v>
       </c>
       <c r="E36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F36">
         <v>-1</v>
@@ -3962,7 +3962,7 @@
         <v>8</v>
       </c>
       <c r="Z36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA36">
         <v>-1</v>
@@ -3988,7 +3988,7 @@
         <v>6</v>
       </c>
       <c r="E37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F37">
         <v>-1</v>
@@ -4051,7 +4051,7 @@
         <v>6</v>
       </c>
       <c r="Z37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA37">
         <v>-1</v>
@@ -4077,7 +4077,7 @@
         <v>9</v>
       </c>
       <c r="E38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F38">
         <v>-1</v>
@@ -4140,7 +4140,7 @@
         <v>9</v>
       </c>
       <c r="Z38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA38">
         <v>-1</v>
@@ -4166,7 +4166,7 @@
         <v>9</v>
       </c>
       <c r="E39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F39">
         <v>-1</v>
@@ -4229,7 +4229,7 @@
         <v>9</v>
       </c>
       <c r="Z39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA39">
         <v>-1</v>
@@ -4255,7 +4255,7 @@
         <v>7</v>
       </c>
       <c r="E40">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F40">
         <v>-1</v>
@@ -4318,7 +4318,7 @@
         <v>7</v>
       </c>
       <c r="Z40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA40">
         <v>-1</v>
@@ -4344,7 +4344,7 @@
         <v>6</v>
       </c>
       <c r="E41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F41">
         <v>-1</v>
@@ -4407,7 +4407,7 @@
         <v>6</v>
       </c>
       <c r="Z41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA41">
         <v>-1</v>
@@ -4433,7 +4433,7 @@
         <v>7</v>
       </c>
       <c r="E42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F42">
         <v>-1</v>
@@ -4496,7 +4496,7 @@
         <v>7</v>
       </c>
       <c r="Z42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA42">
         <v>-1</v>
@@ -4644,7 +4644,7 @@
         <v>96</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -4712,7 +4712,7 @@
         <v>96</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -4780,7 +4780,7 @@
         <v>96</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -4848,7 +4848,7 @@
         <v>96</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -4916,7 +4916,7 @@
         <v>96</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -4984,7 +4984,7 @@
         <v>32</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -5052,7 +5052,7 @@
         <v>96</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -5120,7 +5120,7 @@
         <v>96</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -5188,7 +5188,7 @@
         <v>96</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -5256,7 +5256,7 @@
         <v>88</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -5324,7 +5324,7 @@
         <v>96</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -5392,7 +5392,7 @@
         <v>96</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -5460,7 +5460,7 @@
         <v>96</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -5528,7 +5528,7 @@
         <v>96</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -5596,7 +5596,7 @@
         <v>96</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -5664,7 +5664,7 @@
         <v>96</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -5732,7 +5732,7 @@
         <v>96</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -5800,7 +5800,7 @@
         <v>96</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -5868,7 +5868,7 @@
         <v>96</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -5936,7 +5936,7 @@
         <v>96</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -6004,7 +6004,7 @@
         <v>96</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -6072,7 +6072,7 @@
         <v>96</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -6140,7 +6140,7 @@
         <v>96</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -6208,7 +6208,7 @@
         <v>96</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -6276,7 +6276,7 @@
         <v>96</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -6344,7 +6344,7 @@
         <v>96</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -6412,7 +6412,7 @@
         <v>96</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -6480,7 +6480,7 @@
         <v>96</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -6548,7 +6548,7 @@
         <v>96</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -6616,7 +6616,7 @@
         <v>96</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -6684,7 +6684,7 @@
         <v>96</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -6752,7 +6752,7 @@
         <v>96</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -6820,7 +6820,7 @@
         <v>96</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -6888,7 +6888,7 @@
         <v>96</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -6956,7 +6956,7 @@
         <v>96</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -7024,7 +7024,7 @@
         <v>96</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -7092,7 +7092,7 @@
         <v>96</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -7160,7 +7160,7 @@
         <v>96</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -7228,7 +7228,7 @@
         <v>96</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -7363,57 +7363,60 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C3">
         <v>39</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>56.41</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>43.59</v>
+      </c>
+      <c r="H3">
+        <v>6.6</v>
       </c>
       <c r="I3">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C4">
         <v>39</v>
       </c>
       <c r="D4">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E4">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>56.41</v>
+        <v>74.36</v>
       </c>
       <c r="G4">
-        <v>43.59</v>
+        <v>25.64</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7557,7 +7560,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7606,19 +7609,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>22330051920149</v>
+        <v>22330051920150</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
         <v>64</v>
@@ -7626,16 +7629,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>22330051920150</v>
+        <v>22330051920151</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -7646,19 +7649,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>22330051920150</v>
+        <v>22330051920292</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
         <v>64</v>
@@ -7666,16 +7669,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>22330051920151</v>
+        <v>22330051920383</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D6" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -7686,19 +7689,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>22330051920151</v>
+        <v>22330051920153</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D7" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
         <v>64</v>
@@ -7706,16 +7709,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>22330051920292</v>
+        <v>22330051920155</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D8" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -7726,19 +7729,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>22330051920292</v>
+        <v>22330051920156</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D9" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
         <v>64</v>
@@ -7746,16 +7749,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>22330051920383</v>
+        <v>22330051920154</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="D10" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -7766,19 +7769,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>22330051920383</v>
+        <v>22330051920381</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D11" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
         <v>64</v>
@@ -7786,16 +7789,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>22330051920153</v>
+        <v>22330051920152</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D12" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -7806,19 +7809,19 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>22330051920153</v>
+        <v>22330051920384</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D13" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
         <v>64</v>
@@ -7826,16 +7829,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>22330051920155</v>
+        <v>22330051920157</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C14" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D14" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -7846,19 +7849,19 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>22330051920155</v>
+        <v>22330051920161</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C15" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D15" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F15" t="s">
         <v>64</v>
@@ -7866,16 +7869,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>22330051920156</v>
+        <v>22330051920158</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C16" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D16" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -7886,19 +7889,19 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>22330051920156</v>
+        <v>22330051920159</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C17" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="D17" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F17" t="s">
         <v>64</v>
@@ -7906,16 +7909,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>22330051920154</v>
+        <v>22330051920162</v>
       </c>
       <c r="B18" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C18" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D18" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
@@ -7926,19 +7929,19 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>22330051920154</v>
+        <v>22330051920160</v>
       </c>
       <c r="B19" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="D19" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="E19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F19" t="s">
         <v>64</v>
@@ -7946,16 +7949,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>22330051920381</v>
+        <v>22330051920296</v>
       </c>
       <c r="B20" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="C20" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D20" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
@@ -7966,19 +7969,19 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>22330051920381</v>
+        <v>22330051920163</v>
       </c>
       <c r="B21" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C21" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="D21" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="E21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F21" t="s">
         <v>64</v>
@@ -7986,16 +7989,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>22330051920152</v>
+        <v>22330051920299</v>
       </c>
       <c r="B22" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="C22" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="D22" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
@@ -8006,19 +8009,19 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>22330051920152</v>
+        <v>22330051920165</v>
       </c>
       <c r="B23" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="C23" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="D23" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="E23" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F23" t="s">
         <v>64</v>
@@ -8026,16 +8029,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>22330051920384</v>
+        <v>22330051920385</v>
       </c>
       <c r="B24" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="C24" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="D24" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="E24" t="s">
         <v>9</v>
@@ -8046,19 +8049,19 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>22330051920384</v>
+        <v>22330051920164</v>
       </c>
       <c r="B25" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="C25" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D25" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="E25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F25" t="s">
         <v>64</v>
@@ -8066,16 +8069,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>22330051920157</v>
+        <v>22330051920269</v>
       </c>
       <c r="B26" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="C26" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="D26" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="E26" t="s">
         <v>9</v>
@@ -8086,19 +8089,19 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>22330051920157</v>
+        <v>22330051920167</v>
       </c>
       <c r="B27" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="C27" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="D27" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="E27" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F27" t="s">
         <v>64</v>
@@ -8106,16 +8109,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>22330051920161</v>
+        <v>22330051920168</v>
       </c>
       <c r="B28" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="C28" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="D28" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="E28" t="s">
         <v>9</v>
@@ -8126,19 +8129,19 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>22330051920161</v>
+        <v>22330051920169</v>
       </c>
       <c r="B29" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="C29" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="D29" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="E29" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F29" t="s">
         <v>64</v>
@@ -8146,16 +8149,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>22330051920158</v>
+        <v>22330051920170</v>
       </c>
       <c r="B30" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="D30" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="E30" t="s">
         <v>9</v>
@@ -8166,19 +8169,19 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>22330051920158</v>
+        <v>22330051920275</v>
       </c>
       <c r="B31" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="D31" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="E31" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F31" t="s">
         <v>64</v>
@@ -8186,16 +8189,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>22330051920159</v>
+        <v>22330051920386</v>
       </c>
       <c r="B32" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="C32" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="D32" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="E32" t="s">
         <v>9</v>
@@ -8206,19 +8209,19 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>22330051920159</v>
+        <v>22330051920172</v>
       </c>
       <c r="B33" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="C33" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="D33" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="E33" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F33" t="s">
         <v>64</v>
@@ -8226,16 +8229,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>22330051920162</v>
+        <v>22330051920278</v>
       </c>
       <c r="B34" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="C34" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="D34" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="E34" t="s">
         <v>9</v>
@@ -8246,19 +8249,19 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>22330051920162</v>
+        <v>22330051920171</v>
       </c>
       <c r="B35" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="C35" t="s">
-        <v>98</v>
+        <v>131</v>
       </c>
       <c r="D35" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="E35" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F35" t="s">
         <v>64</v>
@@ -8266,16 +8269,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>22330051920160</v>
+        <v>22330051920174</v>
       </c>
       <c r="B36" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="C36" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="D36" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="E36" t="s">
         <v>9</v>
@@ -8286,19 +8289,19 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>22330051920160</v>
+        <v>22330051920387</v>
       </c>
       <c r="B37" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="C37" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="D37" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="E37" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F37" t="s">
         <v>64</v>
@@ -8306,16 +8309,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>22330051920296</v>
+        <v>22330051920284</v>
       </c>
       <c r="B38" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="C38" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="D38" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="E38" t="s">
         <v>9</v>
@@ -8326,19 +8329,19 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>22330051920296</v>
+        <v>22330051920175</v>
       </c>
       <c r="B39" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="C39" t="s">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="D39" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="E39" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F39" t="s">
         <v>64</v>
@@ -8346,801 +8349,21 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <v>22330051920163</v>
+        <v>22330051920287</v>
       </c>
       <c r="B40" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="C40" t="s">
-        <v>89</v>
+        <v>134</v>
       </c>
       <c r="D40" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="E40" t="s">
         <v>9</v>
       </c>
       <c r="F40" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>22330051920163</v>
-      </c>
-      <c r="B41" t="s">
-        <v>88</v>
-      </c>
-      <c r="C41" t="s">
-        <v>89</v>
-      </c>
-      <c r="D41" t="s">
-        <v>154</v>
-      </c>
-      <c r="E41" t="s">
-        <v>8</v>
-      </c>
-      <c r="F41" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>22330051920299</v>
-      </c>
-      <c r="B42" t="s">
-        <v>89</v>
-      </c>
-      <c r="C42" t="s">
-        <v>121</v>
-      </c>
-      <c r="D42" t="s">
-        <v>155</v>
-      </c>
-      <c r="E42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F42" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>22330051920299</v>
-      </c>
-      <c r="B43" t="s">
-        <v>89</v>
-      </c>
-      <c r="C43" t="s">
-        <v>121</v>
-      </c>
-      <c r="D43" t="s">
-        <v>155</v>
-      </c>
-      <c r="E43" t="s">
-        <v>8</v>
-      </c>
-      <c r="F43" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>22330051920165</v>
-      </c>
-      <c r="B44" t="s">
-        <v>89</v>
-      </c>
-      <c r="C44" t="s">
-        <v>122</v>
-      </c>
-      <c r="D44" t="s">
-        <v>156</v>
-      </c>
-      <c r="E44" t="s">
-        <v>9</v>
-      </c>
-      <c r="F44" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>22330051920165</v>
-      </c>
-      <c r="B45" t="s">
-        <v>89</v>
-      </c>
-      <c r="C45" t="s">
-        <v>122</v>
-      </c>
-      <c r="D45" t="s">
-        <v>156</v>
-      </c>
-      <c r="E45" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>22330051920385</v>
-      </c>
-      <c r="B46" t="s">
-        <v>90</v>
-      </c>
-      <c r="C46" t="s">
-        <v>123</v>
-      </c>
-      <c r="D46" t="s">
-        <v>157</v>
-      </c>
-      <c r="E46" t="s">
-        <v>9</v>
-      </c>
-      <c r="F46" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>22330051920385</v>
-      </c>
-      <c r="B47" t="s">
-        <v>90</v>
-      </c>
-      <c r="C47" t="s">
-        <v>123</v>
-      </c>
-      <c r="D47" t="s">
-        <v>157</v>
-      </c>
-      <c r="E47" t="s">
-        <v>8</v>
-      </c>
-      <c r="F47" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>22330051920164</v>
-      </c>
-      <c r="B48" t="s">
-        <v>91</v>
-      </c>
-      <c r="C48" t="s">
-        <v>124</v>
-      </c>
-      <c r="D48" t="s">
-        <v>158</v>
-      </c>
-      <c r="E48" t="s">
-        <v>9</v>
-      </c>
-      <c r="F48" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>22330051920164</v>
-      </c>
-      <c r="B49" t="s">
-        <v>91</v>
-      </c>
-      <c r="C49" t="s">
-        <v>124</v>
-      </c>
-      <c r="D49" t="s">
-        <v>158</v>
-      </c>
-      <c r="E49" t="s">
-        <v>8</v>
-      </c>
-      <c r="F49" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>22330051920269</v>
-      </c>
-      <c r="B50" t="s">
-        <v>92</v>
-      </c>
-      <c r="C50" t="s">
-        <v>125</v>
-      </c>
-      <c r="D50" t="s">
-        <v>159</v>
-      </c>
-      <c r="E50" t="s">
-        <v>9</v>
-      </c>
-      <c r="F50" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>22330051920269</v>
-      </c>
-      <c r="B51" t="s">
-        <v>92</v>
-      </c>
-      <c r="C51" t="s">
-        <v>125</v>
-      </c>
-      <c r="D51" t="s">
-        <v>159</v>
-      </c>
-      <c r="E51" t="s">
-        <v>8</v>
-      </c>
-      <c r="F51" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>22330051920167</v>
-      </c>
-      <c r="B52" t="s">
-        <v>92</v>
-      </c>
-      <c r="C52" t="s">
-        <v>126</v>
-      </c>
-      <c r="D52" t="s">
-        <v>160</v>
-      </c>
-      <c r="E52" t="s">
-        <v>9</v>
-      </c>
-      <c r="F52" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>22330051920167</v>
-      </c>
-      <c r="B53" t="s">
-        <v>92</v>
-      </c>
-      <c r="C53" t="s">
-        <v>126</v>
-      </c>
-      <c r="D53" t="s">
-        <v>160</v>
-      </c>
-      <c r="E53" t="s">
-        <v>8</v>
-      </c>
-      <c r="F53" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>22330051920168</v>
-      </c>
-      <c r="B54" t="s">
-        <v>93</v>
-      </c>
-      <c r="C54" t="s">
-        <v>92</v>
-      </c>
-      <c r="D54" t="s">
-        <v>161</v>
-      </c>
-      <c r="E54" t="s">
-        <v>9</v>
-      </c>
-      <c r="F54" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>22330051920168</v>
-      </c>
-      <c r="B55" t="s">
-        <v>93</v>
-      </c>
-      <c r="C55" t="s">
-        <v>92</v>
-      </c>
-      <c r="D55" t="s">
-        <v>161</v>
-      </c>
-      <c r="E55" t="s">
-        <v>8</v>
-      </c>
-      <c r="F55" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>22330051920169</v>
-      </c>
-      <c r="B56" t="s">
-        <v>94</v>
-      </c>
-      <c r="C56" t="s">
-        <v>127</v>
-      </c>
-      <c r="D56" t="s">
-        <v>162</v>
-      </c>
-      <c r="E56" t="s">
-        <v>9</v>
-      </c>
-      <c r="F56" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>22330051920169</v>
-      </c>
-      <c r="B57" t="s">
-        <v>94</v>
-      </c>
-      <c r="C57" t="s">
-        <v>127</v>
-      </c>
-      <c r="D57" t="s">
-        <v>162</v>
-      </c>
-      <c r="E57" t="s">
-        <v>8</v>
-      </c>
-      <c r="F57" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>22330051920170</v>
-      </c>
-      <c r="B58" t="s">
-        <v>95</v>
-      </c>
-      <c r="C58" t="s">
-        <v>128</v>
-      </c>
-      <c r="D58" t="s">
-        <v>163</v>
-      </c>
-      <c r="E58" t="s">
-        <v>9</v>
-      </c>
-      <c r="F58" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>22330051920170</v>
-      </c>
-      <c r="B59" t="s">
-        <v>95</v>
-      </c>
-      <c r="C59" t="s">
-        <v>128</v>
-      </c>
-      <c r="D59" t="s">
-        <v>163</v>
-      </c>
-      <c r="E59" t="s">
-        <v>8</v>
-      </c>
-      <c r="F59" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>22330051920275</v>
-      </c>
-      <c r="B60" t="s">
-        <v>96</v>
-      </c>
-      <c r="C60" t="s">
-        <v>82</v>
-      </c>
-      <c r="D60" t="s">
-        <v>164</v>
-      </c>
-      <c r="E60" t="s">
-        <v>9</v>
-      </c>
-      <c r="F60" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>22330051920275</v>
-      </c>
-      <c r="B61" t="s">
-        <v>96</v>
-      </c>
-      <c r="C61" t="s">
-        <v>82</v>
-      </c>
-      <c r="D61" t="s">
-        <v>164</v>
-      </c>
-      <c r="E61" t="s">
-        <v>8</v>
-      </c>
-      <c r="F61" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>22330051920386</v>
-      </c>
-      <c r="B62" t="s">
-        <v>96</v>
-      </c>
-      <c r="C62" t="s">
-        <v>129</v>
-      </c>
-      <c r="D62" t="s">
-        <v>165</v>
-      </c>
-      <c r="E62" t="s">
-        <v>9</v>
-      </c>
-      <c r="F62" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>22330051920386</v>
-      </c>
-      <c r="B63" t="s">
-        <v>96</v>
-      </c>
-      <c r="C63" t="s">
-        <v>129</v>
-      </c>
-      <c r="D63" t="s">
-        <v>165</v>
-      </c>
-      <c r="E63" t="s">
-        <v>8</v>
-      </c>
-      <c r="F63" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>22330051920172</v>
-      </c>
-      <c r="B64" t="s">
-        <v>97</v>
-      </c>
-      <c r="C64" t="s">
-        <v>130</v>
-      </c>
-      <c r="D64" t="s">
-        <v>166</v>
-      </c>
-      <c r="E64" t="s">
-        <v>9</v>
-      </c>
-      <c r="F64" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>22330051920172</v>
-      </c>
-      <c r="B65" t="s">
-        <v>97</v>
-      </c>
-      <c r="C65" t="s">
-        <v>130</v>
-      </c>
-      <c r="D65" t="s">
-        <v>166</v>
-      </c>
-      <c r="E65" t="s">
-        <v>8</v>
-      </c>
-      <c r="F65" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>22330051920278</v>
-      </c>
-      <c r="B66" t="s">
-        <v>98</v>
-      </c>
-      <c r="C66" t="s">
-        <v>89</v>
-      </c>
-      <c r="D66" t="s">
-        <v>167</v>
-      </c>
-      <c r="E66" t="s">
-        <v>9</v>
-      </c>
-      <c r="F66" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>22330051920278</v>
-      </c>
-      <c r="B67" t="s">
-        <v>98</v>
-      </c>
-      <c r="C67" t="s">
-        <v>89</v>
-      </c>
-      <c r="D67" t="s">
-        <v>167</v>
-      </c>
-      <c r="E67" t="s">
-        <v>8</v>
-      </c>
-      <c r="F67" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>22330051920171</v>
-      </c>
-      <c r="B68" t="s">
-        <v>98</v>
-      </c>
-      <c r="C68" t="s">
-        <v>131</v>
-      </c>
-      <c r="D68" t="s">
-        <v>168</v>
-      </c>
-      <c r="E68" t="s">
-        <v>9</v>
-      </c>
-      <c r="F68" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>22330051920171</v>
-      </c>
-      <c r="B69" t="s">
-        <v>98</v>
-      </c>
-      <c r="C69" t="s">
-        <v>131</v>
-      </c>
-      <c r="D69" t="s">
-        <v>168</v>
-      </c>
-      <c r="E69" t="s">
-        <v>8</v>
-      </c>
-      <c r="F69" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>22330051920174</v>
-      </c>
-      <c r="B70" t="s">
-        <v>99</v>
-      </c>
-      <c r="C70" t="s">
-        <v>132</v>
-      </c>
-      <c r="D70" t="s">
-        <v>169</v>
-      </c>
-      <c r="E70" t="s">
-        <v>9</v>
-      </c>
-      <c r="F70" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>22330051920174</v>
-      </c>
-      <c r="B71" t="s">
-        <v>99</v>
-      </c>
-      <c r="C71" t="s">
-        <v>132</v>
-      </c>
-      <c r="D71" t="s">
-        <v>169</v>
-      </c>
-      <c r="E71" t="s">
-        <v>8</v>
-      </c>
-      <c r="F71" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>22330051920387</v>
-      </c>
-      <c r="B72" t="s">
-        <v>100</v>
-      </c>
-      <c r="C72" t="s">
-        <v>89</v>
-      </c>
-      <c r="D72" t="s">
-        <v>170</v>
-      </c>
-      <c r="E72" t="s">
-        <v>9</v>
-      </c>
-      <c r="F72" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>22330051920387</v>
-      </c>
-      <c r="B73" t="s">
-        <v>100</v>
-      </c>
-      <c r="C73" t="s">
-        <v>89</v>
-      </c>
-      <c r="D73" t="s">
-        <v>170</v>
-      </c>
-      <c r="E73" t="s">
-        <v>8</v>
-      </c>
-      <c r="F73" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>22330051920284</v>
-      </c>
-      <c r="B74" t="s">
-        <v>101</v>
-      </c>
-      <c r="C74" t="s">
-        <v>133</v>
-      </c>
-      <c r="D74" t="s">
-        <v>171</v>
-      </c>
-      <c r="E74" t="s">
-        <v>9</v>
-      </c>
-      <c r="F74" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>22330051920284</v>
-      </c>
-      <c r="B75" t="s">
-        <v>101</v>
-      </c>
-      <c r="C75" t="s">
-        <v>133</v>
-      </c>
-      <c r="D75" t="s">
-        <v>171</v>
-      </c>
-      <c r="E75" t="s">
-        <v>8</v>
-      </c>
-      <c r="F75" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>22330051920175</v>
-      </c>
-      <c r="B76" t="s">
-        <v>102</v>
-      </c>
-      <c r="C76" t="s">
-        <v>83</v>
-      </c>
-      <c r="D76" t="s">
-        <v>172</v>
-      </c>
-      <c r="E76" t="s">
-        <v>9</v>
-      </c>
-      <c r="F76" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77">
-        <v>22330051920175</v>
-      </c>
-      <c r="B77" t="s">
-        <v>102</v>
-      </c>
-      <c r="C77" t="s">
-        <v>83</v>
-      </c>
-      <c r="D77" t="s">
-        <v>172</v>
-      </c>
-      <c r="E77" t="s">
-        <v>8</v>
-      </c>
-      <c r="F77" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78">
-        <v>22330051920287</v>
-      </c>
-      <c r="B78" t="s">
-        <v>103</v>
-      </c>
-      <c r="C78" t="s">
-        <v>134</v>
-      </c>
-      <c r="D78" t="s">
-        <v>173</v>
-      </c>
-      <c r="E78" t="s">
-        <v>9</v>
-      </c>
-      <c r="F78" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79">
-        <v>22330051920287</v>
-      </c>
-      <c r="B79" t="s">
-        <v>103</v>
-      </c>
-      <c r="C79" t="s">
-        <v>134</v>
-      </c>
-      <c r="D79" t="s">
-        <v>173</v>
-      </c>
-      <c r="E79" t="s">
-        <v>8</v>
-      </c>
-      <c r="F79" t="s">
         <v>64</v>
       </c>
     </row>
@@ -9189,7 +8412,7 @@
         <v>135</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -9206,7 +8429,7 @@
         <v>136</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -9223,7 +8446,7 @@
         <v>137</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -9240,7 +8463,7 @@
         <v>138</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -9257,7 +8480,7 @@
         <v>139</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -9274,7 +8497,7 @@
         <v>140</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -9291,7 +8514,7 @@
         <v>141</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -9308,7 +8531,7 @@
         <v>142</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -9325,7 +8548,7 @@
         <v>143</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -9342,7 +8565,7 @@
         <v>144</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -9359,7 +8582,7 @@
         <v>145</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -9376,7 +8599,7 @@
         <v>146</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -9393,7 +8616,7 @@
         <v>147</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -9410,7 +8633,7 @@
         <v>148</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -9427,7 +8650,7 @@
         <v>149</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -9444,7 +8667,7 @@
         <v>150</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -9461,7 +8684,7 @@
         <v>151</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -9478,7 +8701,7 @@
         <v>152</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -9495,7 +8718,7 @@
         <v>153</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -9512,7 +8735,7 @@
         <v>154</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -9529,7 +8752,7 @@
         <v>155</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -9546,7 +8769,7 @@
         <v>156</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -9563,7 +8786,7 @@
         <v>157</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -9580,7 +8803,7 @@
         <v>158</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -9597,7 +8820,7 @@
         <v>159</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -9614,7 +8837,7 @@
         <v>160</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -9631,7 +8854,7 @@
         <v>161</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -9648,7 +8871,7 @@
         <v>162</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -9665,7 +8888,7 @@
         <v>163</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -9682,7 +8905,7 @@
         <v>164</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -9699,7 +8922,7 @@
         <v>165</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -9716,7 +8939,7 @@
         <v>166</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -9733,7 +8956,7 @@
         <v>167</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -9750,7 +8973,7 @@
         <v>168</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -9767,7 +8990,7 @@
         <v>169</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -9784,7 +9007,7 @@
         <v>170</v>
       </c>
       <c r="E37">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -9801,7 +9024,7 @@
         <v>171</v>
       </c>
       <c r="E38">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -9818,7 +9041,7 @@
         <v>172</v>
       </c>
       <c r="E39">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -9835,7 +9058,7 @@
         <v>173</v>
       </c>
       <c r="E40">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -9845,7 +9068,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -9877,39 +9100,39 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920149</v>
+        <v>22330051920383</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920149</v>
+        <v>22330051920383</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -9923,39 +9146,39 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920151</v>
+        <v>22330051920155</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D4" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920151</v>
+        <v>22330051920155</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D5" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -9969,39 +9192,39 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920292</v>
+        <v>22330051920381</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D6" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920292</v>
+        <v>22330051920381</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D7" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -10015,39 +9238,39 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920153</v>
+        <v>22330051920163</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="D8" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920153</v>
+        <v>22330051920163</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="C9" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="D9" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -10061,39 +9284,39 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920156</v>
+        <v>22330051920299</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="C10" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="D10" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920156</v>
+        <v>22330051920299</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="C11" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="D11" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -10107,39 +9330,39 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920154</v>
+        <v>22330051920164</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="C12" t="s">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="D12" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920154</v>
+        <v>22330051920164</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="C13" t="s">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="D13" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -10153,39 +9376,39 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920158</v>
+        <v>22330051920170</v>
       </c>
       <c r="B14" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="C14" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="D14" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920158</v>
+        <v>22330051920170</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="C15" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="D15" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -10199,39 +9422,39 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920162</v>
+        <v>22330051920287</v>
       </c>
       <c r="B16" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="C16" t="s">
-        <v>98</v>
+        <v>134</v>
       </c>
       <c r="D16" t="s">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920162</v>
+        <v>22330051920287</v>
       </c>
       <c r="B17" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="C17" t="s">
-        <v>98</v>
+        <v>134</v>
       </c>
       <c r="D17" t="s">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
@@ -10245,19 +9468,19 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920165</v>
+        <v>22330051920149</v>
       </c>
       <c r="B18" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="C18" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="D18" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
         <v>64</v>
@@ -10268,16 +9491,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920165</v>
+        <v>22330051920151</v>
       </c>
       <c r="B19" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="C19" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D19" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
@@ -10291,19 +9514,19 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920385</v>
+        <v>22330051920292</v>
       </c>
       <c r="B20" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="C20" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="D20" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="E20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F20" t="s">
         <v>64</v>
@@ -10314,16 +9537,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>22330051920385</v>
+        <v>22330051920153</v>
       </c>
       <c r="B21" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="C21" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="D21" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
@@ -10337,19 +9560,19 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22330051920269</v>
+        <v>22330051920156</v>
       </c>
       <c r="B22" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="C22" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="D22" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="E22" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F22" t="s">
         <v>64</v>
@@ -10360,16 +9583,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>22330051920269</v>
+        <v>22330051920154</v>
       </c>
       <c r="B23" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="C23" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="D23" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="E23" t="s">
         <v>9</v>
@@ -10383,19 +9606,19 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>22330051920167</v>
+        <v>22330051920158</v>
       </c>
       <c r="B24" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C24" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D24" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="E24" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F24" t="s">
         <v>64</v>
@@ -10406,16 +9629,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>22330051920167</v>
+        <v>22330051920162</v>
       </c>
       <c r="B25" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C25" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="D25" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="E25" t="s">
         <v>9</v>
@@ -10429,19 +9652,19 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>22330051920168</v>
+        <v>22330051920165</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C26" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="D26" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="E26" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F26" t="s">
         <v>64</v>
@@ -10452,16 +9675,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>22330051920168</v>
+        <v>22330051920385</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C27" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="D27" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E27" t="s">
         <v>9</v>
@@ -10475,19 +9698,19 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>22330051920169</v>
+        <v>22330051920269</v>
       </c>
       <c r="B28" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C28" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D28" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E28" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F28" t="s">
         <v>64</v>
@@ -10498,16 +9721,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>22330051920169</v>
+        <v>22330051920167</v>
       </c>
       <c r="B29" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C29" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D29" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E29" t="s">
         <v>9</v>
@@ -10521,19 +9744,19 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>22330051920275</v>
+        <v>22330051920168</v>
       </c>
       <c r="B30" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C30" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="D30" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E30" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F30" t="s">
         <v>64</v>
@@ -10544,16 +9767,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>22330051920275</v>
+        <v>22330051920169</v>
       </c>
       <c r="B31" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C31" t="s">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="D31" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E31" t="s">
         <v>9</v>
@@ -10567,19 +9790,19 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>22330051920278</v>
+        <v>22330051920275</v>
       </c>
       <c r="B32" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C32" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="D32" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E32" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F32" t="s">
         <v>64</v>
@@ -10625,7 +9848,7 @@
         <v>168</v>
       </c>
       <c r="E34" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F34" t="s">
         <v>64</v>
@@ -10636,16 +9859,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>22330051920171</v>
+        <v>22330051920174</v>
       </c>
       <c r="B35" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C35" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D35" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E35" t="s">
         <v>9</v>
@@ -10659,19 +9882,19 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>22330051920174</v>
+        <v>22330051920387</v>
       </c>
       <c r="B36" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C36" t="s">
-        <v>132</v>
+        <v>89</v>
       </c>
       <c r="D36" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E36" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F36" t="s">
         <v>64</v>
@@ -10682,16 +9905,16 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>22330051920174</v>
+        <v>22330051920284</v>
       </c>
       <c r="B37" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C37" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D37" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E37" t="s">
         <v>9</v>
@@ -10700,98 +9923,6 @@
         <v>64</v>
       </c>
       <c r="G37">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>22330051920387</v>
-      </c>
-      <c r="B38" t="s">
-        <v>100</v>
-      </c>
-      <c r="C38" t="s">
-        <v>89</v>
-      </c>
-      <c r="D38" t="s">
-        <v>170</v>
-      </c>
-      <c r="E38" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" t="s">
-        <v>64</v>
-      </c>
-      <c r="G38">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>22330051920387</v>
-      </c>
-      <c r="B39" t="s">
-        <v>100</v>
-      </c>
-      <c r="C39" t="s">
-        <v>89</v>
-      </c>
-      <c r="D39" t="s">
-        <v>170</v>
-      </c>
-      <c r="E39" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" t="s">
-        <v>64</v>
-      </c>
-      <c r="G39">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40">
-        <v>22330051920284</v>
-      </c>
-      <c r="B40" t="s">
-        <v>101</v>
-      </c>
-      <c r="C40" t="s">
-        <v>133</v>
-      </c>
-      <c r="D40" t="s">
-        <v>171</v>
-      </c>
-      <c r="E40" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" t="s">
-        <v>64</v>
-      </c>
-      <c r="G40">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41">
-        <v>22330051920284</v>
-      </c>
-      <c r="B41" t="s">
-        <v>101</v>
-      </c>
-      <c r="C41" t="s">
-        <v>133</v>
-      </c>
-      <c r="D41" t="s">
-        <v>171</v>
-      </c>
-      <c r="E41" t="s">
-        <v>9</v>
-      </c>
-      <c r="F41" t="s">
-        <v>64</v>
-      </c>
-      <c r="G41">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/2APM - Estadisticos 20222.xlsx
+++ b/grupos/2APM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="174">
   <si>
     <t>Materia</t>
   </si>
@@ -213,10 +213,10 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Herrera Serrano Mayra Iliana</t>
+  </si>
+  <si>
     <t>Desc Desc Desc</t>
-  </si>
-  <si>
-    <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
     <t>De Jesús Orduña Sofía del Pilar</t>
@@ -1054,7 +1054,7 @@
         <v>10</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>10</v>
@@ -1117,7 +1117,7 @@
         <v>10</v>
       </c>
       <c r="AA4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB4">
         <v>10</v>
@@ -1143,7 +1143,7 @@
         <v>4</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G5">
         <v>10</v>
@@ -1206,7 +1206,7 @@
         <v>5</v>
       </c>
       <c r="AA5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB5">
         <v>10</v>
@@ -1232,7 +1232,7 @@
         <v>7</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G6">
         <v>10</v>
@@ -1295,7 +1295,7 @@
         <v>7</v>
       </c>
       <c r="AA6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB6">
         <v>10</v>
@@ -1321,7 +1321,7 @@
         <v>6</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G7">
         <v>8</v>
@@ -1384,7 +1384,7 @@
         <v>6</v>
       </c>
       <c r="AA7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB7">
         <v>8</v>
@@ -1410,7 +1410,7 @@
         <v>6</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G8">
         <v>10</v>
@@ -1473,7 +1473,7 @@
         <v>6</v>
       </c>
       <c r="AA8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB8">
         <v>10</v>
@@ -1499,7 +1499,7 @@
         <v>3</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -1562,7 +1562,7 @@
         <v>5</v>
       </c>
       <c r="AA9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB9">
         <v>5</v>
@@ -1588,7 +1588,7 @@
         <v>6</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G10">
         <v>8</v>
@@ -1651,7 +1651,7 @@
         <v>6</v>
       </c>
       <c r="AA10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB10">
         <v>8</v>
@@ -1677,7 +1677,7 @@
         <v>9</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G11">
         <v>10</v>
@@ -1740,7 +1740,7 @@
         <v>9</v>
       </c>
       <c r="AA11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB11">
         <v>10</v>
@@ -1766,7 +1766,7 @@
         <v>6</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G12">
         <v>8</v>
@@ -1829,7 +1829,7 @@
         <v>6</v>
       </c>
       <c r="AA12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB12">
         <v>8</v>
@@ -1855,7 +1855,7 @@
         <v>4</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G13">
         <v>7</v>
@@ -1918,7 +1918,7 @@
         <v>5</v>
       </c>
       <c r="AA13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB13">
         <v>7</v>
@@ -1944,7 +1944,7 @@
         <v>6</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G14">
         <v>7</v>
@@ -2007,7 +2007,7 @@
         <v>6</v>
       </c>
       <c r="AA14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB14">
         <v>7</v>
@@ -2033,7 +2033,7 @@
         <v>6</v>
       </c>
       <c r="F15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G15">
         <v>8</v>
@@ -2096,7 +2096,7 @@
         <v>6</v>
       </c>
       <c r="AA15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB15">
         <v>8</v>
@@ -2122,7 +2122,7 @@
         <v>6</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G16">
         <v>7</v>
@@ -2185,7 +2185,7 @@
         <v>6</v>
       </c>
       <c r="AA16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB16">
         <v>7</v>
@@ -2211,7 +2211,7 @@
         <v>6</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G17">
         <v>10</v>
@@ -2274,7 +2274,7 @@
         <v>6</v>
       </c>
       <c r="AA17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB17">
         <v>10</v>
@@ -2300,7 +2300,7 @@
         <v>4</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G18">
         <v>7</v>
@@ -2363,7 +2363,7 @@
         <v>5</v>
       </c>
       <c r="AA18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB18">
         <v>7</v>
@@ -2389,7 +2389,7 @@
         <v>4</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G19">
         <v>7</v>
@@ -2452,7 +2452,7 @@
         <v>5</v>
       </c>
       <c r="AA19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB19">
         <v>7</v>
@@ -2478,7 +2478,7 @@
         <v>3</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G20">
         <v>8</v>
@@ -2541,7 +2541,7 @@
         <v>5</v>
       </c>
       <c r="AA20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB20">
         <v>8</v>
@@ -2567,7 +2567,7 @@
         <v>7</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G21">
         <v>10</v>
@@ -2630,7 +2630,7 @@
         <v>8</v>
       </c>
       <c r="AA21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB21">
         <v>10</v>
@@ -2656,7 +2656,7 @@
         <v>4</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G22">
         <v>5</v>
@@ -2719,7 +2719,7 @@
         <v>5</v>
       </c>
       <c r="AA22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB22">
         <v>5</v>
@@ -2745,7 +2745,7 @@
         <v>6</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G23">
         <v>9</v>
@@ -2808,7 +2808,7 @@
         <v>6</v>
       </c>
       <c r="AA23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB23">
         <v>9</v>
@@ -2834,7 +2834,7 @@
         <v>6</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G24">
         <v>9</v>
@@ -2897,7 +2897,7 @@
         <v>6</v>
       </c>
       <c r="AA24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB24">
         <v>9</v>
@@ -2923,7 +2923,7 @@
         <v>6</v>
       </c>
       <c r="F25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G25">
         <v>10</v>
@@ -2986,7 +2986,7 @@
         <v>6</v>
       </c>
       <c r="AA25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB25">
         <v>10</v>
@@ -3012,7 +3012,7 @@
         <v>8</v>
       </c>
       <c r="F26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G26">
         <v>10</v>
@@ -3075,7 +3075,7 @@
         <v>8</v>
       </c>
       <c r="AA26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB26">
         <v>10</v>
@@ -3101,7 +3101,7 @@
         <v>7</v>
       </c>
       <c r="F27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G27">
         <v>10</v>
@@ -3164,7 +3164,7 @@
         <v>7</v>
       </c>
       <c r="AA27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB27">
         <v>10</v>
@@ -3190,7 +3190,7 @@
         <v>7</v>
       </c>
       <c r="F28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G28">
         <v>10</v>
@@ -3253,7 +3253,7 @@
         <v>7</v>
       </c>
       <c r="AA28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB28">
         <v>10</v>
@@ -3279,7 +3279,7 @@
         <v>7</v>
       </c>
       <c r="F29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G29">
         <v>10</v>
@@ -3342,7 +3342,7 @@
         <v>7</v>
       </c>
       <c r="AA29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB29">
         <v>10</v>
@@ -3368,7 +3368,7 @@
         <v>8</v>
       </c>
       <c r="F30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G30">
         <v>10</v>
@@ -3431,7 +3431,7 @@
         <v>8</v>
       </c>
       <c r="AA30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB30">
         <v>10</v>
@@ -3457,7 +3457,7 @@
         <v>8</v>
       </c>
       <c r="F31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G31">
         <v>8</v>
@@ -3520,7 +3520,7 @@
         <v>8</v>
       </c>
       <c r="AA31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB31">
         <v>8</v>
@@ -3546,7 +3546,7 @@
         <v>10</v>
       </c>
       <c r="F32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G32">
         <v>10</v>
@@ -3609,7 +3609,7 @@
         <v>10</v>
       </c>
       <c r="AA32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB32">
         <v>10</v>
@@ -3635,7 +3635,7 @@
         <v>4</v>
       </c>
       <c r="F33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G33">
         <v>7</v>
@@ -3698,7 +3698,7 @@
         <v>5</v>
       </c>
       <c r="AA33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB33">
         <v>7</v>
@@ -3724,7 +3724,7 @@
         <v>6</v>
       </c>
       <c r="F34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G34">
         <v>8</v>
@@ -3787,7 +3787,7 @@
         <v>6</v>
       </c>
       <c r="AA34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB34">
         <v>8</v>
@@ -3813,7 +3813,7 @@
         <v>7</v>
       </c>
       <c r="F35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G35">
         <v>8</v>
@@ -3876,7 +3876,7 @@
         <v>7</v>
       </c>
       <c r="AA35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB35">
         <v>8</v>
@@ -3902,7 +3902,7 @@
         <v>7</v>
       </c>
       <c r="F36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G36">
         <v>10</v>
@@ -3965,7 +3965,7 @@
         <v>7</v>
       </c>
       <c r="AA36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB36">
         <v>10</v>
@@ -3991,7 +3991,7 @@
         <v>5</v>
       </c>
       <c r="F37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G37">
         <v>8</v>
@@ -4054,7 +4054,7 @@
         <v>5</v>
       </c>
       <c r="AA37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB37">
         <v>8</v>
@@ -4080,7 +4080,7 @@
         <v>9</v>
       </c>
       <c r="F38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G38">
         <v>10</v>
@@ -4143,7 +4143,7 @@
         <v>9</v>
       </c>
       <c r="AA38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB38">
         <v>10</v>
@@ -4169,7 +4169,7 @@
         <v>7</v>
       </c>
       <c r="F39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G39">
         <v>10</v>
@@ -4232,7 +4232,7 @@
         <v>7</v>
       </c>
       <c r="AA39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB39">
         <v>10</v>
@@ -4258,7 +4258,7 @@
         <v>4</v>
       </c>
       <c r="F40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G40">
         <v>6</v>
@@ -4321,7 +4321,7 @@
         <v>5</v>
       </c>
       <c r="AA40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB40">
         <v>6</v>
@@ -4347,7 +4347,7 @@
         <v>6</v>
       </c>
       <c r="F41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G41">
         <v>10</v>
@@ -4410,7 +4410,7 @@
         <v>6</v>
       </c>
       <c r="AA41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB41">
         <v>10</v>
@@ -4436,7 +4436,7 @@
         <v>6</v>
       </c>
       <c r="F42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G42">
         <v>8</v>
@@ -4499,7 +4499,7 @@
         <v>6</v>
       </c>
       <c r="AA42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB42">
         <v>8</v>
@@ -4647,7 +4647,7 @@
         <v>100</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G4">
         <v>95</v>
@@ -4715,7 +4715,7 @@
         <v>100</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="G5">
         <v>80</v>
@@ -4783,7 +4783,7 @@
         <v>100</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G6">
         <v>95</v>
@@ -4851,7 +4851,7 @@
         <v>100</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G7">
         <v>90</v>
@@ -4919,7 +4919,7 @@
         <v>100</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G8">
         <v>85</v>
@@ -4987,7 +4987,7 @@
         <v>85</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G9">
         <v>55</v>
@@ -5055,7 +5055,7 @@
         <v>100</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G10">
         <v>95</v>
@@ -5123,7 +5123,7 @@
         <v>100</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G11">
         <v>100</v>
@@ -5191,7 +5191,7 @@
         <v>100</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G12">
         <v>85</v>
@@ -5259,7 +5259,7 @@
         <v>85</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="G13">
         <v>70</v>
@@ -5327,7 +5327,7 @@
         <v>100</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G14">
         <v>90</v>
@@ -5395,7 +5395,7 @@
         <v>100</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15">
         <v>100</v>
@@ -5463,7 +5463,7 @@
         <v>100</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G16">
         <v>80</v>
@@ -5531,7 +5531,7 @@
         <v>100</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G17">
         <v>85</v>
@@ -5599,7 +5599,7 @@
         <v>100</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G18">
         <v>85</v>
@@ -5667,7 +5667,7 @@
         <v>100</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G19">
         <v>80</v>
@@ -5735,7 +5735,7 @@
         <v>100</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G20">
         <v>95</v>
@@ -5803,7 +5803,7 @@
         <v>100</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G21">
         <v>90</v>
@@ -5871,7 +5871,7 @@
         <v>100</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G22">
         <v>90</v>
@@ -5939,7 +5939,7 @@
         <v>100</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G23">
         <v>100</v>
@@ -6007,7 +6007,7 @@
         <v>100</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G24">
         <v>95</v>
@@ -6075,7 +6075,7 @@
         <v>100</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G25">
         <v>95</v>
@@ -6143,7 +6143,7 @@
         <v>100</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G26">
         <v>90</v>
@@ -6211,7 +6211,7 @@
         <v>100</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G27">
         <v>100</v>
@@ -6279,7 +6279,7 @@
         <v>100</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G28">
         <v>95</v>
@@ -6347,7 +6347,7 @@
         <v>100</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G29">
         <v>100</v>
@@ -6415,7 +6415,7 @@
         <v>100</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G30">
         <v>100</v>
@@ -6483,7 +6483,7 @@
         <v>100</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G31">
         <v>90</v>
@@ -6551,7 +6551,7 @@
         <v>100</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G32">
         <v>95</v>
@@ -6619,7 +6619,7 @@
         <v>100</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G33">
         <v>100</v>
@@ -6687,7 +6687,7 @@
         <v>100</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G34">
         <v>100</v>
@@ -6755,7 +6755,7 @@
         <v>100</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="G35">
         <v>85</v>
@@ -6823,7 +6823,7 @@
         <v>100</v>
       </c>
       <c r="F36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G36">
         <v>80</v>
@@ -6891,7 +6891,7 @@
         <v>100</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G37">
         <v>70</v>
@@ -6959,7 +6959,7 @@
         <v>100</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G38">
         <v>100</v>
@@ -7027,7 +7027,7 @@
         <v>100</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G39">
         <v>100</v>
@@ -7095,7 +7095,7 @@
         <v>100</v>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G40">
         <v>85</v>
@@ -7163,7 +7163,7 @@
         <v>100</v>
       </c>
       <c r="F41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G41">
         <v>95</v>
@@ -7231,7 +7231,7 @@
         <v>100</v>
       </c>
       <c r="F42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G42">
         <v>90</v>
@@ -7334,7 +7334,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
@@ -7343,27 +7343,30 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>56.41</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>43.59</v>
+      </c>
+      <c r="H2">
+        <v>6.6</v>
       </c>
       <c r="I2">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>65</v>
@@ -7372,19 +7375,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E3">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>56.41</v>
+        <v>74.36</v>
       </c>
       <c r="G3">
-        <v>43.59</v>
+        <v>25.64</v>
       </c>
       <c r="H3">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7395,28 +7398,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C4">
         <v>39</v>
       </c>
       <c r="D4">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>74.36</v>
+        <v>87.18000000000001</v>
       </c>
       <c r="G4">
-        <v>25.64</v>
+        <v>12.82</v>
       </c>
       <c r="H4">
-        <v>6.5</v>
+        <v>7.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7427,10 +7430,10 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C5">
         <v>39</v>
@@ -7448,7 +7451,7 @@
         <v>12.82</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7459,28 +7462,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C6">
         <v>39</v>
       </c>
       <c r="D6">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>87.18000000000001</v>
+        <v>92.31</v>
       </c>
       <c r="G6">
-        <v>12.82</v>
+        <v>7.69</v>
       </c>
       <c r="H6">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7494,7 +7497,7 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C7">
         <v>39</v>
@@ -7560,7 +7563,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7585,786 +7588,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>22330051920149</v>
-      </c>
-      <c r="B2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D2" t="s">
-        <v>135</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>22330051920150</v>
-      </c>
-      <c r="B3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C3" t="s">
-        <v>105</v>
-      </c>
-      <c r="D3" t="s">
-        <v>136</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>22330051920151</v>
-      </c>
-      <c r="B4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D4" t="s">
-        <v>137</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>22330051920292</v>
-      </c>
-      <c r="B5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C5" t="s">
-        <v>107</v>
-      </c>
-      <c r="D5" t="s">
-        <v>138</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>22330051920383</v>
-      </c>
-      <c r="B6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C6" t="s">
-        <v>108</v>
-      </c>
-      <c r="D6" t="s">
-        <v>139</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>22330051920153</v>
-      </c>
-      <c r="B7" t="s">
-        <v>77</v>
-      </c>
-      <c r="C7" t="s">
-        <v>109</v>
-      </c>
-      <c r="D7" t="s">
-        <v>140</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>22330051920155</v>
-      </c>
-      <c r="B8" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D8" t="s">
-        <v>141</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>22330051920156</v>
-      </c>
-      <c r="B9" t="s">
-        <v>78</v>
-      </c>
-      <c r="C9" t="s">
-        <v>111</v>
-      </c>
-      <c r="D9" t="s">
-        <v>142</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>22330051920154</v>
-      </c>
-      <c r="B10" t="s">
-        <v>79</v>
-      </c>
-      <c r="C10" t="s">
-        <v>95</v>
-      </c>
-      <c r="D10" t="s">
-        <v>143</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>22330051920381</v>
-      </c>
-      <c r="B11" t="s">
-        <v>80</v>
-      </c>
-      <c r="C11" t="s">
-        <v>112</v>
-      </c>
-      <c r="D11" t="s">
-        <v>144</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>22330051920152</v>
-      </c>
-      <c r="B12" t="s">
-        <v>81</v>
-      </c>
-      <c r="C12" t="s">
-        <v>113</v>
-      </c>
-      <c r="D12" t="s">
-        <v>145</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>22330051920384</v>
-      </c>
-      <c r="B13" t="s">
-        <v>82</v>
-      </c>
-      <c r="C13" t="s">
-        <v>114</v>
-      </c>
-      <c r="D13" t="s">
-        <v>146</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>22330051920157</v>
-      </c>
-      <c r="B14" t="s">
-        <v>83</v>
-      </c>
-      <c r="C14" t="s">
-        <v>115</v>
-      </c>
-      <c r="D14" t="s">
-        <v>147</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>22330051920161</v>
-      </c>
-      <c r="B15" t="s">
-        <v>84</v>
-      </c>
-      <c r="C15" t="s">
-        <v>116</v>
-      </c>
-      <c r="D15" t="s">
-        <v>148</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>22330051920158</v>
-      </c>
-      <c r="B16" t="s">
-        <v>85</v>
-      </c>
-      <c r="C16" t="s">
-        <v>117</v>
-      </c>
-      <c r="D16" t="s">
-        <v>149</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>22330051920159</v>
-      </c>
-      <c r="B17" t="s">
-        <v>85</v>
-      </c>
-      <c r="C17" t="s">
-        <v>118</v>
-      </c>
-      <c r="D17" t="s">
-        <v>150</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>22330051920162</v>
-      </c>
-      <c r="B18" t="s">
-        <v>86</v>
-      </c>
-      <c r="C18" t="s">
-        <v>98</v>
-      </c>
-      <c r="D18" t="s">
-        <v>151</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>22330051920160</v>
-      </c>
-      <c r="B19" t="s">
-        <v>85</v>
-      </c>
-      <c r="C19" t="s">
-        <v>119</v>
-      </c>
-      <c r="D19" t="s">
-        <v>152</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>22330051920296</v>
-      </c>
-      <c r="B20" t="s">
-        <v>87</v>
-      </c>
-      <c r="C20" t="s">
-        <v>120</v>
-      </c>
-      <c r="D20" t="s">
-        <v>153</v>
-      </c>
-      <c r="E20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>22330051920163</v>
-      </c>
-      <c r="B21" t="s">
-        <v>88</v>
-      </c>
-      <c r="C21" t="s">
-        <v>89</v>
-      </c>
-      <c r="D21" t="s">
-        <v>154</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>22330051920299</v>
-      </c>
-      <c r="B22" t="s">
-        <v>89</v>
-      </c>
-      <c r="C22" t="s">
-        <v>121</v>
-      </c>
-      <c r="D22" t="s">
-        <v>155</v>
-      </c>
-      <c r="E22" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>22330051920165</v>
-      </c>
-      <c r="B23" t="s">
-        <v>89</v>
-      </c>
-      <c r="C23" t="s">
-        <v>122</v>
-      </c>
-      <c r="D23" t="s">
-        <v>156</v>
-      </c>
-      <c r="E23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>22330051920385</v>
-      </c>
-      <c r="B24" t="s">
-        <v>90</v>
-      </c>
-      <c r="C24" t="s">
-        <v>123</v>
-      </c>
-      <c r="D24" t="s">
-        <v>157</v>
-      </c>
-      <c r="E24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>22330051920164</v>
-      </c>
-      <c r="B25" t="s">
-        <v>91</v>
-      </c>
-      <c r="C25" t="s">
-        <v>124</v>
-      </c>
-      <c r="D25" t="s">
-        <v>158</v>
-      </c>
-      <c r="E25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>22330051920269</v>
-      </c>
-      <c r="B26" t="s">
-        <v>92</v>
-      </c>
-      <c r="C26" t="s">
-        <v>125</v>
-      </c>
-      <c r="D26" t="s">
-        <v>159</v>
-      </c>
-      <c r="E26" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>22330051920167</v>
-      </c>
-      <c r="B27" t="s">
-        <v>92</v>
-      </c>
-      <c r="C27" t="s">
-        <v>126</v>
-      </c>
-      <c r="D27" t="s">
-        <v>160</v>
-      </c>
-      <c r="E27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>22330051920168</v>
-      </c>
-      <c r="B28" t="s">
-        <v>93</v>
-      </c>
-      <c r="C28" t="s">
-        <v>92</v>
-      </c>
-      <c r="D28" t="s">
-        <v>161</v>
-      </c>
-      <c r="E28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>22330051920169</v>
-      </c>
-      <c r="B29" t="s">
-        <v>94</v>
-      </c>
-      <c r="C29" t="s">
-        <v>127</v>
-      </c>
-      <c r="D29" t="s">
-        <v>162</v>
-      </c>
-      <c r="E29" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>22330051920170</v>
-      </c>
-      <c r="B30" t="s">
-        <v>95</v>
-      </c>
-      <c r="C30" t="s">
-        <v>128</v>
-      </c>
-      <c r="D30" t="s">
-        <v>163</v>
-      </c>
-      <c r="E30" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>22330051920275</v>
-      </c>
-      <c r="B31" t="s">
-        <v>96</v>
-      </c>
-      <c r="C31" t="s">
-        <v>82</v>
-      </c>
-      <c r="D31" t="s">
-        <v>164</v>
-      </c>
-      <c r="E31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>22330051920386</v>
-      </c>
-      <c r="B32" t="s">
-        <v>96</v>
-      </c>
-      <c r="C32" t="s">
-        <v>129</v>
-      </c>
-      <c r="D32" t="s">
-        <v>165</v>
-      </c>
-      <c r="E32" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>22330051920172</v>
-      </c>
-      <c r="B33" t="s">
-        <v>97</v>
-      </c>
-      <c r="C33" t="s">
-        <v>130</v>
-      </c>
-      <c r="D33" t="s">
-        <v>166</v>
-      </c>
-      <c r="E33" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>22330051920278</v>
-      </c>
-      <c r="B34" t="s">
-        <v>98</v>
-      </c>
-      <c r="C34" t="s">
-        <v>89</v>
-      </c>
-      <c r="D34" t="s">
-        <v>167</v>
-      </c>
-      <c r="E34" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>22330051920171</v>
-      </c>
-      <c r="B35" t="s">
-        <v>98</v>
-      </c>
-      <c r="C35" t="s">
-        <v>131</v>
-      </c>
-      <c r="D35" t="s">
-        <v>168</v>
-      </c>
-      <c r="E35" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>22330051920174</v>
-      </c>
-      <c r="B36" t="s">
-        <v>99</v>
-      </c>
-      <c r="C36" t="s">
-        <v>132</v>
-      </c>
-      <c r="D36" t="s">
-        <v>169</v>
-      </c>
-      <c r="E36" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>22330051920387</v>
-      </c>
-      <c r="B37" t="s">
-        <v>100</v>
-      </c>
-      <c r="C37" t="s">
-        <v>89</v>
-      </c>
-      <c r="D37" t="s">
-        <v>170</v>
-      </c>
-      <c r="E37" t="s">
-        <v>9</v>
-      </c>
-      <c r="F37" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>22330051920284</v>
-      </c>
-      <c r="B38" t="s">
-        <v>101</v>
-      </c>
-      <c r="C38" t="s">
-        <v>133</v>
-      </c>
-      <c r="D38" t="s">
-        <v>171</v>
-      </c>
-      <c r="E38" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>22330051920175</v>
-      </c>
-      <c r="B39" t="s">
-        <v>102</v>
-      </c>
-      <c r="C39" t="s">
-        <v>83</v>
-      </c>
-      <c r="D39" t="s">
-        <v>172</v>
-      </c>
-      <c r="E39" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>22330051920287</v>
-      </c>
-      <c r="B40" t="s">
-        <v>103</v>
-      </c>
-      <c r="C40" t="s">
-        <v>134</v>
-      </c>
-      <c r="D40" t="s">
-        <v>173</v>
-      </c>
-      <c r="E40" t="s">
-        <v>9</v>
-      </c>
-      <c r="F40" t="s">
-        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -8412,7 +7635,7 @@
         <v>135</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -8429,7 +7652,7 @@
         <v>136</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -8446,7 +7669,7 @@
         <v>137</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -8463,7 +7686,7 @@
         <v>138</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -8480,7 +7703,7 @@
         <v>139</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -8497,7 +7720,7 @@
         <v>140</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -8514,7 +7737,7 @@
         <v>141</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -8531,7 +7754,7 @@
         <v>142</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -8548,7 +7771,7 @@
         <v>143</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -8565,7 +7788,7 @@
         <v>144</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -8582,7 +7805,7 @@
         <v>145</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -8599,7 +7822,7 @@
         <v>146</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -8616,7 +7839,7 @@
         <v>147</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -8633,7 +7856,7 @@
         <v>148</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -8650,7 +7873,7 @@
         <v>149</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -8667,7 +7890,7 @@
         <v>150</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -8684,7 +7907,7 @@
         <v>151</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -8701,7 +7924,7 @@
         <v>152</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -8718,7 +7941,7 @@
         <v>153</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -8735,7 +7958,7 @@
         <v>154</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -8752,7 +7975,7 @@
         <v>155</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -8769,7 +7992,7 @@
         <v>156</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -8786,7 +8009,7 @@
         <v>157</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -8803,7 +8026,7 @@
         <v>158</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -8820,7 +8043,7 @@
         <v>159</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -8837,7 +8060,7 @@
         <v>160</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -8854,7 +8077,7 @@
         <v>161</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -8871,7 +8094,7 @@
         <v>162</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -8888,7 +8111,7 @@
         <v>163</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -8905,7 +8128,7 @@
         <v>164</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -8922,7 +8145,7 @@
         <v>165</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -8939,7 +8162,7 @@
         <v>166</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -8956,7 +8179,7 @@
         <v>167</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -8973,7 +8196,7 @@
         <v>168</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -8990,7 +8213,7 @@
         <v>169</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -9007,7 +8230,7 @@
         <v>170</v>
       </c>
       <c r="E37">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -9024,7 +8247,7 @@
         <v>171</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -9041,7 +8264,7 @@
         <v>172</v>
       </c>
       <c r="E39">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -9058,7 +8281,7 @@
         <v>173</v>
       </c>
       <c r="E40">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -9068,7 +8291,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -9100,19 +8323,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920383</v>
+        <v>22330051920150</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
         <v>65</v>
@@ -9123,45 +8346,45 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920383</v>
+        <v>22330051920150</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920155</v>
+        <v>22330051920386</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="C4" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="D4" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -9169,45 +8392,45 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920155</v>
+        <v>22330051920386</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="C5" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="D5" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920381</v>
+        <v>22330051920172</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="C6" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="D6" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -9215,45 +8438,45 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920381</v>
+        <v>22330051920172</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="C7" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="D7" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920163</v>
+        <v>22330051920175</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -9261,45 +8484,45 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920163</v>
+        <v>22330051920175</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="C9" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920299</v>
+        <v>22330051920383</v>
       </c>
       <c r="B10" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="C10" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="D10" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -9307,45 +8530,45 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920299</v>
+        <v>22330051920155</v>
       </c>
       <c r="B11" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="D11" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
         <v>64</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920164</v>
+        <v>22330051920381</v>
       </c>
       <c r="B12" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="D12" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="E12" t="s">
         <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -9353,45 +8576,45 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920164</v>
+        <v>22330051920163</v>
       </c>
       <c r="B13" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>124</v>
+        <v>89</v>
       </c>
       <c r="D13" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F13" t="s">
         <v>64</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920170</v>
+        <v>22330051920299</v>
       </c>
       <c r="B14" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C14" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D14" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -9399,45 +8622,45 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920170</v>
+        <v>22330051920164</v>
       </c>
       <c r="B15" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C15" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D15" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F15" t="s">
         <v>64</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920287</v>
+        <v>22330051920170</v>
       </c>
       <c r="B16" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C16" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="D16" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="E16" t="s">
         <v>5</v>
       </c>
       <c r="F16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -9457,473 +8680,13 @@
         <v>173</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F17" t="s">
         <v>64</v>
       </c>
       <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920149</v>
-      </c>
-      <c r="B18" t="s">
-        <v>72</v>
-      </c>
-      <c r="C18" t="s">
-        <v>104</v>
-      </c>
-      <c r="D18" t="s">
-        <v>135</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>64</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>22330051920151</v>
-      </c>
-      <c r="B19" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" t="s">
-        <v>106</v>
-      </c>
-      <c r="D19" t="s">
-        <v>137</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>64</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>22330051920292</v>
-      </c>
-      <c r="B20" t="s">
-        <v>75</v>
-      </c>
-      <c r="C20" t="s">
-        <v>107</v>
-      </c>
-      <c r="D20" t="s">
-        <v>138</v>
-      </c>
-      <c r="E20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" t="s">
-        <v>64</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>22330051920153</v>
-      </c>
-      <c r="B21" t="s">
-        <v>77</v>
-      </c>
-      <c r="C21" t="s">
-        <v>109</v>
-      </c>
-      <c r="D21" t="s">
-        <v>140</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>64</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>22330051920156</v>
-      </c>
-      <c r="B22" t="s">
-        <v>78</v>
-      </c>
-      <c r="C22" t="s">
-        <v>111</v>
-      </c>
-      <c r="D22" t="s">
-        <v>142</v>
-      </c>
-      <c r="E22" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" t="s">
-        <v>64</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>22330051920154</v>
-      </c>
-      <c r="B23" t="s">
-        <v>79</v>
-      </c>
-      <c r="C23" t="s">
-        <v>95</v>
-      </c>
-      <c r="D23" t="s">
-        <v>143</v>
-      </c>
-      <c r="E23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" t="s">
-        <v>64</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>22330051920158</v>
-      </c>
-      <c r="B24" t="s">
-        <v>85</v>
-      </c>
-      <c r="C24" t="s">
-        <v>117</v>
-      </c>
-      <c r="D24" t="s">
-        <v>149</v>
-      </c>
-      <c r="E24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" t="s">
-        <v>64</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>22330051920162</v>
-      </c>
-      <c r="B25" t="s">
-        <v>86</v>
-      </c>
-      <c r="C25" t="s">
-        <v>98</v>
-      </c>
-      <c r="D25" t="s">
-        <v>151</v>
-      </c>
-      <c r="E25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" t="s">
-        <v>64</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>22330051920165</v>
-      </c>
-      <c r="B26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C26" t="s">
-        <v>122</v>
-      </c>
-      <c r="D26" t="s">
-        <v>156</v>
-      </c>
-      <c r="E26" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" t="s">
-        <v>64</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>22330051920385</v>
-      </c>
-      <c r="B27" t="s">
-        <v>90</v>
-      </c>
-      <c r="C27" t="s">
-        <v>123</v>
-      </c>
-      <c r="D27" t="s">
-        <v>157</v>
-      </c>
-      <c r="E27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" t="s">
-        <v>64</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>22330051920269</v>
-      </c>
-      <c r="B28" t="s">
-        <v>92</v>
-      </c>
-      <c r="C28" t="s">
-        <v>125</v>
-      </c>
-      <c r="D28" t="s">
-        <v>159</v>
-      </c>
-      <c r="E28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" t="s">
-        <v>64</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>22330051920167</v>
-      </c>
-      <c r="B29" t="s">
-        <v>92</v>
-      </c>
-      <c r="C29" t="s">
-        <v>126</v>
-      </c>
-      <c r="D29" t="s">
-        <v>160</v>
-      </c>
-      <c r="E29" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" t="s">
-        <v>64</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>22330051920168</v>
-      </c>
-      <c r="B30" t="s">
-        <v>93</v>
-      </c>
-      <c r="C30" t="s">
-        <v>92</v>
-      </c>
-      <c r="D30" t="s">
-        <v>161</v>
-      </c>
-      <c r="E30" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" t="s">
-        <v>64</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>22330051920169</v>
-      </c>
-      <c r="B31" t="s">
-        <v>94</v>
-      </c>
-      <c r="C31" t="s">
-        <v>127</v>
-      </c>
-      <c r="D31" t="s">
-        <v>162</v>
-      </c>
-      <c r="E31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" t="s">
-        <v>64</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>22330051920275</v>
-      </c>
-      <c r="B32" t="s">
-        <v>96</v>
-      </c>
-      <c r="C32" t="s">
-        <v>82</v>
-      </c>
-      <c r="D32" t="s">
-        <v>164</v>
-      </c>
-      <c r="E32" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" t="s">
-        <v>64</v>
-      </c>
-      <c r="G32">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>22330051920278</v>
-      </c>
-      <c r="B33" t="s">
-        <v>98</v>
-      </c>
-      <c r="C33" t="s">
-        <v>89</v>
-      </c>
-      <c r="D33" t="s">
-        <v>167</v>
-      </c>
-      <c r="E33" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" t="s">
-        <v>64</v>
-      </c>
-      <c r="G33">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>22330051920171</v>
-      </c>
-      <c r="B34" t="s">
-        <v>98</v>
-      </c>
-      <c r="C34" t="s">
-        <v>131</v>
-      </c>
-      <c r="D34" t="s">
-        <v>168</v>
-      </c>
-      <c r="E34" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" t="s">
-        <v>64</v>
-      </c>
-      <c r="G34">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>22330051920174</v>
-      </c>
-      <c r="B35" t="s">
-        <v>99</v>
-      </c>
-      <c r="C35" t="s">
-        <v>132</v>
-      </c>
-      <c r="D35" t="s">
-        <v>169</v>
-      </c>
-      <c r="E35" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" t="s">
-        <v>64</v>
-      </c>
-      <c r="G35">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>22330051920387</v>
-      </c>
-      <c r="B36" t="s">
-        <v>100</v>
-      </c>
-      <c r="C36" t="s">
-        <v>89</v>
-      </c>
-      <c r="D36" t="s">
-        <v>170</v>
-      </c>
-      <c r="E36" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" t="s">
-        <v>64</v>
-      </c>
-      <c r="G36">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>22330051920284</v>
-      </c>
-      <c r="B37" t="s">
-        <v>101</v>
-      </c>
-      <c r="C37" t="s">
-        <v>133</v>
-      </c>
-      <c r="D37" t="s">
-        <v>171</v>
-      </c>
-      <c r="E37" t="s">
-        <v>9</v>
-      </c>
-      <c r="F37" t="s">
-        <v>64</v>
-      </c>
-      <c r="G37">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/2APM - Estadisticos 20222.xlsx
+++ b/grupos/2APM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="177">
   <si>
     <t>Materia</t>
   </si>
@@ -216,10 +216,19 @@
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
-    <t>Desc Desc Desc</t>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
+    <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
     <t>De Jesús Orduña Sofía del Pilar</t>
+  </si>
+  <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
+    <t>Moreno Aroyo Anél</t>
   </si>
   <si>
     <t>Pesce Bautista Victor Manuel</t>
@@ -7401,7 +7410,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C4">
         <v>39</v>
@@ -7433,7 +7442,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C5">
         <v>39</v>
@@ -7465,7 +7474,7 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C6">
         <v>39</v>
@@ -7497,7 +7506,7 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C7">
         <v>39</v>
@@ -7529,7 +7538,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C8">
         <v>39</v>
@@ -7572,16 +7581,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -7606,16 +7615,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>62</v>
@@ -7626,13 +7635,13 @@
         <v>22330051920149</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D2" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -7643,13 +7652,13 @@
         <v>22330051920150</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -7660,13 +7669,13 @@
         <v>22330051920151</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D4" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -7677,13 +7686,13 @@
         <v>22330051920292</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D5" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -7694,13 +7703,13 @@
         <v>22330051920383</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D6" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -7711,13 +7720,13 @@
         <v>22330051920153</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D7" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -7728,13 +7737,13 @@
         <v>22330051920155</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -7745,13 +7754,13 @@
         <v>22330051920156</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D9" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -7762,13 +7771,13 @@
         <v>22330051920154</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -7779,13 +7788,13 @@
         <v>22330051920381</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D11" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -7796,13 +7805,13 @@
         <v>22330051920152</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D12" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -7813,13 +7822,13 @@
         <v>22330051920384</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C13" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D13" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -7830,13 +7839,13 @@
         <v>22330051920157</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C14" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D14" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -7847,13 +7856,13 @@
         <v>22330051920161</v>
       </c>
       <c r="B15" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C15" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D15" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -7864,13 +7873,13 @@
         <v>22330051920158</v>
       </c>
       <c r="B16" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D16" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -7881,13 +7890,13 @@
         <v>22330051920159</v>
       </c>
       <c r="B17" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D17" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -7898,13 +7907,13 @@
         <v>22330051920162</v>
       </c>
       <c r="B18" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D18" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -7915,13 +7924,13 @@
         <v>22330051920160</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C19" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D19" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -7932,13 +7941,13 @@
         <v>22330051920296</v>
       </c>
       <c r="B20" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C20" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D20" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -7949,13 +7958,13 @@
         <v>22330051920163</v>
       </c>
       <c r="B21" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C21" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D21" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -7966,13 +7975,13 @@
         <v>22330051920299</v>
       </c>
       <c r="B22" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C22" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D22" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -7983,13 +7992,13 @@
         <v>22330051920165</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C23" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D23" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -8000,13 +8009,13 @@
         <v>22330051920385</v>
       </c>
       <c r="B24" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C24" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D24" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -8017,13 +8026,13 @@
         <v>22330051920164</v>
       </c>
       <c r="B25" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C25" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D25" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -8034,13 +8043,13 @@
         <v>22330051920269</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C26" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D26" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -8051,13 +8060,13 @@
         <v>22330051920167</v>
       </c>
       <c r="B27" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C27" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D27" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -8068,13 +8077,13 @@
         <v>22330051920168</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C28" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D28" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -8085,13 +8094,13 @@
         <v>22330051920169</v>
       </c>
       <c r="B29" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C29" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D29" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -8102,13 +8111,13 @@
         <v>22330051920170</v>
       </c>
       <c r="B30" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C30" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D30" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -8119,13 +8128,13 @@
         <v>22330051920275</v>
       </c>
       <c r="B31" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C31" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D31" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -8136,13 +8145,13 @@
         <v>22330051920386</v>
       </c>
       <c r="B32" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C32" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D32" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -8153,13 +8162,13 @@
         <v>22330051920172</v>
       </c>
       <c r="B33" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C33" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D33" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -8170,13 +8179,13 @@
         <v>22330051920278</v>
       </c>
       <c r="B34" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C34" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D34" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -8187,13 +8196,13 @@
         <v>22330051920171</v>
       </c>
       <c r="B35" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C35" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D35" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -8204,13 +8213,13 @@
         <v>22330051920174</v>
       </c>
       <c r="B36" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C36" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D36" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -8221,13 +8230,13 @@
         <v>22330051920387</v>
       </c>
       <c r="B37" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C37" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D37" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -8238,13 +8247,13 @@
         <v>22330051920284</v>
       </c>
       <c r="B38" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C38" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D38" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -8255,13 +8264,13 @@
         <v>22330051920175</v>
       </c>
       <c r="B39" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C39" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D39" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -8272,13 +8281,13 @@
         <v>22330051920287</v>
       </c>
       <c r="B40" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C40" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D40" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -8300,16 +8309,16 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -8326,13 +8335,13 @@
         <v>22330051920150</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -8349,19 +8358,19 @@
         <v>22330051920150</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -8372,13 +8381,13 @@
         <v>22330051920386</v>
       </c>
       <c r="B4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D4" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -8395,13 +8404,13 @@
         <v>22330051920386</v>
       </c>
       <c r="B5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C5" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D5" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -8418,13 +8427,13 @@
         <v>22330051920172</v>
       </c>
       <c r="B6" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D6" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -8441,13 +8450,13 @@
         <v>22330051920172</v>
       </c>
       <c r="B7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C7" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D7" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -8464,13 +8473,13 @@
         <v>22330051920175</v>
       </c>
       <c r="B8" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D8" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -8487,13 +8496,13 @@
         <v>22330051920175</v>
       </c>
       <c r="B9" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D9" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -8510,13 +8519,13 @@
         <v>22330051920383</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D10" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
@@ -8533,13 +8542,13 @@
         <v>22330051920155</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D11" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E11" t="s">
         <v>5</v>
@@ -8556,13 +8565,13 @@
         <v>22330051920381</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D12" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E12" t="s">
         <v>5</v>
@@ -8579,13 +8588,13 @@
         <v>22330051920163</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D13" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E13" t="s">
         <v>5</v>
@@ -8602,13 +8611,13 @@
         <v>22330051920299</v>
       </c>
       <c r="B14" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C14" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D14" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
@@ -8625,13 +8634,13 @@
         <v>22330051920164</v>
       </c>
       <c r="B15" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C15" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D15" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E15" t="s">
         <v>5</v>
@@ -8648,13 +8657,13 @@
         <v>22330051920170</v>
       </c>
       <c r="B16" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C16" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D16" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E16" t="s">
         <v>5</v>
@@ -8671,13 +8680,13 @@
         <v>22330051920287</v>
       </c>
       <c r="B17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C17" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D17" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E17" t="s">
         <v>5</v>

--- a/grupos/2APM - Estadisticos 20222.xlsx
+++ b/grupos/2APM - Estadisticos 20222.xlsx
@@ -11,15 +11,14 @@
     <sheet name="Asistencias" sheetId="2" r:id="rId2"/>
     <sheet name="Totales" sheetId="3" r:id="rId3"/>
     <sheet name="Blancos" sheetId="4" r:id="rId4"/>
-    <sheet name="Totales Blanco" sheetId="5" r:id="rId5"/>
-    <sheet name="Rescatables" sheetId="6" r:id="rId6"/>
+    <sheet name="Rescatables" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="110">
   <si>
     <t>Materia</t>
   </si>
@@ -219,12 +218,12 @@
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
+    <t>De Jesús Orduña Sofía del Pilar</t>
+  </si>
+  <si>
     <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
-    <t>De Jesús Orduña Sofía del Pilar</t>
-  </si>
-  <si>
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
@@ -246,307 +245,106 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
     <t>BAEZ</t>
   </si>
   <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>BELLO</t>
-  </si>
-  <si>
     <t>CASTELLANOS</t>
   </si>
   <si>
-    <t>CAMARILLO</t>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
   </si>
   <si>
     <t>CASTRO</t>
   </si>
   <si>
-    <t>CARDENAS</t>
-  </si>
-  <si>
     <t>CALOCA</t>
   </si>
   <si>
-    <t>CALVO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>VELASCO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>CHICO</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>ANGUIANO</t>
   </si>
   <si>
     <t>CERON</t>
   </si>
   <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>CORRO</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>NATIVIDAD</t>
-  </si>
-  <si>
-    <t>ORTIGOZA</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>VELASCO</t>
-  </si>
-  <si>
-    <t>ZAVALETA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>PEÑA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>CHICO</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
     <t>MONTIEL</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>URIAS</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>CUAQUEHUA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>TEQUILIQUIHUA</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
     <t>LEON</t>
   </si>
   <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>GAMBINO</t>
-  </si>
-  <si>
     <t>SORIANO</t>
   </si>
   <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>VOTTE</t>
-  </si>
-  <si>
-    <t>ARGUELLES</t>
-  </si>
-  <si>
     <t>ALFONSO</t>
   </si>
   <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>ANGUIANO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>AVALOS</t>
-  </si>
-  <si>
     <t>SAN JUAN</t>
   </si>
   <si>
-    <t>CAMILA JEZABEL</t>
-  </si>
-  <si>
     <t>EDUARDO EMER</t>
   </si>
   <si>
-    <t>ISAAC ASAEL</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
     <t>EDNA YOSSELIN</t>
   </si>
   <si>
-    <t>MIGUEL ANGEL</t>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>FRIDA SOFIA</t>
   </si>
   <si>
     <t>LESLY VIANEY</t>
   </si>
   <si>
-    <t>ESMERALDA</t>
-  </si>
-  <si>
-    <t>ERICK ALEJANDRO</t>
-  </si>
-  <si>
     <t>ARLETH MARELY</t>
   </si>
   <si>
-    <t>ANGEL EMMANUEL</t>
-  </si>
-  <si>
-    <t>RUFINA ISABEL</t>
-  </si>
-  <si>
-    <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
-    <t>LUIS BRANDON</t>
-  </si>
-  <si>
-    <t>MELANIE</t>
-  </si>
-  <si>
-    <t>GLORIA</t>
-  </si>
-  <si>
-    <t>DINORAH AZUL</t>
-  </si>
-  <si>
-    <t>MARIAM</t>
-  </si>
-  <si>
-    <t>MARIO</t>
-  </si>
-  <si>
     <t>LLUVIA RUBI</t>
   </si>
   <si>
     <t>TONALLI</t>
   </si>
   <si>
-    <t>MARIA PAULINA</t>
-  </si>
-  <si>
-    <t>WENDY</t>
-  </si>
-  <si>
     <t>LIZBETH</t>
   </si>
   <si>
-    <t>IVETTE NAOMI</t>
-  </si>
-  <si>
-    <t>KAY LEILANI</t>
-  </si>
-  <si>
-    <t>JEAN KARLLO</t>
-  </si>
-  <si>
-    <t>GEOVANI</t>
-  </si>
-  <si>
     <t>JULIO</t>
-  </si>
-  <si>
-    <t>KEVIN GAEL</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>JUAN MANUEL</t>
-  </si>
-  <si>
-    <t>STEPHANIE</t>
-  </si>
-  <si>
-    <t>CALEB ELI</t>
-  </si>
-  <si>
-    <t>GERARDO ALBERTO</t>
-  </si>
-  <si>
-    <t>GIOVANNI</t>
-  </si>
-  <si>
-    <t>FRIDA SOFIA</t>
   </si>
   <si>
     <t>DULCE REGINA</t>
@@ -556,6 +354,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -608,11 +409,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1072,10 +874,10 @@
         <v>10</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K4">
         <v>-1</v>
@@ -1117,7 +919,7 @@
         <v>10</v>
       </c>
       <c r="X4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y4">
         <v>9</v>
@@ -1161,10 +963,10 @@
         <v>5</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K5">
         <v>-1</v>
@@ -1203,7 +1005,7 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X5">
         <v>10</v>
@@ -1250,10 +1052,10 @@
         <v>8</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K6">
         <v>-1</v>
@@ -1339,10 +1141,10 @@
         <v>8</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
         <v>-1</v>
@@ -1428,10 +1230,10 @@
         <v>6</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K8">
         <v>-1</v>
@@ -1517,10 +1319,10 @@
         <v>6</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K9">
         <v>-1</v>
@@ -1606,10 +1408,10 @@
         <v>8</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K10">
         <v>-1</v>
@@ -1651,7 +1453,7 @@
         <v>7</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y10">
         <v>9</v>
@@ -1695,10 +1497,10 @@
         <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K11">
         <v>-1</v>
@@ -1737,7 +1539,7 @@
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X11">
         <v>9</v>
@@ -1784,10 +1586,10 @@
         <v>6</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K12">
         <v>-1</v>
@@ -1829,7 +1631,7 @@
         <v>5</v>
       </c>
       <c r="X12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y12">
         <v>6</v>
@@ -1873,10 +1675,10 @@
         <v>5</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K13">
         <v>-1</v>
@@ -1962,10 +1764,10 @@
         <v>8</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
         <v>-1</v>
@@ -2051,10 +1853,10 @@
         <v>8</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
         <v>-1</v>
@@ -2096,7 +1898,7 @@
         <v>7</v>
       </c>
       <c r="X15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y15">
         <v>8</v>
@@ -2140,10 +1942,10 @@
         <v>5</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
         <v>-1</v>
@@ -2229,10 +2031,10 @@
         <v>9</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K17">
         <v>-1</v>
@@ -2318,10 +2120,10 @@
         <v>5</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K18">
         <v>-1</v>
@@ -2363,7 +2165,7 @@
         <v>5</v>
       </c>
       <c r="X18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y18">
         <v>7</v>
@@ -2407,10 +2209,10 @@
         <v>5</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K19">
         <v>-1</v>
@@ -2496,10 +2298,10 @@
         <v>8</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K20">
         <v>-1</v>
@@ -2585,10 +2387,10 @@
         <v>7</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
         <v>-1</v>
@@ -2674,10 +2476,10 @@
         <v>6</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K22">
         <v>-1</v>
@@ -2763,10 +2565,10 @@
         <v>8</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K23">
         <v>-1</v>
@@ -2808,7 +2610,7 @@
         <v>5</v>
       </c>
       <c r="X23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y23">
         <v>7</v>
@@ -2852,10 +2654,10 @@
         <v>8</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K24">
         <v>-1</v>
@@ -2897,7 +2699,7 @@
         <v>5</v>
       </c>
       <c r="X24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y24">
         <v>7</v>
@@ -2941,10 +2743,10 @@
         <v>7</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K25">
         <v>-1</v>
@@ -3030,10 +2832,10 @@
         <v>9</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K26">
         <v>-1</v>
@@ -3072,7 +2874,7 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X26">
         <v>9</v>
@@ -3119,10 +2921,10 @@
         <v>9</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K27">
         <v>-1</v>
@@ -3208,10 +3010,10 @@
         <v>9</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K28">
         <v>-1</v>
@@ -3250,10 +3052,10 @@
         <v>-1</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y28">
         <v>8</v>
@@ -3297,10 +3099,10 @@
         <v>9</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K29">
         <v>-1</v>
@@ -3342,7 +3144,7 @@
         <v>8</v>
       </c>
       <c r="X29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y29">
         <v>8</v>
@@ -3386,10 +3188,10 @@
         <v>9</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K30">
         <v>-1</v>
@@ -3475,10 +3277,10 @@
         <v>9</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K31">
         <v>-1</v>
@@ -3517,7 +3319,7 @@
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X31">
         <v>9</v>
@@ -3564,10 +3366,10 @@
         <v>9</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K32">
         <v>-1</v>
@@ -3653,10 +3455,10 @@
         <v>8</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K33">
         <v>-1</v>
@@ -3698,7 +3500,7 @@
         <v>5</v>
       </c>
       <c r="X33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y33">
         <v>7</v>
@@ -3742,10 +3544,10 @@
         <v>8</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K34">
         <v>-1</v>
@@ -3831,10 +3633,10 @@
         <v>8</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K35">
         <v>-1</v>
@@ -3876,7 +3678,7 @@
         <v>7</v>
       </c>
       <c r="X35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y35">
         <v>8</v>
@@ -3920,10 +3722,10 @@
         <v>9</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K36">
         <v>-1</v>
@@ -3965,7 +3767,7 @@
         <v>8</v>
       </c>
       <c r="X36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y36">
         <v>8</v>
@@ -4009,10 +3811,10 @@
         <v>7</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K37">
         <v>-1</v>
@@ -4054,7 +3856,7 @@
         <v>5</v>
       </c>
       <c r="X37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y37">
         <v>6</v>
@@ -4098,10 +3900,10 @@
         <v>9</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K38">
         <v>-1</v>
@@ -4187,10 +3989,10 @@
         <v>8</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K39">
         <v>-1</v>
@@ -4276,10 +4078,10 @@
         <v>8</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K40">
         <v>-1</v>
@@ -4321,7 +4123,7 @@
         <v>5</v>
       </c>
       <c r="X40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y40">
         <v>7</v>
@@ -4365,10 +4167,10 @@
         <v>9</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K41">
         <v>-1</v>
@@ -4454,10 +4256,10 @@
         <v>6</v>
       </c>
       <c r="I42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K42">
         <v>-1</v>
@@ -4499,7 +4301,7 @@
         <v>5</v>
       </c>
       <c r="X42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y42">
         <v>7</v>
@@ -4665,10 +4467,10 @@
         <v>100</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K4">
         <v>0</v>
@@ -4733,10 +4535,10 @@
         <v>85</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -4801,10 +4603,10 @@
         <v>100</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K6">
         <v>0</v>
@@ -4869,10 +4671,10 @@
         <v>100</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -4937,10 +4739,10 @@
         <v>85</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -5005,10 +4807,10 @@
         <v>95</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -5073,10 +4875,10 @@
         <v>90</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -5141,10 +4943,10 @@
         <v>100</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K11">
         <v>0</v>
@@ -5209,10 +5011,10 @@
         <v>100</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -5277,10 +5079,10 @@
         <v>80</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -5345,10 +5147,10 @@
         <v>100</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -5413,10 +5215,10 @@
         <v>100</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -5481,10 +5283,10 @@
         <v>80</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="K16">
         <v>0</v>
@@ -5549,10 +5351,10 @@
         <v>100</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K17">
         <v>0</v>
@@ -5617,10 +5419,10 @@
         <v>95</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="K18">
         <v>0</v>
@@ -5685,10 +5487,10 @@
         <v>95</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K19">
         <v>0</v>
@@ -5753,10 +5555,10 @@
         <v>100</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="K20">
         <v>0</v>
@@ -5821,10 +5623,10 @@
         <v>90</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K21">
         <v>0</v>
@@ -5889,10 +5691,10 @@
         <v>90</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -5957,10 +5759,10 @@
         <v>100</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -6025,10 +5827,10 @@
         <v>95</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -6093,10 +5895,10 @@
         <v>95</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K25">
         <v>0</v>
@@ -6161,10 +5963,10 @@
         <v>100</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K26">
         <v>0</v>
@@ -6229,10 +6031,10 @@
         <v>100</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="K27">
         <v>0</v>
@@ -6297,10 +6099,10 @@
         <v>95</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K28">
         <v>0</v>
@@ -6365,10 +6167,10 @@
         <v>100</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K29">
         <v>0</v>
@@ -6433,10 +6235,10 @@
         <v>100</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K30">
         <v>0</v>
@@ -6501,10 +6303,10 @@
         <v>100</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K31">
         <v>0</v>
@@ -6569,10 +6371,10 @@
         <v>100</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K32">
         <v>0</v>
@@ -6637,10 +6439,10 @@
         <v>100</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K33">
         <v>0</v>
@@ -6705,10 +6507,10 @@
         <v>100</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K34">
         <v>0</v>
@@ -6773,10 +6575,10 @@
         <v>90</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="K35">
         <v>0</v>
@@ -6841,10 +6643,10 @@
         <v>95</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K36">
         <v>0</v>
@@ -6909,10 +6711,10 @@
         <v>90</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K37">
         <v>0</v>
@@ -6977,10 +6779,10 @@
         <v>100</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K38">
         <v>0</v>
@@ -7045,10 +6847,10 @@
         <v>100</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K39">
         <v>0</v>
@@ -7113,10 +6915,10 @@
         <v>100</v>
       </c>
       <c r="I40">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="J40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K40">
         <v>0</v>
@@ -7181,10 +6983,10 @@
         <v>100</v>
       </c>
       <c r="I41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J41">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="K41">
         <v>0</v>
@@ -7249,10 +7051,10 @@
         <v>90</v>
       </c>
       <c r="I42">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="J42">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="K42">
         <v>0</v>
@@ -7307,6 +7109,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="50.7109375" customWidth="1"/>
+    <col min="6" max="7" width="9.140625" style="2"/>
+    <col min="10" max="10" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -7357,19 +7161,19 @@
       <c r="E2">
         <v>17</v>
       </c>
-      <c r="F2">
-        <v>56.41</v>
-      </c>
-      <c r="G2">
-        <v>43.59</v>
+      <c r="F2" s="2">
+        <v>56.4</v>
+      </c>
+      <c r="G2" s="2">
+        <v>43.6</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7389,11 +7193,11 @@
       <c r="E3">
         <v>10</v>
       </c>
-      <c r="F3">
-        <v>74.36</v>
-      </c>
-      <c r="G3">
-        <v>25.64</v>
+      <c r="F3" s="2">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="G3" s="2">
+        <v>25.6</v>
       </c>
       <c r="H3">
         <v>6.5</v>
@@ -7401,13 +7205,13 @@
       <c r="I3">
         <v>0</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>66</v>
@@ -7416,30 +7220,30 @@
         <v>39</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E4">
-        <v>5</v>
-      </c>
-      <c r="F4">
-        <v>87.18000000000001</v>
-      </c>
-      <c r="G4">
-        <v>12.82</v>
+        <v>6</v>
+      </c>
+      <c r="F4" s="2">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="G4" s="2">
+        <v>15.4</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
@@ -7453,19 +7257,19 @@
       <c r="E5">
         <v>5</v>
       </c>
-      <c r="F5">
-        <v>87.18000000000001</v>
-      </c>
-      <c r="G5">
-        <v>12.82</v>
+      <c r="F5" s="2">
+        <v>87.2</v>
+      </c>
+      <c r="G5" s="2">
+        <v>12.8</v>
       </c>
       <c r="H5">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7485,11 +7289,11 @@
       <c r="E6">
         <v>3</v>
       </c>
-      <c r="F6">
-        <v>92.31</v>
-      </c>
-      <c r="G6">
-        <v>7.69</v>
+      <c r="F6" s="2">
+        <v>92.3</v>
+      </c>
+      <c r="G6" s="2">
+        <v>7.7</v>
       </c>
       <c r="H6">
         <v>7.7</v>
@@ -7497,7 +7301,7 @@
       <c r="I6">
         <v>0</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7517,11 +7321,11 @@
       <c r="E7">
         <v>2</v>
       </c>
-      <c r="F7">
-        <v>94.87</v>
-      </c>
-      <c r="G7">
-        <v>5.13</v>
+      <c r="F7" s="2">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="G7" s="2">
+        <v>5.1</v>
       </c>
       <c r="H7">
         <v>8.6</v>
@@ -7529,7 +7333,7 @@
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7549,11 +7353,11 @@
       <c r="E8">
         <v>2</v>
       </c>
-      <c r="F8">
-        <v>94.87</v>
-      </c>
-      <c r="G8">
-        <v>5.13</v>
+      <c r="F8" s="2">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="G8" s="2">
+        <v>5.1</v>
       </c>
       <c r="H8">
         <v>7.4</v>
@@ -7561,7 +7365,7 @@
       <c r="I8">
         <v>0</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7606,701 +7410,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E40"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="4" width="50.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>22330051920149</v>
-      </c>
-      <c r="B2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D2" t="s">
-        <v>138</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>22330051920150</v>
-      </c>
-      <c r="B3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C3" t="s">
-        <v>108</v>
-      </c>
-      <c r="D3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>22330051920151</v>
-      </c>
-      <c r="B4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D4" t="s">
-        <v>140</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
-        <v>22330051920292</v>
-      </c>
-      <c r="B5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D5" t="s">
-        <v>141</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
-        <v>22330051920383</v>
-      </c>
-      <c r="B6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D6" t="s">
-        <v>142</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
-        <v>22330051920153</v>
-      </c>
-      <c r="B7" t="s">
-        <v>80</v>
-      </c>
-      <c r="C7" t="s">
-        <v>112</v>
-      </c>
-      <c r="D7" t="s">
-        <v>143</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
-        <v>22330051920155</v>
-      </c>
-      <c r="B8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C8" t="s">
-        <v>113</v>
-      </c>
-      <c r="D8" t="s">
-        <v>144</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
-        <v>22330051920156</v>
-      </c>
-      <c r="B9" t="s">
-        <v>81</v>
-      </c>
-      <c r="C9" t="s">
-        <v>114</v>
-      </c>
-      <c r="D9" t="s">
-        <v>145</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10">
-        <v>22330051920154</v>
-      </c>
-      <c r="B10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C10" t="s">
-        <v>98</v>
-      </c>
-      <c r="D10" t="s">
-        <v>146</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11">
-        <v>22330051920381</v>
-      </c>
-      <c r="B11" t="s">
-        <v>83</v>
-      </c>
-      <c r="C11" t="s">
-        <v>115</v>
-      </c>
-      <c r="D11" t="s">
-        <v>147</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12">
-        <v>22330051920152</v>
-      </c>
-      <c r="B12" t="s">
-        <v>84</v>
-      </c>
-      <c r="C12" t="s">
-        <v>116</v>
-      </c>
-      <c r="D12" t="s">
-        <v>148</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13">
-        <v>22330051920384</v>
-      </c>
-      <c r="B13" t="s">
-        <v>85</v>
-      </c>
-      <c r="C13" t="s">
-        <v>117</v>
-      </c>
-      <c r="D13" t="s">
-        <v>149</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14">
-        <v>22330051920157</v>
-      </c>
-      <c r="B14" t="s">
-        <v>86</v>
-      </c>
-      <c r="C14" t="s">
-        <v>118</v>
-      </c>
-      <c r="D14" t="s">
-        <v>150</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15">
-        <v>22330051920161</v>
-      </c>
-      <c r="B15" t="s">
-        <v>87</v>
-      </c>
-      <c r="C15" t="s">
-        <v>119</v>
-      </c>
-      <c r="D15" t="s">
-        <v>151</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16">
-        <v>22330051920158</v>
-      </c>
-      <c r="B16" t="s">
-        <v>88</v>
-      </c>
-      <c r="C16" t="s">
-        <v>120</v>
-      </c>
-      <c r="D16" t="s">
-        <v>152</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>22330051920159</v>
-      </c>
-      <c r="B17" t="s">
-        <v>88</v>
-      </c>
-      <c r="C17" t="s">
-        <v>121</v>
-      </c>
-      <c r="D17" t="s">
-        <v>153</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>22330051920162</v>
-      </c>
-      <c r="B18" t="s">
-        <v>89</v>
-      </c>
-      <c r="C18" t="s">
-        <v>101</v>
-      </c>
-      <c r="D18" t="s">
-        <v>154</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>22330051920160</v>
-      </c>
-      <c r="B19" t="s">
-        <v>88</v>
-      </c>
-      <c r="C19" t="s">
-        <v>122</v>
-      </c>
-      <c r="D19" t="s">
-        <v>155</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>22330051920296</v>
-      </c>
-      <c r="B20" t="s">
-        <v>90</v>
-      </c>
-      <c r="C20" t="s">
-        <v>123</v>
-      </c>
-      <c r="D20" t="s">
-        <v>156</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21">
-        <v>22330051920163</v>
-      </c>
-      <c r="B21" t="s">
-        <v>91</v>
-      </c>
-      <c r="C21" t="s">
-        <v>92</v>
-      </c>
-      <c r="D21" t="s">
-        <v>157</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22">
-        <v>22330051920299</v>
-      </c>
-      <c r="B22" t="s">
-        <v>92</v>
-      </c>
-      <c r="C22" t="s">
-        <v>124</v>
-      </c>
-      <c r="D22" t="s">
-        <v>158</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23">
-        <v>22330051920165</v>
-      </c>
-      <c r="B23" t="s">
-        <v>92</v>
-      </c>
-      <c r="C23" t="s">
-        <v>125</v>
-      </c>
-      <c r="D23" t="s">
-        <v>159</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24">
-        <v>22330051920385</v>
-      </c>
-      <c r="B24" t="s">
-        <v>93</v>
-      </c>
-      <c r="C24" t="s">
-        <v>126</v>
-      </c>
-      <c r="D24" t="s">
-        <v>160</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25">
-        <v>22330051920164</v>
-      </c>
-      <c r="B25" t="s">
-        <v>94</v>
-      </c>
-      <c r="C25" t="s">
-        <v>127</v>
-      </c>
-      <c r="D25" t="s">
-        <v>161</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26">
-        <v>22330051920269</v>
-      </c>
-      <c r="B26" t="s">
-        <v>95</v>
-      </c>
-      <c r="C26" t="s">
-        <v>128</v>
-      </c>
-      <c r="D26" t="s">
-        <v>162</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27">
-        <v>22330051920167</v>
-      </c>
-      <c r="B27" t="s">
-        <v>95</v>
-      </c>
-      <c r="C27" t="s">
-        <v>129</v>
-      </c>
-      <c r="D27" t="s">
-        <v>163</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28">
-        <v>22330051920168</v>
-      </c>
-      <c r="B28" t="s">
-        <v>96</v>
-      </c>
-      <c r="C28" t="s">
-        <v>95</v>
-      </c>
-      <c r="D28" t="s">
-        <v>164</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29">
-        <v>22330051920169</v>
-      </c>
-      <c r="B29" t="s">
-        <v>97</v>
-      </c>
-      <c r="C29" t="s">
-        <v>130</v>
-      </c>
-      <c r="D29" t="s">
-        <v>165</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30">
-        <v>22330051920170</v>
-      </c>
-      <c r="B30" t="s">
-        <v>98</v>
-      </c>
-      <c r="C30" t="s">
-        <v>131</v>
-      </c>
-      <c r="D30" t="s">
-        <v>166</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31">
-        <v>22330051920275</v>
-      </c>
-      <c r="B31" t="s">
-        <v>99</v>
-      </c>
-      <c r="C31" t="s">
-        <v>85</v>
-      </c>
-      <c r="D31" t="s">
-        <v>167</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32">
-        <v>22330051920386</v>
-      </c>
-      <c r="B32" t="s">
-        <v>99</v>
-      </c>
-      <c r="C32" t="s">
-        <v>132</v>
-      </c>
-      <c r="D32" t="s">
-        <v>168</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33">
-        <v>22330051920172</v>
-      </c>
-      <c r="B33" t="s">
-        <v>100</v>
-      </c>
-      <c r="C33" t="s">
-        <v>133</v>
-      </c>
-      <c r="D33" t="s">
-        <v>169</v>
-      </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34">
-        <v>22330051920278</v>
-      </c>
-      <c r="B34" t="s">
-        <v>101</v>
-      </c>
-      <c r="C34" t="s">
-        <v>92</v>
-      </c>
-      <c r="D34" t="s">
-        <v>170</v>
-      </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35">
-        <v>22330051920171</v>
-      </c>
-      <c r="B35" t="s">
-        <v>101</v>
-      </c>
-      <c r="C35" t="s">
-        <v>134</v>
-      </c>
-      <c r="D35" t="s">
-        <v>171</v>
-      </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36">
-        <v>22330051920174</v>
-      </c>
-      <c r="B36" t="s">
-        <v>102</v>
-      </c>
-      <c r="C36" t="s">
-        <v>135</v>
-      </c>
-      <c r="D36" t="s">
-        <v>172</v>
-      </c>
-      <c r="E36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37">
-        <v>22330051920387</v>
-      </c>
-      <c r="B37" t="s">
-        <v>103</v>
-      </c>
-      <c r="C37" t="s">
-        <v>92</v>
-      </c>
-      <c r="D37" t="s">
-        <v>173</v>
-      </c>
-      <c r="E37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38">
-        <v>22330051920284</v>
-      </c>
-      <c r="B38" t="s">
-        <v>104</v>
-      </c>
-      <c r="C38" t="s">
-        <v>136</v>
-      </c>
-      <c r="D38" t="s">
-        <v>174</v>
-      </c>
-      <c r="E38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39">
-        <v>22330051920175</v>
-      </c>
-      <c r="B39" t="s">
-        <v>105</v>
-      </c>
-      <c r="C39" t="s">
-        <v>86</v>
-      </c>
-      <c r="D39" t="s">
-        <v>175</v>
-      </c>
-      <c r="E39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40">
-        <v>22330051920287</v>
-      </c>
-      <c r="B40" t="s">
-        <v>106</v>
-      </c>
-      <c r="C40" t="s">
-        <v>137</v>
-      </c>
-      <c r="D40" t="s">
-        <v>176</v>
-      </c>
-      <c r="E40">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -8335,13 +7445,13 @@
         <v>22330051920150</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>139</v>
+        <v>98</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -8358,19 +7468,19 @@
         <v>22330051920150</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>139</v>
+        <v>98</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -8378,16 +7488,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920386</v>
+        <v>22330051920383</v>
       </c>
       <c r="B4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D4" t="s">
         <v>99</v>
-      </c>
-      <c r="C4" t="s">
-        <v>132</v>
-      </c>
-      <c r="D4" t="s">
-        <v>168</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -8401,22 +7511,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920386</v>
+        <v>22330051920383</v>
       </c>
       <c r="B5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5" t="s">
         <v>99</v>
       </c>
-      <c r="C5" t="s">
-        <v>132</v>
-      </c>
-      <c r="D5" t="s">
-        <v>168</v>
-      </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -8424,16 +7534,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920172</v>
+        <v>22330051920386</v>
       </c>
       <c r="B6" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>133</v>
+        <v>89</v>
       </c>
       <c r="D6" t="s">
-        <v>169</v>
+        <v>100</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -8447,16 +7557,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920172</v>
+        <v>22330051920386</v>
       </c>
       <c r="B7" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>133</v>
+        <v>89</v>
       </c>
       <c r="D7" t="s">
-        <v>169</v>
+        <v>100</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -8470,16 +7580,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920175</v>
+        <v>22330051920172</v>
       </c>
       <c r="B8" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>175</v>
+        <v>101</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -8493,16 +7603,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920175</v>
+        <v>22330051920172</v>
       </c>
       <c r="B9" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>175</v>
+        <v>101</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -8516,16 +7626,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920383</v>
+        <v>22330051920175</v>
       </c>
       <c r="B10" t="s">
         <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="D10" t="s">
-        <v>142</v>
+        <v>102</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
@@ -8539,22 +7649,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920155</v>
+        <v>22330051920175</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="D11" t="s">
-        <v>144</v>
+        <v>102</v>
       </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -8562,16 +7672,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920381</v>
+        <v>22330051920155</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="D12" t="s">
-        <v>147</v>
+        <v>103</v>
       </c>
       <c r="E12" t="s">
         <v>5</v>
@@ -8585,16 +7695,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920163</v>
+        <v>22330051920381</v>
       </c>
       <c r="B13" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s">
-        <v>157</v>
+        <v>104</v>
       </c>
       <c r="E13" t="s">
         <v>5</v>
@@ -8608,16 +7718,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920299</v>
+        <v>22330051920163</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="C14" t="s">
-        <v>124</v>
+        <v>83</v>
       </c>
       <c r="D14" t="s">
-        <v>158</v>
+        <v>105</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
@@ -8631,16 +7741,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920164</v>
+        <v>22330051920299</v>
       </c>
       <c r="B15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15" t="s">
         <v>94</v>
       </c>
-      <c r="C15" t="s">
-        <v>127</v>
-      </c>
       <c r="D15" t="s">
-        <v>161</v>
+        <v>106</v>
       </c>
       <c r="E15" t="s">
         <v>5</v>
@@ -8654,16 +7764,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920170</v>
+        <v>22330051920164</v>
       </c>
       <c r="B16" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="C16" t="s">
-        <v>131</v>
+        <v>95</v>
       </c>
       <c r="D16" t="s">
-        <v>166</v>
+        <v>107</v>
       </c>
       <c r="E16" t="s">
         <v>5</v>
@@ -8677,16 +7787,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920287</v>
+        <v>22330051920170</v>
       </c>
       <c r="B17" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="C17" t="s">
-        <v>137</v>
+        <v>96</v>
       </c>
       <c r="D17" t="s">
-        <v>176</v>
+        <v>108</v>
       </c>
       <c r="E17" t="s">
         <v>5</v>
@@ -8695,6 +7805,29 @@
         <v>64</v>
       </c>
       <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>22330051920287</v>
+      </c>
+      <c r="B18" t="s">
+        <v>86</v>
+      </c>
+      <c r="C18" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18" t="s">
+        <v>109</v>
+      </c>
+      <c r="E18" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" t="s">
+        <v>64</v>
+      </c>
+      <c r="G18">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2APM - Estadisticos 20222.xlsx
+++ b/grupos/2APM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="107">
   <si>
     <t>Materia</t>
   </si>
@@ -212,21 +212,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
-    <t>González Sánchez Rene Aurelio</t>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
     <t>De Jesús Orduña Sofía del Pilar</t>
   </si>
   <si>
-    <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
     <t>Moreno Aroyo Anél</t>
   </si>
   <si>
@@ -245,109 +245,100 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>VELASCO</t>
+  </si>
+  <si>
     <t>BAEZ</t>
   </si>
   <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
     <t>CASTRO</t>
   </si>
   <si>
     <t>CALOCA</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
+    <t>COCOTLE</t>
   </si>
   <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>VELASCO</t>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>ANGUIANO</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>SAN JUAN</t>
   </si>
   <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>CHICO</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>ANGUIANO</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
     <t>MONTIEL</t>
   </si>
   <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>LEON</t>
+    <t>CUAQUEHUA</t>
   </si>
   <si>
     <t>SORIANO</t>
   </si>
   <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>SAN JUAN</t>
+    <t>LLUVIA RUBI</t>
+  </si>
+  <si>
+    <t>TONALLI</t>
+  </si>
+  <si>
+    <t>JULIO</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>FRIDA SOFIA</t>
+  </si>
+  <si>
+    <t>DULCE REGINA</t>
   </si>
   <si>
     <t>EDUARDO EMER</t>
   </si>
   <si>
-    <t>EDNA YOSSELIN</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>FRIDA SOFIA</t>
-  </si>
-  <si>
     <t>LESLY VIANEY</t>
   </si>
   <si>
     <t>ARLETH MARELY</t>
   </si>
   <si>
-    <t>LLUVIA RUBI</t>
-  </si>
-  <si>
-    <t>TONALLI</t>
+    <t>MELANIE</t>
   </si>
   <si>
     <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>JULIO</t>
-  </si>
-  <si>
-    <t>DULCE REGINA</t>
   </si>
 </sst>
 </file>
@@ -880,19 +871,19 @@
         <v>8</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
         <v>-1</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -922,7 +913,7 @@
         <v>9</v>
       </c>
       <c r="Y4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z4">
         <v>10</v>
@@ -969,19 +960,19 @@
         <v>10</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
         <v>-1</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -1011,19 +1002,19 @@
         <v>10</v>
       </c>
       <c r="Y5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z5">
         <v>5</v>
       </c>
       <c r="AA5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB5">
         <v>10</v>
       </c>
       <c r="AC5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1058,19 +1049,19 @@
         <v>8</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N6">
         <v>-1</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1100,10 +1091,10 @@
         <v>9</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA6">
         <v>9</v>
@@ -1147,19 +1138,19 @@
         <v>8</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N7">
         <v>-1</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1189,19 +1180,19 @@
         <v>8</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB7">
         <v>8</v>
       </c>
       <c r="AC7">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1236,19 +1227,19 @@
         <v>7</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N8">
         <v>-1</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1325,19 +1316,19 @@
         <v>5</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N9">
         <v>-1</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1373,13 +1364,13 @@
         <v>5</v>
       </c>
       <c r="AA9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB9">
         <v>5</v>
       </c>
       <c r="AC9">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1414,19 +1405,19 @@
         <v>6</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N10">
         <v>-1</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1468,7 +1459,7 @@
         <v>8</v>
       </c>
       <c r="AC10">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1503,19 +1494,19 @@
         <v>8</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
         <v>-1</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1545,10 +1536,10 @@
         <v>9</v>
       </c>
       <c r="Y11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA11">
         <v>10</v>
@@ -1592,19 +1583,19 @@
         <v>5</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12">
         <v>-1</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1634,19 +1625,19 @@
         <v>5</v>
       </c>
       <c r="Y12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB12">
         <v>8</v>
       </c>
       <c r="AC12">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1681,19 +1672,19 @@
         <v>5</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N13">
         <v>-1</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1723,7 +1714,7 @@
         <v>5</v>
       </c>
       <c r="Y13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z13">
         <v>5</v>
@@ -1770,19 +1761,19 @@
         <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N14">
         <v>-1</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1812,7 +1803,7 @@
         <v>8</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z14">
         <v>6</v>
@@ -1824,7 +1815,7 @@
         <v>7</v>
       </c>
       <c r="AC14">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1859,19 +1850,19 @@
         <v>7</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N15">
         <v>-1</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1901,13 +1892,13 @@
         <v>8</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z15">
         <v>6</v>
       </c>
       <c r="AA15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB15">
         <v>8</v>
@@ -1948,19 +1939,19 @@
         <v>6</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N16">
         <v>-1</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -1990,10 +1981,10 @@
         <v>5</v>
       </c>
       <c r="Y16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA16">
         <v>5</v>
@@ -2037,19 +2028,19 @@
         <v>7</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N17">
         <v>-1</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2079,10 +2070,10 @@
         <v>8</v>
       </c>
       <c r="Y17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA17">
         <v>8</v>
@@ -2091,7 +2082,7 @@
         <v>10</v>
       </c>
       <c r="AC17">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2126,19 +2117,19 @@
         <v>5</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N18">
         <v>-1</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2168,13 +2159,13 @@
         <v>6</v>
       </c>
       <c r="Y18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z18">
         <v>5</v>
       </c>
       <c r="AA18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB18">
         <v>7</v>
@@ -2215,19 +2206,19 @@
         <v>6</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N19">
         <v>-1</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2257,13 +2248,13 @@
         <v>6</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z19">
         <v>5</v>
       </c>
       <c r="AA19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB19">
         <v>7</v>
@@ -2304,19 +2295,19 @@
         <v>5</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N20">
         <v>-1</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2346,7 +2337,7 @@
         <v>5</v>
       </c>
       <c r="Y20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z20">
         <v>5</v>
@@ -2358,7 +2349,7 @@
         <v>8</v>
       </c>
       <c r="AC20">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2393,19 +2384,19 @@
         <v>9</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N21">
         <v>-1</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2435,13 +2426,13 @@
         <v>9</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z21">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB21">
         <v>10</v>
@@ -2482,19 +2473,19 @@
         <v>5</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N22">
         <v>-1</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2524,7 +2515,7 @@
         <v>5</v>
       </c>
       <c r="Y22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z22">
         <v>5</v>
@@ -2536,7 +2527,7 @@
         <v>5</v>
       </c>
       <c r="AC22">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2571,19 +2562,19 @@
         <v>6</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N23">
         <v>-1</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2613,19 +2604,19 @@
         <v>8</v>
       </c>
       <c r="Y23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB23">
         <v>9</v>
       </c>
       <c r="AC23">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2660,19 +2651,19 @@
         <v>6</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N24">
         <v>-1</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2702,19 +2693,19 @@
         <v>8</v>
       </c>
       <c r="Y24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z24">
         <v>6</v>
       </c>
       <c r="AA24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB24">
         <v>9</v>
       </c>
       <c r="AC24">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2749,19 +2740,19 @@
         <v>7</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N25">
         <v>-1</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2791,10 +2782,10 @@
         <v>8</v>
       </c>
       <c r="Y25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA25">
         <v>8</v>
@@ -2838,19 +2829,19 @@
         <v>8</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N26">
         <v>-1</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2880,7 +2871,7 @@
         <v>9</v>
       </c>
       <c r="Y26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z26">
         <v>8</v>
@@ -2927,19 +2918,19 @@
         <v>8</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N27">
         <v>-1</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -2969,10 +2960,10 @@
         <v>9</v>
       </c>
       <c r="Y27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA27">
         <v>10</v>
@@ -2981,7 +2972,7 @@
         <v>10</v>
       </c>
       <c r="AC27">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -3016,19 +3007,19 @@
         <v>6</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N28">
         <v>-1</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -3058,19 +3049,19 @@
         <v>8</v>
       </c>
       <c r="Y28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB28">
         <v>10</v>
       </c>
       <c r="AC28">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3105,19 +3096,19 @@
         <v>8</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N29">
         <v>-1</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -3147,13 +3138,13 @@
         <v>9</v>
       </c>
       <c r="Y29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z29">
         <v>7</v>
       </c>
       <c r="AA29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB29">
         <v>10</v>
@@ -3194,19 +3185,19 @@
         <v>8</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
         <v>-1</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3236,10 +3227,10 @@
         <v>9</v>
       </c>
       <c r="Y30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA30">
         <v>10</v>
@@ -3283,19 +3274,19 @@
         <v>8</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N31">
         <v>-1</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3325,7 +3316,7 @@
         <v>9</v>
       </c>
       <c r="Y31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z31">
         <v>8</v>
@@ -3372,19 +3363,19 @@
         <v>9</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N32">
         <v>-1</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -3414,13 +3405,13 @@
         <v>9</v>
       </c>
       <c r="Y32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z32">
         <v>10</v>
       </c>
       <c r="AA32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB32">
         <v>10</v>
@@ -3461,19 +3452,19 @@
         <v>6</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N33">
         <v>-1</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -3503,19 +3494,19 @@
         <v>7</v>
       </c>
       <c r="Y33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z33">
         <v>5</v>
       </c>
       <c r="AA33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB33">
         <v>7</v>
       </c>
       <c r="AC33">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:29">
@@ -3550,19 +3541,19 @@
         <v>6</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N34">
         <v>-1</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -3592,10 +3583,10 @@
         <v>7</v>
       </c>
       <c r="Y34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA34">
         <v>6</v>
@@ -3604,7 +3595,7 @@
         <v>8</v>
       </c>
       <c r="AC34">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:29">
@@ -3639,19 +3630,19 @@
         <v>7</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N35">
         <v>-1</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P35">
         <v>-1</v>
@@ -3681,10 +3672,10 @@
         <v>8</v>
       </c>
       <c r="Y35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA35">
         <v>8</v>
@@ -3693,7 +3684,7 @@
         <v>8</v>
       </c>
       <c r="AC35">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:29">
@@ -3728,19 +3719,19 @@
         <v>7</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N36">
         <v>-1</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P36">
         <v>-1</v>
@@ -3770,10 +3761,10 @@
         <v>8</v>
       </c>
       <c r="Y36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA36">
         <v>8</v>
@@ -3817,19 +3808,19 @@
         <v>5</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N37">
         <v>-1</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P37">
         <v>-1</v>
@@ -3859,19 +3850,19 @@
         <v>6</v>
       </c>
       <c r="Y37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z37">
         <v>5</v>
       </c>
       <c r="AA37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB37">
         <v>8</v>
       </c>
       <c r="AC37">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:29">
@@ -3906,19 +3897,19 @@
         <v>9</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N38">
         <v>-1</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P38">
         <v>-1</v>
@@ -3948,7 +3939,7 @@
         <v>9</v>
       </c>
       <c r="Y38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z38">
         <v>9</v>
@@ -3995,19 +3986,19 @@
         <v>8</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N39">
         <v>-1</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P39">
         <v>-1</v>
@@ -4037,7 +4028,7 @@
         <v>9</v>
       </c>
       <c r="Y39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z39">
         <v>7</v>
@@ -4049,7 +4040,7 @@
         <v>10</v>
       </c>
       <c r="AC39">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:29">
@@ -4084,19 +4075,19 @@
         <v>8</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N40">
         <v>-1</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P40">
         <v>-1</v>
@@ -4126,19 +4117,19 @@
         <v>8</v>
       </c>
       <c r="Y40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z40">
         <v>5</v>
       </c>
       <c r="AA40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB40">
         <v>6</v>
       </c>
       <c r="AC40">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:29">
@@ -4173,19 +4164,19 @@
         <v>7</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N41">
         <v>-1</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P41">
         <v>-1</v>
@@ -4215,10 +4206,10 @@
         <v>8</v>
       </c>
       <c r="Y41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA41">
         <v>9</v>
@@ -4227,7 +4218,7 @@
         <v>10</v>
       </c>
       <c r="AC41">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:29">
@@ -4262,19 +4253,19 @@
         <v>5</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N42">
         <v>-1</v>
       </c>
       <c r="O42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P42">
         <v>-1</v>
@@ -4307,7 +4298,7 @@
         <v>7</v>
       </c>
       <c r="Z42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA42">
         <v>6</v>
@@ -4473,19 +4464,19 @@
         <v>100</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N4">
         <v>0</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -4541,19 +4532,19 @@
         <v>100</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N5">
         <v>0</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -4609,19 +4600,19 @@
         <v>100</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N6">
         <v>0</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -4677,19 +4668,19 @@
         <v>100</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N7">
         <v>0</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -4745,19 +4736,19 @@
         <v>92</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N8">
         <v>0</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -4813,19 +4804,19 @@
         <v>80</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="N9">
         <v>0</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -4881,19 +4872,19 @@
         <v>88</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N10">
         <v>0</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -4949,19 +4940,19 @@
         <v>100</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P11">
         <v>0</v>
@@ -5017,19 +5008,19 @@
         <v>92</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -5085,19 +5076,19 @@
         <v>96</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N13">
         <v>0</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -5153,19 +5144,19 @@
         <v>100</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N14">
         <v>0</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -5221,19 +5212,19 @@
         <v>100</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N15">
         <v>0</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -5289,19 +5280,19 @@
         <v>92</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N16">
         <v>0</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="P16">
         <v>0</v>
@@ -5357,19 +5348,19 @@
         <v>100</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N17">
         <v>0</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -5425,19 +5416,19 @@
         <v>92</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="N18">
         <v>0</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -5493,19 +5484,19 @@
         <v>100</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="N19">
         <v>0</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -5561,19 +5552,19 @@
         <v>96</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N20">
         <v>0</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -5629,19 +5620,19 @@
         <v>100</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="N21">
         <v>0</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="P21">
         <v>0</v>
@@ -5697,19 +5688,19 @@
         <v>92</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="N22">
         <v>0</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="P22">
         <v>0</v>
@@ -5765,19 +5756,19 @@
         <v>100</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N23">
         <v>0</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="P23">
         <v>0</v>
@@ -5833,19 +5824,19 @@
         <v>100</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N24">
         <v>0</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="P24">
         <v>0</v>
@@ -5901,19 +5892,19 @@
         <v>100</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N25">
         <v>0</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="P25">
         <v>0</v>
@@ -5969,19 +5960,19 @@
         <v>100</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N26">
         <v>0</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P26">
         <v>0</v>
@@ -6037,19 +6028,19 @@
         <v>96</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N27">
         <v>0</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -6105,19 +6096,19 @@
         <v>100</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N28">
         <v>0</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -6173,19 +6164,19 @@
         <v>100</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="N29">
         <v>0</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="P29">
         <v>0</v>
@@ -6241,19 +6232,19 @@
         <v>100</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N30">
         <v>0</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P30">
         <v>0</v>
@@ -6309,19 +6300,19 @@
         <v>100</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N31">
         <v>0</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="P31">
         <v>0</v>
@@ -6377,19 +6368,19 @@
         <v>100</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N32">
         <v>0</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P32">
         <v>0</v>
@@ -6445,19 +6436,19 @@
         <v>100</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="N33">
         <v>0</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="P33">
         <v>0</v>
@@ -6513,19 +6504,19 @@
         <v>100</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N34">
         <v>0</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="P34">
         <v>0</v>
@@ -6581,19 +6572,19 @@
         <v>88</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M35">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N35">
         <v>0</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="P35">
         <v>0</v>
@@ -6649,19 +6640,19 @@
         <v>100</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N36">
         <v>0</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P36">
         <v>0</v>
@@ -6717,19 +6708,19 @@
         <v>100</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M37">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="N37">
         <v>0</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="P37">
         <v>0</v>
@@ -6785,19 +6776,19 @@
         <v>100</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N38">
         <v>0</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P38">
         <v>0</v>
@@ -6853,19 +6844,19 @@
         <v>100</v>
       </c>
       <c r="K39">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N39">
         <v>0</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P39">
         <v>0</v>
@@ -6921,19 +6912,19 @@
         <v>100</v>
       </c>
       <c r="K40">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M40">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="N40">
         <v>0</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P40">
         <v>0</v>
@@ -6989,19 +6980,19 @@
         <v>92</v>
       </c>
       <c r="K41">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N41">
         <v>0</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P41">
         <v>0</v>
@@ -7057,19 +7048,19 @@
         <v>96</v>
       </c>
       <c r="K42">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N42">
         <v>0</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P42">
         <v>0</v>
@@ -7147,7 +7138,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
@@ -7179,7 +7170,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>65</v>
@@ -7188,16 +7179,16 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F3" s="2">
-        <v>74.40000000000001</v>
+        <v>56.4</v>
       </c>
       <c r="G3" s="2">
-        <v>25.6</v>
+        <v>43.6</v>
       </c>
       <c r="H3">
         <v>6.5</v>
@@ -7211,7 +7202,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>66</v>
@@ -7220,19 +7211,19 @@
         <v>39</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2">
-        <v>84.59999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G4" s="2">
-        <v>15.4</v>
+        <v>17.9</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7243,7 +7234,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
@@ -7252,19 +7243,19 @@
         <v>39</v>
       </c>
       <c r="D5">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5" s="2">
-        <v>87.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G5" s="2">
-        <v>12.8</v>
+        <v>15.4</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7275,7 +7266,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>68</v>
@@ -7284,19 +7275,19 @@
         <v>39</v>
       </c>
       <c r="D6">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F6" s="2">
-        <v>92.3</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G6" s="2">
-        <v>7.7</v>
+        <v>15.4</v>
       </c>
       <c r="H6">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7348,19 +7339,19 @@
         <v>39</v>
       </c>
       <c r="D8">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2">
-        <v>94.90000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="G8" s="2">
-        <v>5.1</v>
+        <v>2.6</v>
       </c>
       <c r="H8">
-        <v>7.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7442,19 +7433,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920150</v>
+        <v>22330051920163</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
         <v>65</v>
@@ -7465,22 +7456,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920150</v>
+        <v>22330051920163</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -7488,22 +7479,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920383</v>
+        <v>22330051920299</v>
       </c>
       <c r="B4" t="s">
         <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7511,22 +7502,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920383</v>
+        <v>22330051920299</v>
       </c>
       <c r="B5" t="s">
         <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7534,22 +7525,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920386</v>
+        <v>22330051920170</v>
       </c>
       <c r="B6" t="s">
         <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7557,22 +7548,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920386</v>
+        <v>22330051920170</v>
       </c>
       <c r="B7" t="s">
         <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7586,16 +7577,16 @@
         <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7609,16 +7600,16 @@
         <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D9" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -7632,16 +7623,16 @@
         <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D10" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -7655,16 +7646,16 @@
         <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D11" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -7672,22 +7663,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920155</v>
+        <v>22330051920287</v>
       </c>
       <c r="B12" t="s">
         <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D12" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E12" t="s">
         <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -7695,19 +7686,19 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920381</v>
+        <v>22330051920287</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C13" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D13" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
         <v>64</v>
@@ -7718,19 +7709,19 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920163</v>
+        <v>22330051920150</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D14" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
         <v>64</v>
@@ -7741,22 +7732,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920299</v>
+        <v>22330051920155</v>
       </c>
       <c r="B15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C15" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D15" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E15" t="s">
         <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -7764,22 +7755,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920164</v>
+        <v>22330051920381</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D16" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E16" t="s">
         <v>5</v>
       </c>
       <c r="F16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -7787,19 +7778,19 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920170</v>
+        <v>22330051920158</v>
       </c>
       <c r="B17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D17" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E17" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
         <v>64</v>
@@ -7810,22 +7801,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920287</v>
+        <v>22330051920164</v>
       </c>
       <c r="B18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C18" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D18" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E18" t="s">
         <v>5</v>
       </c>
       <c r="F18" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G18">
         <v>5</v>

--- a/grupos/2APM - Estadisticos 20222.xlsx
+++ b/grupos/2APM - Estadisticos 20222.xlsx
@@ -880,7 +880,7 @@
         <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
         <v>7</v>
@@ -1058,7 +1058,7 @@
         <v>9</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
         <v>7</v>
@@ -1147,7 +1147,7 @@
         <v>8</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O7">
         <v>9</v>
@@ -1236,7 +1236,7 @@
         <v>8</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
         <v>6</v>
@@ -1325,7 +1325,7 @@
         <v>5</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O9">
         <v>5</v>
@@ -1414,7 +1414,7 @@
         <v>7</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O10">
         <v>6</v>
@@ -1456,7 +1456,7 @@
         <v>8</v>
       </c>
       <c r="AB10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC10">
         <v>7</v>
@@ -1503,7 +1503,7 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
         <v>9</v>
@@ -1592,7 +1592,7 @@
         <v>5</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O12">
         <v>5</v>
@@ -1634,7 +1634,7 @@
         <v>5</v>
       </c>
       <c r="AB12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC12">
         <v>5</v>
@@ -1681,7 +1681,7 @@
         <v>6</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O13">
         <v>5</v>
@@ -1723,7 +1723,7 @@
         <v>6</v>
       </c>
       <c r="AB13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC13">
         <v>5</v>
@@ -1770,7 +1770,7 @@
         <v>6</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
         <v>6</v>
@@ -1812,7 +1812,7 @@
         <v>7</v>
       </c>
       <c r="AB14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC14">
         <v>7</v>
@@ -1859,7 +1859,7 @@
         <v>9</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
         <v>8</v>
@@ -1901,7 +1901,7 @@
         <v>8</v>
       </c>
       <c r="AB15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC15">
         <v>8</v>
@@ -1948,7 +1948,7 @@
         <v>6</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O16">
         <v>5</v>
@@ -1990,7 +1990,7 @@
         <v>5</v>
       </c>
       <c r="AB16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC16">
         <v>5</v>
@@ -2037,7 +2037,7 @@
         <v>7</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O17">
         <v>7</v>
@@ -2079,7 +2079,7 @@
         <v>8</v>
       </c>
       <c r="AB17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC17">
         <v>8</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O18">
         <v>5</v>
@@ -2215,7 +2215,7 @@
         <v>5</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O19">
         <v>5</v>
@@ -2257,7 +2257,7 @@
         <v>6</v>
       </c>
       <c r="AB19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC19">
         <v>5</v>
@@ -2304,7 +2304,7 @@
         <v>5</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O20">
         <v>5</v>
@@ -2346,7 +2346,7 @@
         <v>5</v>
       </c>
       <c r="AB20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC20">
         <v>7</v>
@@ -2393,7 +2393,7 @@
         <v>7</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O21">
         <v>6</v>
@@ -2435,7 +2435,7 @@
         <v>8</v>
       </c>
       <c r="AB21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC21">
         <v>7</v>
@@ -2482,7 +2482,7 @@
         <v>5</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O22">
         <v>5</v>
@@ -2571,7 +2571,7 @@
         <v>6</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
         <v>6</v>
@@ -2613,7 +2613,7 @@
         <v>7</v>
       </c>
       <c r="AB23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC23">
         <v>7</v>
@@ -2660,7 +2660,7 @@
         <v>9</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O24">
         <v>6</v>
@@ -2702,7 +2702,7 @@
         <v>8</v>
       </c>
       <c r="AB24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC24">
         <v>7</v>
@@ -2749,7 +2749,7 @@
         <v>7</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O25">
         <v>6</v>
@@ -2791,7 +2791,7 @@
         <v>8</v>
       </c>
       <c r="AB25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC25">
         <v>7</v>
@@ -2838,7 +2838,7 @@
         <v>9</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
         <v>8</v>
@@ -2927,7 +2927,7 @@
         <v>9</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
         <v>6</v>
@@ -3016,7 +3016,7 @@
         <v>9</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
         <v>6</v>
@@ -3105,7 +3105,7 @@
         <v>6</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O29">
         <v>8</v>
@@ -3194,7 +3194,7 @@
         <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
         <v>9</v>
@@ -3283,7 +3283,7 @@
         <v>10</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
         <v>8</v>
@@ -3325,7 +3325,7 @@
         <v>10</v>
       </c>
       <c r="AB31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC31">
         <v>9</v>
@@ -3372,7 +3372,7 @@
         <v>10</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
         <v>9</v>
@@ -3461,7 +3461,7 @@
         <v>5</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O33">
         <v>5</v>
@@ -3550,7 +3550,7 @@
         <v>6</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O34">
         <v>6</v>
@@ -3592,7 +3592,7 @@
         <v>6</v>
       </c>
       <c r="AB34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC34">
         <v>7</v>
@@ -3639,7 +3639,7 @@
         <v>8</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O35">
         <v>6</v>
@@ -3728,7 +3728,7 @@
         <v>8</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O36">
         <v>8</v>
@@ -3817,7 +3817,7 @@
         <v>5</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O37">
         <v>5</v>
@@ -3859,7 +3859,7 @@
         <v>6</v>
       </c>
       <c r="AB37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC37">
         <v>6</v>
@@ -3906,7 +3906,7 @@
         <v>10</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O38">
         <v>9</v>
@@ -3995,7 +3995,7 @@
         <v>10</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O39">
         <v>6</v>
@@ -4084,7 +4084,7 @@
         <v>8</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O40">
         <v>6</v>
@@ -4126,7 +4126,7 @@
         <v>7</v>
       </c>
       <c r="AB40">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC40">
         <v>7</v>
@@ -4173,7 +4173,7 @@
         <v>8</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O41">
         <v>7</v>
@@ -4215,7 +4215,7 @@
         <v>9</v>
       </c>
       <c r="AB41">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC41">
         <v>8</v>
@@ -4262,7 +4262,7 @@
         <v>6</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O42">
         <v>6</v>
@@ -4473,7 +4473,7 @@
         <v>100</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="O4">
         <v>100</v>
@@ -4541,7 +4541,7 @@
         <v>80</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O5">
         <v>80</v>
@@ -4609,7 +4609,7 @@
         <v>100</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="O6">
         <v>100</v>
@@ -4677,7 +4677,7 @@
         <v>100</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="O7">
         <v>100</v>
@@ -4745,7 +4745,7 @@
         <v>100</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="O8">
         <v>85</v>
@@ -4813,7 +4813,7 @@
         <v>73.3</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="O9">
         <v>60</v>
@@ -4881,7 +4881,7 @@
         <v>100</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="O10">
         <v>65</v>
@@ -4949,7 +4949,7 @@
         <v>100</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O11">
         <v>100</v>
@@ -5017,7 +5017,7 @@
         <v>73.3</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="O12">
         <v>70</v>
@@ -5085,7 +5085,7 @@
         <v>80</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O13">
         <v>70</v>
@@ -5153,7 +5153,7 @@
         <v>100</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O14">
         <v>95</v>
@@ -5221,7 +5221,7 @@
         <v>100</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="O15">
         <v>100</v>
@@ -5289,7 +5289,7 @@
         <v>80</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="O16">
         <v>90</v>
@@ -5357,7 +5357,7 @@
         <v>100</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O17">
         <v>100</v>
@@ -5425,7 +5425,7 @@
         <v>66.7</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O18">
         <v>70</v>
@@ -5493,7 +5493,7 @@
         <v>66.7</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="O19">
         <v>80</v>
@@ -5561,7 +5561,7 @@
         <v>100</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="O20">
         <v>85</v>
@@ -5629,7 +5629,7 @@
         <v>73.3</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="O21">
         <v>95</v>
@@ -5697,7 +5697,7 @@
         <v>66.7</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="O22">
         <v>90</v>
@@ -5765,7 +5765,7 @@
         <v>100</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="O23">
         <v>95</v>
@@ -5833,7 +5833,7 @@
         <v>100</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="O24">
         <v>95</v>
@@ -5901,7 +5901,7 @@
         <v>80</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O25">
         <v>80</v>
@@ -5969,7 +5969,7 @@
         <v>100</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="O26">
         <v>100</v>
@@ -6037,7 +6037,7 @@
         <v>100</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="O27">
         <v>90</v>
@@ -6105,7 +6105,7 @@
         <v>100</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="O28">
         <v>100</v>
@@ -6173,7 +6173,7 @@
         <v>86.7</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="O29">
         <v>95</v>
@@ -6241,7 +6241,7 @@
         <v>100</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="O30">
         <v>100</v>
@@ -6309,7 +6309,7 @@
         <v>100</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="O31">
         <v>95</v>
@@ -6377,7 +6377,7 @@
         <v>100</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O32">
         <v>100</v>
@@ -6445,7 +6445,7 @@
         <v>66.7</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O33">
         <v>95</v>
@@ -6513,7 +6513,7 @@
         <v>80</v>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O34">
         <v>95</v>
@@ -6581,7 +6581,7 @@
         <v>80</v>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="O35">
         <v>85</v>
@@ -6649,7 +6649,7 @@
         <v>100</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="O36">
         <v>100</v>
@@ -6717,7 +6717,7 @@
         <v>73.3</v>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="O37">
         <v>95</v>
@@ -6785,7 +6785,7 @@
         <v>100</v>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="O38">
         <v>100</v>
@@ -6853,7 +6853,7 @@
         <v>100</v>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="O39">
         <v>100</v>
@@ -6921,7 +6921,7 @@
         <v>86.7</v>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="O40">
         <v>100</v>
@@ -6989,7 +6989,7 @@
         <v>100</v>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="O41">
         <v>100</v>
@@ -7057,7 +7057,7 @@
         <v>100</v>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="O42">
         <v>100</v>
@@ -7319,7 +7319,7 @@
         <v>5.1</v>
       </c>
       <c r="H7">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/2APM - Estadisticos 20222.xlsx
+++ b/grupos/2APM - Estadisticos 20222.xlsx
@@ -4443,7 +4443,7 @@
         <v>100</v>
       </c>
       <c r="D4">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E4">
         <v>100</v>
@@ -4464,7 +4464,7 @@
         <v>100</v>
       </c>
       <c r="K4">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L4">
         <v>100</v>
@@ -4473,31 +4473,31 @@
         <v>100</v>
       </c>
       <c r="N4">
-        <v>110</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O4">
         <v>100</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -4511,7 +4511,7 @@
         <v>100</v>
       </c>
       <c r="D5">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E5">
         <v>100</v>
@@ -4526,46 +4526,46 @@
         <v>85</v>
       </c>
       <c r="I5">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="J5">
         <v>100</v>
       </c>
       <c r="K5">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L5">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M5">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="N5">
-        <v>100</v>
+        <v>85.7</v>
       </c>
       <c r="O5">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -4579,7 +4579,7 @@
         <v>100</v>
       </c>
       <c r="D6">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E6">
         <v>100</v>
@@ -4594,13 +4594,13 @@
         <v>100</v>
       </c>
       <c r="I6">
-        <v>97.09999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="J6">
         <v>100</v>
       </c>
       <c r="K6">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L6">
         <v>100</v>
@@ -4609,31 +4609,31 @@
         <v>100</v>
       </c>
       <c r="N6">
-        <v>105</v>
+        <v>95.2</v>
       </c>
       <c r="O6">
         <v>100</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>95.7</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -4647,7 +4647,7 @@
         <v>96</v>
       </c>
       <c r="D7">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E7">
         <v>100</v>
@@ -4665,10 +4665,10 @@
         <v>100</v>
       </c>
       <c r="J7">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K7">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L7">
         <v>100</v>
@@ -4677,31 +4677,31 @@
         <v>100</v>
       </c>
       <c r="N7">
-        <v>110</v>
+        <v>95.2</v>
       </c>
       <c r="O7">
         <v>100</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -4715,7 +4715,7 @@
         <v>96</v>
       </c>
       <c r="D8">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E8">
         <v>100</v>
@@ -4733,10 +4733,10 @@
         <v>94.3</v>
       </c>
       <c r="J8">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K8">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L8">
         <v>100</v>
@@ -4745,31 +4745,31 @@
         <v>100</v>
       </c>
       <c r="N8">
-        <v>105</v>
+        <v>90.5</v>
       </c>
       <c r="O8">
         <v>85</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>90.5</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -4783,7 +4783,7 @@
         <v>88</v>
       </c>
       <c r="D9">
-        <v>32</v>
+        <v>33.3</v>
       </c>
       <c r="E9">
         <v>85</v>
@@ -4798,46 +4798,46 @@
         <v>95</v>
       </c>
       <c r="I9">
-        <v>80</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="J9">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="K9">
-        <v>20</v>
+        <v>27.1</v>
       </c>
       <c r="L9">
-        <v>60</v>
+        <v>72.5</v>
       </c>
       <c r="M9">
-        <v>73.3</v>
+        <v>86.7</v>
       </c>
       <c r="N9">
-        <v>80</v>
+        <v>64.3</v>
       </c>
       <c r="O9">
-        <v>60</v>
+        <v>77.5</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>27.1</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>72.5</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>64.3</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -4851,7 +4851,7 @@
         <v>100</v>
       </c>
       <c r="D10">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E10">
         <v>100</v>
@@ -4866,46 +4866,46 @@
         <v>90</v>
       </c>
       <c r="I10">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="J10">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="K10">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L10">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="M10">
         <v>100</v>
       </c>
       <c r="N10">
-        <v>85</v>
+        <v>85.7</v>
       </c>
       <c r="O10">
-        <v>65</v>
+        <v>77.5</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -4919,7 +4919,7 @@
         <v>100</v>
       </c>
       <c r="D11">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E11">
         <v>100</v>
@@ -4934,13 +4934,13 @@
         <v>100</v>
       </c>
       <c r="I11">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="J11">
         <v>100</v>
       </c>
       <c r="K11">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L11">
         <v>100</v>
@@ -4949,31 +4949,31 @@
         <v>100</v>
       </c>
       <c r="N11">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="O11">
         <v>100</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -4987,7 +4987,7 @@
         <v>96</v>
       </c>
       <c r="D12">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E12">
         <v>100</v>
@@ -5005,43 +5005,43 @@
         <v>94.3</v>
       </c>
       <c r="J12">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K12">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L12">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="M12">
-        <v>73.3</v>
+        <v>86.7</v>
       </c>
       <c r="N12">
-        <v>95</v>
+        <v>85.7</v>
       </c>
       <c r="O12">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -5055,7 +5055,7 @@
         <v>88</v>
       </c>
       <c r="D13">
-        <v>88</v>
+        <v>91.7</v>
       </c>
       <c r="E13">
         <v>85</v>
@@ -5073,43 +5073,43 @@
         <v>85.7</v>
       </c>
       <c r="J13">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="K13">
-        <v>96</v>
+        <v>95.8</v>
       </c>
       <c r="L13">
+        <v>80</v>
+      </c>
+      <c r="M13">
+        <v>83.3</v>
+      </c>
+      <c r="N13">
+        <v>81</v>
+      </c>
+      <c r="O13">
         <v>75</v>
       </c>
-      <c r="M13">
+      <c r="P13">
+        <v>85.7</v>
+      </c>
+      <c r="Q13">
+        <v>92</v>
+      </c>
+      <c r="R13">
+        <v>95.8</v>
+      </c>
+      <c r="S13">
         <v>80</v>
       </c>
-      <c r="N13">
-        <v>100</v>
-      </c>
-      <c r="O13">
-        <v>70</v>
-      </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <v>0</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
       <c r="T13">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -5123,7 +5123,7 @@
         <v>100</v>
       </c>
       <c r="D14">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E14">
         <v>100</v>
@@ -5138,46 +5138,46 @@
         <v>100</v>
       </c>
       <c r="I14">
-        <v>97.09999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="J14">
         <v>100</v>
       </c>
       <c r="K14">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L14">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="M14">
         <v>100</v>
       </c>
       <c r="N14">
-        <v>100</v>
+        <v>90.5</v>
       </c>
       <c r="O14">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>95.7</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>90.5</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -5191,7 +5191,7 @@
         <v>100</v>
       </c>
       <c r="D15">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E15">
         <v>100</v>
@@ -5206,13 +5206,13 @@
         <v>100</v>
       </c>
       <c r="I15">
-        <v>97.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="J15">
         <v>100</v>
       </c>
       <c r="K15">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L15">
         <v>100</v>
@@ -5221,31 +5221,31 @@
         <v>100</v>
       </c>
       <c r="N15">
-        <v>105</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O15">
         <v>100</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -5259,7 +5259,7 @@
         <v>96</v>
       </c>
       <c r="D16">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E16">
         <v>100</v>
@@ -5274,46 +5274,46 @@
         <v>80</v>
       </c>
       <c r="I16">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="J16">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K16">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L16">
         <v>100</v>
       </c>
       <c r="M16">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="N16">
-        <v>110</v>
+        <v>90.5</v>
       </c>
       <c r="O16">
+        <v>85</v>
+      </c>
+      <c r="P16">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="Q16">
+        <v>94</v>
+      </c>
+      <c r="R16">
+        <v>100</v>
+      </c>
+      <c r="S16">
+        <v>100</v>
+      </c>
+      <c r="T16">
         <v>90</v>
       </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="Q16">
-        <v>0</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
       <c r="U16">
-        <v>0</v>
+        <v>90.5</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -5327,7 +5327,7 @@
         <v>100</v>
       </c>
       <c r="D17">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E17">
         <v>100</v>
@@ -5348,40 +5348,40 @@
         <v>100</v>
       </c>
       <c r="K17">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L17">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M17">
         <v>100</v>
       </c>
       <c r="N17">
-        <v>100</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="O17">
         <v>100</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -5395,7 +5395,7 @@
         <v>100</v>
       </c>
       <c r="D18">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E18">
         <v>100</v>
@@ -5413,43 +5413,43 @@
         <v>94.3</v>
       </c>
       <c r="J18">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K18">
+        <v>100</v>
+      </c>
+      <c r="L18">
+        <v>87.5</v>
+      </c>
+      <c r="M18">
+        <v>83.3</v>
+      </c>
+      <c r="N18">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="O18">
+        <v>82.5</v>
+      </c>
+      <c r="P18">
+        <v>94.3</v>
+      </c>
+      <c r="Q18">
         <v>96</v>
       </c>
-      <c r="L18">
-        <v>75</v>
-      </c>
-      <c r="M18">
-        <v>66.7</v>
-      </c>
-      <c r="N18">
-        <v>100</v>
-      </c>
-      <c r="O18">
-        <v>70</v>
-      </c>
-      <c r="P18">
-        <v>0</v>
-      </c>
-      <c r="Q18">
-        <v>0</v>
-      </c>
       <c r="R18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -5463,7 +5463,7 @@
         <v>96</v>
       </c>
       <c r="D19">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E19">
         <v>100</v>
@@ -5481,43 +5481,43 @@
         <v>94.3</v>
       </c>
       <c r="J19">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K19">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L19">
         <v>100</v>
       </c>
       <c r="M19">
-        <v>66.7</v>
+        <v>83.3</v>
       </c>
       <c r="N19">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="O19">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -5531,7 +5531,7 @@
         <v>100</v>
       </c>
       <c r="D20">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E20">
         <v>100</v>
@@ -5549,43 +5549,43 @@
         <v>97.09999999999999</v>
       </c>
       <c r="J20">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K20">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L20">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="M20">
         <v>100</v>
       </c>
       <c r="N20">
-        <v>105</v>
+        <v>95.2</v>
       </c>
       <c r="O20">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -5599,7 +5599,7 @@
         <v>100</v>
       </c>
       <c r="D21">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E21">
         <v>100</v>
@@ -5614,46 +5614,46 @@
         <v>90</v>
       </c>
       <c r="I21">
-        <v>97.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="J21">
         <v>100</v>
       </c>
       <c r="K21">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L21">
         <v>100</v>
       </c>
       <c r="M21">
-        <v>73.3</v>
+        <v>86.7</v>
       </c>
       <c r="N21">
-        <v>110</v>
+        <v>95.2</v>
       </c>
       <c r="O21">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -5667,7 +5667,7 @@
         <v>96</v>
       </c>
       <c r="D22">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E22">
         <v>100</v>
@@ -5685,43 +5685,43 @@
         <v>94.3</v>
       </c>
       <c r="J22">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K22">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L22">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="M22">
-        <v>66.7</v>
+        <v>83.3</v>
       </c>
       <c r="N22">
-        <v>90</v>
+        <v>85.7</v>
       </c>
       <c r="O22">
         <v>90</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -5735,7 +5735,7 @@
         <v>96</v>
       </c>
       <c r="D23">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E23">
         <v>100</v>
@@ -5753,10 +5753,10 @@
         <v>94.3</v>
       </c>
       <c r="J23">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K23">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L23">
         <v>100</v>
@@ -5765,31 +5765,31 @@
         <v>100</v>
       </c>
       <c r="N23">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="O23">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -5803,7 +5803,7 @@
         <v>100</v>
       </c>
       <c r="D24">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E24">
         <v>100</v>
@@ -5824,7 +5824,7 @@
         <v>100</v>
       </c>
       <c r="K24">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L24">
         <v>100</v>
@@ -5833,31 +5833,31 @@
         <v>100</v>
       </c>
       <c r="N24">
-        <v>105</v>
+        <v>95.2</v>
       </c>
       <c r="O24">
         <v>95</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -5871,7 +5871,7 @@
         <v>100</v>
       </c>
       <c r="D25">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E25">
         <v>100</v>
@@ -5886,46 +5886,46 @@
         <v>95</v>
       </c>
       <c r="I25">
-        <v>97.09999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="J25">
         <v>100</v>
       </c>
       <c r="K25">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L25">
         <v>100</v>
       </c>
       <c r="M25">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="N25">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="O25">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>95.7</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -5939,7 +5939,7 @@
         <v>100</v>
       </c>
       <c r="D26">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E26">
         <v>100</v>
@@ -5960,7 +5960,7 @@
         <v>100</v>
       </c>
       <c r="K26">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L26">
         <v>100</v>
@@ -5969,31 +5969,31 @@
         <v>100</v>
       </c>
       <c r="N26">
-        <v>105</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="O26">
         <v>100</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -6007,7 +6007,7 @@
         <v>100</v>
       </c>
       <c r="D27">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E27">
         <v>100</v>
@@ -6022,13 +6022,13 @@
         <v>100</v>
       </c>
       <c r="I27">
-        <v>97.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="J27">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K27">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L27">
         <v>100</v>
@@ -6037,31 +6037,31 @@
         <v>100</v>
       </c>
       <c r="N27">
-        <v>105</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O27">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>95</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -6075,7 +6075,7 @@
         <v>100</v>
       </c>
       <c r="D28">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E28">
         <v>100</v>
@@ -6090,13 +6090,13 @@
         <v>95</v>
       </c>
       <c r="I28">
-        <v>97.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="J28">
         <v>100</v>
       </c>
       <c r="K28">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L28">
         <v>100</v>
@@ -6105,31 +6105,31 @@
         <v>100</v>
       </c>
       <c r="N28">
-        <v>105</v>
+        <v>95.2</v>
       </c>
       <c r="O28">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -6143,7 +6143,7 @@
         <v>100</v>
       </c>
       <c r="D29">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E29">
         <v>100</v>
@@ -6164,40 +6164,40 @@
         <v>100</v>
       </c>
       <c r="K29">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L29">
         <v>100</v>
       </c>
       <c r="M29">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="N29">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="O29">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -6211,7 +6211,7 @@
         <v>100</v>
       </c>
       <c r="D30">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E30">
         <v>100</v>
@@ -6232,7 +6232,7 @@
         <v>100</v>
       </c>
       <c r="K30">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L30">
         <v>100</v>
@@ -6241,31 +6241,31 @@
         <v>100</v>
       </c>
       <c r="N30">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="O30">
         <v>100</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -6279,7 +6279,7 @@
         <v>100</v>
       </c>
       <c r="D31">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E31">
         <v>100</v>
@@ -6300,7 +6300,7 @@
         <v>100</v>
       </c>
       <c r="K31">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L31">
         <v>100</v>
@@ -6309,31 +6309,31 @@
         <v>100</v>
       </c>
       <c r="N31">
-        <v>110</v>
+        <v>95.2</v>
       </c>
       <c r="O31">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -6347,7 +6347,7 @@
         <v>100</v>
       </c>
       <c r="D32">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E32">
         <v>100</v>
@@ -6362,13 +6362,13 @@
         <v>100</v>
       </c>
       <c r="I32">
-        <v>97.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="J32">
         <v>100</v>
       </c>
       <c r="K32">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L32">
         <v>100</v>
@@ -6377,31 +6377,31 @@
         <v>100</v>
       </c>
       <c r="N32">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="O32">
         <v>100</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -6415,7 +6415,7 @@
         <v>100</v>
       </c>
       <c r="D33">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E33">
         <v>100</v>
@@ -6436,40 +6436,40 @@
         <v>100</v>
       </c>
       <c r="K33">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L33">
         <v>100</v>
       </c>
       <c r="M33">
-        <v>66.7</v>
+        <v>83.3</v>
       </c>
       <c r="N33">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="O33">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -6483,7 +6483,7 @@
         <v>96</v>
       </c>
       <c r="D34">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E34">
         <v>100</v>
@@ -6501,43 +6501,43 @@
         <v>100</v>
       </c>
       <c r="J34">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K34">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L34">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M34">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="N34">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="O34">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="35" spans="1:22">
@@ -6551,7 +6551,7 @@
         <v>96</v>
       </c>
       <c r="D35">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E35">
         <v>100</v>
@@ -6569,43 +6569,43 @@
         <v>97.09999999999999</v>
       </c>
       <c r="J35">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K35">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L35">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M35">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="N35">
-        <v>110</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="O35">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="36" spans="1:22">
@@ -6619,7 +6619,7 @@
         <v>96</v>
       </c>
       <c r="D36">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E36">
         <v>100</v>
@@ -6637,43 +6637,43 @@
         <v>100</v>
       </c>
       <c r="J36">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K36">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L36">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M36">
         <v>100</v>
       </c>
       <c r="N36">
-        <v>110</v>
+        <v>90.5</v>
       </c>
       <c r="O36">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>90.5</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="37" spans="1:22">
@@ -6687,7 +6687,7 @@
         <v>96</v>
       </c>
       <c r="D37">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E37">
         <v>100</v>
@@ -6702,46 +6702,46 @@
         <v>90</v>
       </c>
       <c r="I37">
-        <v>97.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="J37">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K37">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L37">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M37">
-        <v>73.3</v>
+        <v>86.7</v>
       </c>
       <c r="N37">
-        <v>95</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="O37">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="38" spans="1:22">
@@ -6755,7 +6755,7 @@
         <v>100</v>
       </c>
       <c r="D38">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E38">
         <v>100</v>
@@ -6776,7 +6776,7 @@
         <v>100</v>
       </c>
       <c r="K38">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L38">
         <v>100</v>
@@ -6785,31 +6785,31 @@
         <v>100</v>
       </c>
       <c r="N38">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="O38">
         <v>100</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:22">
@@ -6823,7 +6823,7 @@
         <v>100</v>
       </c>
       <c r="D39">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E39">
         <v>100</v>
@@ -6838,13 +6838,13 @@
         <v>100</v>
       </c>
       <c r="I39">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="J39">
         <v>100</v>
       </c>
       <c r="K39">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L39">
         <v>100</v>
@@ -6853,31 +6853,31 @@
         <v>100</v>
       </c>
       <c r="N39">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="O39">
         <v>100</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:22">
@@ -6891,7 +6891,7 @@
         <v>96</v>
       </c>
       <c r="D40">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E40">
         <v>100</v>
@@ -6906,46 +6906,46 @@
         <v>100</v>
       </c>
       <c r="I40">
-        <v>94.3</v>
+        <v>95.7</v>
       </c>
       <c r="J40">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K40">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L40">
         <v>100</v>
       </c>
       <c r="M40">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="N40">
-        <v>110</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="O40">
         <v>100</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>95.7</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:22">
@@ -6959,7 +6959,7 @@
         <v>96</v>
       </c>
       <c r="D41">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E41">
         <v>100</v>
@@ -6977,10 +6977,10 @@
         <v>100</v>
       </c>
       <c r="J41">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K41">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L41">
         <v>100</v>
@@ -6989,31 +6989,31 @@
         <v>100</v>
       </c>
       <c r="N41">
-        <v>110</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O41">
         <v>100</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:22">
@@ -7027,7 +7027,7 @@
         <v>100</v>
       </c>
       <c r="D42">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E42">
         <v>100</v>
@@ -7042,13 +7042,13 @@
         <v>90</v>
       </c>
       <c r="I42">
-        <v>97.09999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="J42">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K42">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L42">
         <v>100</v>
@@ -7057,31 +7057,31 @@
         <v>100</v>
       </c>
       <c r="N42">
-        <v>105</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="O42">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>95.7</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/2APM - Estadisticos 20222.xlsx
+++ b/grupos/2APM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="106">
   <si>
     <t>Materia</t>
   </si>
@@ -212,18 +212,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Herrera Serrano Mayra Iliana</t>
+  </si>
+  <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
-    <t>Herrera Serrano Mayra Iliana</t>
-  </si>
-  <si>
-    <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
     <t>De Jesús Orduña Sofía del Pilar</t>
   </si>
   <si>
@@ -245,12 +245,27 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CALOCA</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
     <t>RAMOS</t>
   </si>
   <si>
@@ -263,49 +278,43 @@
     <t>VELASCO</t>
   </si>
   <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CALOCA</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
   </si>
   <si>
     <t>LEON</t>
   </si>
   <si>
+    <t>SORIANO</t>
+  </si>
+  <si>
     <t>ALFONSO</t>
   </si>
   <si>
     <t>ANGUIANO</t>
   </si>
   <si>
-    <t>CERON</t>
-  </si>
-  <si>
     <t>SAN JUAN</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>CUAQUEHUA</t>
-  </si>
-  <si>
-    <t>SORIANO</t>
+    <t>JESUS EMMANUEL</t>
+  </si>
+  <si>
+    <t>EDUARDO EMER</t>
+  </si>
+  <si>
+    <t>LESLY VIANEY</t>
+  </si>
+  <si>
+    <t>ARLETH MARELY</t>
   </si>
   <si>
     <t>LLUVIA RUBI</t>
@@ -314,6 +323,9 @@
     <t>TONALLI</t>
   </si>
   <si>
+    <t>LIZBETH</t>
+  </si>
+  <si>
     <t>JULIO</t>
   </si>
   <si>
@@ -324,21 +336,6 @@
   </si>
   <si>
     <t>DULCE REGINA</t>
-  </si>
-  <si>
-    <t>EDUARDO EMER</t>
-  </si>
-  <si>
-    <t>LESLY VIANEY</t>
-  </si>
-  <si>
-    <t>ARLETH MARELY</t>
-  </si>
-  <si>
-    <t>MELANIE</t>
-  </si>
-  <si>
-    <t>LIZBETH</t>
   </si>
 </sst>
 </file>
@@ -895,10 +892,10 @@
         <v>-1</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U4">
         <v>-1</v>
@@ -984,10 +981,10 @@
         <v>-1</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U5">
         <v>-1</v>
@@ -1073,10 +1070,10 @@
         <v>-1</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U6">
         <v>-1</v>
@@ -1162,10 +1159,10 @@
         <v>-1</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U7">
         <v>-1</v>
@@ -1183,7 +1180,7 @@
         <v>9</v>
       </c>
       <c r="Z7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA7">
         <v>7</v>
@@ -1251,10 +1248,10 @@
         <v>-1</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U8">
         <v>-1</v>
@@ -1275,7 +1272,7 @@
         <v>6</v>
       </c>
       <c r="AA8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB8">
         <v>10</v>
@@ -1340,10 +1337,10 @@
         <v>-1</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U9">
         <v>-1</v>
@@ -1429,10 +1426,10 @@
         <v>-1</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U10">
         <v>-1</v>
@@ -1518,10 +1515,10 @@
         <v>-1</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U11">
         <v>-1</v>
@@ -1539,7 +1536,7 @@
         <v>9</v>
       </c>
       <c r="Z11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA11">
         <v>10</v>
@@ -1607,10 +1604,10 @@
         <v>-1</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U12">
         <v>-1</v>
@@ -1628,7 +1625,7 @@
         <v>7</v>
       </c>
       <c r="Z12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA12">
         <v>5</v>
@@ -1696,10 +1693,10 @@
         <v>-1</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U13">
         <v>-1</v>
@@ -1785,10 +1782,10 @@
         <v>-1</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U14">
         <v>-1</v>
@@ -1809,7 +1806,7 @@
         <v>6</v>
       </c>
       <c r="AA14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB14">
         <v>9</v>
@@ -1874,10 +1871,10 @@
         <v>-1</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U15">
         <v>-1</v>
@@ -1963,10 +1960,10 @@
         <v>-1</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U16">
         <v>-1</v>
@@ -1984,10 +1981,10 @@
         <v>8</v>
       </c>
       <c r="Z16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB16">
         <v>6</v>
@@ -2052,10 +2049,10 @@
         <v>-1</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U17">
         <v>-1</v>
@@ -2073,10 +2070,10 @@
         <v>8</v>
       </c>
       <c r="Z17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB17">
         <v>9</v>
@@ -2141,10 +2138,10 @@
         <v>-1</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U18">
         <v>-1</v>
@@ -2162,10 +2159,10 @@
         <v>8</v>
       </c>
       <c r="Z18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA18">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AB18">
         <v>7</v>
@@ -2230,10 +2227,10 @@
         <v>-1</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U19">
         <v>-1</v>
@@ -2251,10 +2248,10 @@
         <v>8</v>
       </c>
       <c r="Z19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB19">
         <v>6</v>
@@ -2319,10 +2316,10 @@
         <v>-1</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U20">
         <v>-1</v>
@@ -2408,10 +2405,10 @@
         <v>-1</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U21">
         <v>-1</v>
@@ -2429,7 +2426,7 @@
         <v>8</v>
       </c>
       <c r="Z21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA21">
         <v>8</v>
@@ -2497,10 +2494,10 @@
         <v>-1</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U22">
         <v>-1</v>
@@ -2586,10 +2583,10 @@
         <v>-1</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U23">
         <v>-1</v>
@@ -2607,7 +2604,7 @@
         <v>8</v>
       </c>
       <c r="Z23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA23">
         <v>7</v>
@@ -2675,10 +2672,10 @@
         <v>-1</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U24">
         <v>-1</v>
@@ -2699,7 +2696,7 @@
         <v>6</v>
       </c>
       <c r="AA24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB24">
         <v>8</v>
@@ -2764,10 +2761,10 @@
         <v>-1</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U25">
         <v>-1</v>
@@ -2785,10 +2782,10 @@
         <v>8</v>
       </c>
       <c r="Z25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB25">
         <v>9</v>
@@ -2853,10 +2850,10 @@
         <v>-1</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U26">
         <v>-1</v>
@@ -2874,10 +2871,10 @@
         <v>9</v>
       </c>
       <c r="Z26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB26">
         <v>10</v>
@@ -2942,10 +2939,10 @@
         <v>-1</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U27">
         <v>-1</v>
@@ -2966,7 +2963,7 @@
         <v>8</v>
       </c>
       <c r="AA27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB27">
         <v>10</v>
@@ -3031,10 +3028,10 @@
         <v>-1</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U28">
         <v>-1</v>
@@ -3055,7 +3052,7 @@
         <v>6</v>
       </c>
       <c r="AA28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB28">
         <v>10</v>
@@ -3120,10 +3117,10 @@
         <v>-1</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U29">
         <v>-1</v>
@@ -3141,7 +3138,7 @@
         <v>9</v>
       </c>
       <c r="Z29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA29">
         <v>7</v>
@@ -3209,10 +3206,10 @@
         <v>-1</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U30">
         <v>-1</v>
@@ -3230,7 +3227,7 @@
         <v>10</v>
       </c>
       <c r="Z30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA30">
         <v>10</v>
@@ -3298,10 +3295,10 @@
         <v>-1</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U31">
         <v>-1</v>
@@ -3322,7 +3319,7 @@
         <v>8</v>
       </c>
       <c r="AA31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB31">
         <v>9</v>
@@ -3387,10 +3384,10 @@
         <v>-1</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U32">
         <v>-1</v>
@@ -3408,10 +3405,10 @@
         <v>10</v>
       </c>
       <c r="Z32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB32">
         <v>10</v>
@@ -3476,10 +3473,10 @@
         <v>-1</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U33">
         <v>-1</v>
@@ -3565,10 +3562,10 @@
         <v>-1</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U34">
         <v>-1</v>
@@ -3586,7 +3583,7 @@
         <v>8</v>
       </c>
       <c r="Z34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA34">
         <v>6</v>
@@ -3654,10 +3651,10 @@
         <v>-1</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U35">
         <v>-1</v>
@@ -3743,10 +3740,10 @@
         <v>-1</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U36">
         <v>-1</v>
@@ -3767,7 +3764,7 @@
         <v>8</v>
       </c>
       <c r="AA36">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB36">
         <v>10</v>
@@ -3832,10 +3829,10 @@
         <v>-1</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U37">
         <v>-1</v>
@@ -3853,7 +3850,7 @@
         <v>7</v>
       </c>
       <c r="Z37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA37">
         <v>6</v>
@@ -3921,10 +3918,10 @@
         <v>-1</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U38">
         <v>-1</v>
@@ -4010,10 +4007,10 @@
         <v>-1</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U39">
         <v>-1</v>
@@ -4034,7 +4031,7 @@
         <v>7</v>
       </c>
       <c r="AA39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB39">
         <v>10</v>
@@ -4099,10 +4096,10 @@
         <v>-1</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U40">
         <v>-1</v>
@@ -4120,7 +4117,7 @@
         <v>8</v>
       </c>
       <c r="Z40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA40">
         <v>7</v>
@@ -4188,10 +4185,10 @@
         <v>-1</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U41">
         <v>-1</v>
@@ -4212,7 +4209,7 @@
         <v>7</v>
       </c>
       <c r="AA41">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB41">
         <v>9</v>
@@ -4277,10 +4274,10 @@
         <v>-1</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U42">
         <v>-1</v>
@@ -4298,7 +4295,7 @@
         <v>7</v>
       </c>
       <c r="Z42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA42">
         <v>6</v>
@@ -4556,7 +4553,7 @@
         <v>100</v>
       </c>
       <c r="S5">
-        <v>97.5</v>
+        <v>60.9</v>
       </c>
       <c r="T5">
         <v>83.3</v>
@@ -4763,7 +4760,7 @@
         <v>100</v>
       </c>
       <c r="T8">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="U8">
         <v>90.5</v>
@@ -4828,10 +4825,10 @@
         <v>27.1</v>
       </c>
       <c r="S9">
-        <v>72.5</v>
+        <v>45.3</v>
       </c>
       <c r="T9">
-        <v>86.7</v>
+        <v>54.2</v>
       </c>
       <c r="U9">
         <v>64.3</v>
@@ -4896,7 +4893,7 @@
         <v>100</v>
       </c>
       <c r="S10">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="T10">
         <v>100</v>
@@ -5032,10 +5029,10 @@
         <v>100</v>
       </c>
       <c r="S12">
-        <v>85</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="T12">
-        <v>86.7</v>
+        <v>60.4</v>
       </c>
       <c r="U12">
         <v>85.7</v>
@@ -5100,10 +5097,10 @@
         <v>95.8</v>
       </c>
       <c r="S13">
-        <v>80</v>
+        <v>81.3</v>
       </c>
       <c r="T13">
-        <v>83.3</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="U13">
         <v>81</v>
@@ -5168,7 +5165,7 @@
         <v>100</v>
       </c>
       <c r="S14">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="T14">
         <v>100</v>
@@ -5307,7 +5304,7 @@
         <v>100</v>
       </c>
       <c r="T16">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="U16">
         <v>90.5</v>
@@ -5372,10 +5369,10 @@
         <v>100</v>
       </c>
       <c r="S17">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T17">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="U17">
         <v>88.09999999999999</v>
@@ -5440,10 +5437,10 @@
         <v>100</v>
       </c>
       <c r="S18">
-        <v>87.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="T18">
-        <v>83.3</v>
+        <v>68.8</v>
       </c>
       <c r="U18">
         <v>88.09999999999999</v>
@@ -5508,10 +5505,10 @@
         <v>100</v>
       </c>
       <c r="S19">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T19">
-        <v>83.3</v>
+        <v>68.8</v>
       </c>
       <c r="U19">
         <v>81</v>
@@ -5576,7 +5573,7 @@
         <v>100</v>
       </c>
       <c r="S20">
-        <v>92.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="T20">
         <v>100</v>
@@ -5644,10 +5641,10 @@
         <v>100</v>
       </c>
       <c r="S21">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T21">
-        <v>86.7</v>
+        <v>91.7</v>
       </c>
       <c r="U21">
         <v>95.2</v>
@@ -5712,10 +5709,10 @@
         <v>100</v>
       </c>
       <c r="S22">
-        <v>87.5</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="T22">
-        <v>83.3</v>
+        <v>60.4</v>
       </c>
       <c r="U22">
         <v>85.7</v>
@@ -5916,10 +5913,10 @@
         <v>100</v>
       </c>
       <c r="S25">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T25">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="U25">
         <v>92.90000000000001</v>
@@ -6191,7 +6188,7 @@
         <v>100</v>
       </c>
       <c r="T29">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="U29">
         <v>100</v>
@@ -6463,7 +6460,7 @@
         <v>100</v>
       </c>
       <c r="T33">
-        <v>83.3</v>
+        <v>75</v>
       </c>
       <c r="U33">
         <v>95.2</v>
@@ -6528,10 +6525,10 @@
         <v>100</v>
       </c>
       <c r="S34">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T34">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="U34">
         <v>95.2</v>
@@ -6596,10 +6593,10 @@
         <v>100</v>
       </c>
       <c r="S35">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T35">
-        <v>83.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="U35">
         <v>92.90000000000001</v>
@@ -6664,7 +6661,7 @@
         <v>100</v>
       </c>
       <c r="S36">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T36">
         <v>100</v>
@@ -6732,10 +6729,10 @@
         <v>100</v>
       </c>
       <c r="S37">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T37">
-        <v>86.7</v>
+        <v>91.7</v>
       </c>
       <c r="U37">
         <v>78.59999999999999</v>
@@ -6939,7 +6936,7 @@
         <v>100</v>
       </c>
       <c r="T40">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="U40">
         <v>92.90000000000001</v>
@@ -7138,7 +7135,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
@@ -7170,7 +7167,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
         <v>65</v>
@@ -7179,19 +7176,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="E3">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="F3" s="2">
-        <v>56.4</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G3" s="2">
-        <v>43.6</v>
+        <v>17.9</v>
       </c>
       <c r="H3">
-        <v>6.5</v>
+        <v>7.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7202,7 +7199,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>66</v>
@@ -7234,7 +7231,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
@@ -7255,7 +7252,7 @@
         <v>15.4</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7401,7 +7398,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7433,22 +7430,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920163</v>
+        <v>22330051920157</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7456,22 +7453,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920163</v>
+        <v>22330051920157</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="D3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -7479,22 +7476,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920299</v>
+        <v>22330051920150</v>
       </c>
       <c r="B4" t="s">
         <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7502,19 +7499,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920299</v>
+        <v>22330051920155</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D5" t="s">
         <v>97</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F5" t="s">
         <v>64</v>
@@ -7525,13 +7522,13 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920170</v>
+        <v>22330051920381</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D6" t="s">
         <v>98</v>
@@ -7540,7 +7537,7 @@
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7548,19 +7545,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920170</v>
+        <v>22330051920163</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
         <v>64</v>
@@ -7571,22 +7568,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920172</v>
+        <v>22330051920299</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7594,19 +7591,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920172</v>
+        <v>22330051920164</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
         <v>64</v>
@@ -7617,22 +7614,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920175</v>
+        <v>22330051920170</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -7640,19 +7637,19 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920175</v>
+        <v>22330051920172</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D11" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
         <v>64</v>
@@ -7663,22 +7660,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920287</v>
+        <v>22330051920175</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="D12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E12" t="s">
         <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -7689,136 +7686,21 @@
         <v>22330051920287</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C13" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D13" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F13" t="s">
         <v>64</v>
       </c>
       <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920150</v>
-      </c>
-      <c r="B14" t="s">
-        <v>81</v>
-      </c>
-      <c r="C14" t="s">
-        <v>91</v>
-      </c>
-      <c r="D14" t="s">
-        <v>102</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>64</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920155</v>
-      </c>
-      <c r="B15" t="s">
-        <v>82</v>
-      </c>
-      <c r="C15" t="s">
-        <v>92</v>
-      </c>
-      <c r="D15" t="s">
-        <v>103</v>
-      </c>
-      <c r="E15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" t="s">
-        <v>65</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920381</v>
-      </c>
-      <c r="B16" t="s">
-        <v>83</v>
-      </c>
-      <c r="C16" t="s">
-        <v>93</v>
-      </c>
-      <c r="D16" t="s">
-        <v>104</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>65</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920158</v>
-      </c>
-      <c r="B17" t="s">
-        <v>84</v>
-      </c>
-      <c r="C17" t="s">
-        <v>94</v>
-      </c>
-      <c r="D17" t="s">
-        <v>105</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>64</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920164</v>
-      </c>
-      <c r="B18" t="s">
-        <v>85</v>
-      </c>
-      <c r="C18" t="s">
-        <v>95</v>
-      </c>
-      <c r="D18" t="s">
-        <v>106</v>
-      </c>
-      <c r="E18" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" t="s">
-        <v>65</v>
-      </c>
-      <c r="G18">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2APM - Estadisticos 20222.xlsx
+++ b/grupos/2APM - Estadisticos 20222.xlsx
@@ -227,10 +227,10 @@
     <t>De Jesús Orduña Sofía del Pilar</t>
   </si>
   <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
     <t>Moreno Aroyo Anél</t>
-  </si>
-  <si>
-    <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
     <t>NC</t>
@@ -889,7 +889,7 @@
         <v>-1</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
         <v>10</v>
@@ -978,7 +978,7 @@
         <v>-1</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
         <v>5</v>
@@ -1067,7 +1067,7 @@
         <v>-1</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S6">
         <v>8</v>
@@ -1156,7 +1156,7 @@
         <v>-1</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S7">
         <v>7</v>
@@ -1245,7 +1245,7 @@
         <v>-1</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S8">
         <v>7</v>
@@ -1334,7 +1334,7 @@
         <v>-1</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S9">
         <v>5</v>
@@ -1423,7 +1423,7 @@
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S10">
         <v>6</v>
@@ -1512,7 +1512,7 @@
         <v>-1</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
         <v>8</v>
@@ -1601,7 +1601,7 @@
         <v>-1</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S12">
         <v>7</v>
@@ -1622,7 +1622,7 @@
         <v>5</v>
       </c>
       <c r="Y12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z12">
         <v>6</v>
@@ -1690,7 +1690,7 @@
         <v>-1</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S13">
         <v>5</v>
@@ -1779,7 +1779,7 @@
         <v>-1</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S14">
         <v>7</v>
@@ -1800,7 +1800,7 @@
         <v>8</v>
       </c>
       <c r="Y14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z14">
         <v>6</v>
@@ -1868,7 +1868,7 @@
         <v>-1</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
         <v>7</v>
@@ -1889,7 +1889,7 @@
         <v>8</v>
       </c>
       <c r="Y15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z15">
         <v>6</v>
@@ -1957,7 +1957,7 @@
         <v>-1</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S16">
         <v>7</v>
@@ -1978,7 +1978,7 @@
         <v>5</v>
       </c>
       <c r="Y16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z16">
         <v>6</v>
@@ -2046,7 +2046,7 @@
         <v>-1</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
         <v>7</v>
@@ -2135,7 +2135,7 @@
         <v>-1</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S18">
         <v>9</v>
@@ -2156,7 +2156,7 @@
         <v>6</v>
       </c>
       <c r="Y18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z18">
         <v>6</v>
@@ -2224,7 +2224,7 @@
         <v>-1</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S19">
         <v>9</v>
@@ -2245,7 +2245,7 @@
         <v>6</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z19">
         <v>6</v>
@@ -2313,7 +2313,7 @@
         <v>-1</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S20">
         <v>5</v>
@@ -2334,7 +2334,7 @@
         <v>5</v>
       </c>
       <c r="Y20">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z20">
         <v>5</v>
@@ -2402,7 +2402,7 @@
         <v>-1</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
         <v>8</v>
@@ -2491,7 +2491,7 @@
         <v>-1</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S22">
         <v>5</v>
@@ -2512,7 +2512,7 @@
         <v>5</v>
       </c>
       <c r="Y22">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z22">
         <v>5</v>
@@ -2580,7 +2580,7 @@
         <v>-1</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S23">
         <v>7</v>
@@ -2669,7 +2669,7 @@
         <v>-1</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S24">
         <v>7</v>
@@ -2758,7 +2758,7 @@
         <v>-1</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S25">
         <v>7</v>
@@ -2847,7 +2847,7 @@
         <v>-1</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S26">
         <v>7</v>
@@ -2868,7 +2868,7 @@
         <v>9</v>
       </c>
       <c r="Y26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z26">
         <v>7</v>
@@ -2936,7 +2936,7 @@
         <v>-1</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S27">
         <v>8</v>
@@ -3025,7 +3025,7 @@
         <v>-1</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S28">
         <v>7</v>
@@ -3046,7 +3046,7 @@
         <v>8</v>
       </c>
       <c r="Y28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z28">
         <v>6</v>
@@ -3114,7 +3114,7 @@
         <v>-1</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S29">
         <v>6</v>
@@ -3135,7 +3135,7 @@
         <v>9</v>
       </c>
       <c r="Y29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z29">
         <v>6</v>
@@ -3203,7 +3203,7 @@
         <v>-1</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
         <v>8</v>
@@ -3292,7 +3292,7 @@
         <v>-1</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
         <v>8</v>
@@ -3381,7 +3381,7 @@
         <v>-1</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
         <v>8</v>
@@ -3470,7 +3470,7 @@
         <v>-1</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S33">
         <v>6</v>
@@ -3491,7 +3491,7 @@
         <v>7</v>
       </c>
       <c r="Y33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z33">
         <v>5</v>
@@ -3559,7 +3559,7 @@
         <v>-1</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S34">
         <v>7</v>
@@ -3580,7 +3580,7 @@
         <v>7</v>
       </c>
       <c r="Y34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z34">
         <v>6</v>
@@ -3648,7 +3648,7 @@
         <v>-1</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S35">
         <v>8</v>
@@ -3737,7 +3737,7 @@
         <v>-1</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S36">
         <v>8</v>
@@ -3758,7 +3758,7 @@
         <v>8</v>
       </c>
       <c r="Y36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z36">
         <v>8</v>
@@ -3826,7 +3826,7 @@
         <v>-1</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S37">
         <v>8</v>
@@ -3847,7 +3847,7 @@
         <v>6</v>
       </c>
       <c r="Y37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z37">
         <v>6</v>
@@ -3915,7 +3915,7 @@
         <v>-1</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S38">
         <v>8</v>
@@ -4004,7 +4004,7 @@
         <v>-1</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S39">
         <v>7</v>
@@ -4093,7 +4093,7 @@
         <v>-1</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S40">
         <v>9</v>
@@ -4182,7 +4182,7 @@
         <v>-1</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S41">
         <v>8</v>
@@ -4271,7 +4271,7 @@
         <v>-1</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S42">
         <v>7</v>
@@ -4292,7 +4292,7 @@
         <v>6</v>
       </c>
       <c r="Y42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z42">
         <v>6</v>
@@ -4822,7 +4822,7 @@
         <v>84</v>
       </c>
       <c r="R9">
-        <v>27.1</v>
+        <v>18.1</v>
       </c>
       <c r="S9">
         <v>45.3</v>
@@ -5026,7 +5026,7 @@
         <v>94</v>
       </c>
       <c r="R12">
-        <v>100</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="S12">
         <v>90.59999999999999</v>
@@ -5094,7 +5094,7 @@
         <v>92</v>
       </c>
       <c r="R13">
-        <v>95.8</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="S13">
         <v>81.3</v>
@@ -5570,7 +5570,7 @@
         <v>98</v>
       </c>
       <c r="R20">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="S20">
         <v>89.09999999999999</v>
@@ -5706,7 +5706,7 @@
         <v>94</v>
       </c>
       <c r="R22">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="S22">
         <v>78.09999999999999</v>
@@ -7066,7 +7066,7 @@
         <v>98</v>
       </c>
       <c r="R42">
-        <v>100</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="S42">
         <v>100</v>
@@ -7295,7 +7295,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>69</v>
@@ -7304,19 +7304,19 @@
         <v>39</v>
       </c>
       <c r="D7">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" s="2">
-        <v>94.90000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="G7" s="2">
-        <v>5.1</v>
+        <v>7.7</v>
       </c>
       <c r="H7">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7327,7 +7327,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
         <v>70</v>
@@ -7336,19 +7336,19 @@
         <v>39</v>
       </c>
       <c r="D8">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="2">
-        <v>97.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="G8" s="2">
-        <v>2.6</v>
+        <v>5.1</v>
       </c>
       <c r="H8">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="I8">
         <v>0</v>

--- a/grupos/2APM - Estadisticos 20222.xlsx
+++ b/grupos/2APM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="90">
   <si>
     <t>Materia</t>
   </si>
@@ -212,27 +212,27 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
+    <t>Moreno Aroyo Anél</t>
+  </si>
+  <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
-    <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
-    <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
     <t>De Jesús Orduña Sofía del Pilar</t>
   </si>
   <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
-    <t>Moreno Aroyo Anél</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -248,94 +248,46 @@
     <t>CERON</t>
   </si>
   <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
     <t>BAEZ</t>
   </si>
   <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CALOCA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
     <t>ROJAS</t>
   </si>
   <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>VELASCO</t>
-  </si>
-  <si>
     <t>ORTEGA</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>SORIANO</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
     <t>ANGUIANO</t>
   </si>
   <si>
-    <t>SAN JUAN</t>
-  </si>
-  <si>
     <t>JESUS EMMANUEL</t>
   </si>
   <si>
+    <t>GLORIA</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
     <t>EDUARDO EMER</t>
   </si>
   <si>
-    <t>LESLY VIANEY</t>
-  </si>
-  <si>
-    <t>ARLETH MARELY</t>
-  </si>
-  <si>
-    <t>LLUVIA RUBI</t>
-  </si>
-  <si>
-    <t>TONALLI</t>
-  </si>
-  <si>
-    <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>JULIO</t>
-  </si>
-  <si>
     <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>FRIDA SOFIA</t>
-  </si>
-  <si>
-    <t>DULCE REGINA</t>
   </si>
 </sst>
 </file>
@@ -883,10 +835,10 @@
         <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>10</v>
@@ -898,7 +850,7 @@
         <v>10</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V4">
         <v>-1</v>
@@ -972,10 +924,10 @@
         <v>7</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R5">
         <v>9</v>
@@ -987,7 +939,7 @@
         <v>7</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V5">
         <v>-1</v>
@@ -996,7 +948,7 @@
         <v>8</v>
       </c>
       <c r="X5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y5">
         <v>9</v>
@@ -1008,7 +960,7 @@
         <v>7</v>
       </c>
       <c r="AB5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC5">
         <v>6</v>
@@ -1061,10 +1013,10 @@
         <v>7</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R6">
         <v>8</v>
@@ -1076,7 +1028,7 @@
         <v>8</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V6">
         <v>-1</v>
@@ -1085,7 +1037,7 @@
         <v>8</v>
       </c>
       <c r="X6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y6">
         <v>8</v>
@@ -1097,7 +1049,7 @@
         <v>9</v>
       </c>
       <c r="AB6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC6">
         <v>8</v>
@@ -1150,10 +1102,10 @@
         <v>9</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R7">
         <v>9</v>
@@ -1165,7 +1117,7 @@
         <v>7</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V7">
         <v>-1</v>
@@ -1174,7 +1126,7 @@
         <v>7</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y7">
         <v>9</v>
@@ -1186,7 +1138,7 @@
         <v>7</v>
       </c>
       <c r="AB7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC7">
         <v>9</v>
@@ -1239,10 +1191,10 @@
         <v>6</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
         <v>8</v>
@@ -1254,13 +1206,13 @@
         <v>6</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V8">
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X8">
         <v>8</v>
@@ -1275,7 +1227,7 @@
         <v>7</v>
       </c>
       <c r="AB8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC8">
         <v>6</v>
@@ -1328,10 +1280,10 @@
         <v>5</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R9">
         <v>5</v>
@@ -1343,7 +1295,7 @@
         <v>5</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V9">
         <v>-1</v>
@@ -1417,10 +1369,10 @@
         <v>6</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R10">
         <v>8</v>
@@ -1432,13 +1384,13 @@
         <v>9</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V10">
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X10">
         <v>7</v>
@@ -1453,7 +1405,7 @@
         <v>8</v>
       </c>
       <c r="AB10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC10">
         <v>7</v>
@@ -1506,10 +1458,10 @@
         <v>9</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
         <v>10</v>
@@ -1521,7 +1473,7 @@
         <v>10</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V11">
         <v>-1</v>
@@ -1595,10 +1547,10 @@
         <v>5</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R12">
         <v>5</v>
@@ -1610,7 +1562,7 @@
         <v>5</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V12">
         <v>-1</v>
@@ -1631,7 +1583,7 @@
         <v>5</v>
       </c>
       <c r="AB12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC12">
         <v>5</v>
@@ -1684,10 +1636,10 @@
         <v>5</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R13">
         <v>6</v>
@@ -1699,7 +1651,7 @@
         <v>6</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V13">
         <v>-1</v>
@@ -1720,7 +1672,7 @@
         <v>6</v>
       </c>
       <c r="AB13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC13">
         <v>5</v>
@@ -1773,10 +1725,10 @@
         <v>6</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R14">
         <v>6</v>
@@ -1788,16 +1740,16 @@
         <v>6</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V14">
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y14">
         <v>6</v>
@@ -1809,7 +1761,7 @@
         <v>6</v>
       </c>
       <c r="AB14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC14">
         <v>7</v>
@@ -1862,10 +1814,10 @@
         <v>8</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R15">
         <v>8</v>
@@ -1877,13 +1829,13 @@
         <v>8</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V15">
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X15">
         <v>8</v>
@@ -1898,7 +1850,7 @@
         <v>8</v>
       </c>
       <c r="AB15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC15">
         <v>8</v>
@@ -1951,10 +1903,10 @@
         <v>5</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R16">
         <v>7</v>
@@ -1966,7 +1918,7 @@
         <v>7</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V16">
         <v>-1</v>
@@ -1975,7 +1927,7 @@
         <v>6</v>
       </c>
       <c r="X16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y16">
         <v>7</v>
@@ -1987,7 +1939,7 @@
         <v>6</v>
       </c>
       <c r="AB16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC16">
         <v>5</v>
@@ -2040,10 +1992,10 @@
         <v>7</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R17">
         <v>8</v>
@@ -2055,7 +2007,7 @@
         <v>6</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V17">
         <v>-1</v>
@@ -2064,7 +2016,7 @@
         <v>7</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y17">
         <v>8</v>
@@ -2076,7 +2028,7 @@
         <v>7</v>
       </c>
       <c r="AB17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC17">
         <v>8</v>
@@ -2129,10 +2081,10 @@
         <v>5</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R18">
         <v>7</v>
@@ -2144,13 +2096,13 @@
         <v>5</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V18">
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X18">
         <v>6</v>
@@ -2165,7 +2117,7 @@
         <v>5</v>
       </c>
       <c r="AB18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC18">
         <v>5</v>
@@ -2218,10 +2170,10 @@
         <v>5</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R19">
         <v>6</v>
@@ -2233,13 +2185,13 @@
         <v>5</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V19">
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X19">
         <v>6</v>
@@ -2254,7 +2206,7 @@
         <v>5</v>
       </c>
       <c r="AB19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC19">
         <v>5</v>
@@ -2307,10 +2259,10 @@
         <v>5</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R20">
         <v>5</v>
@@ -2322,7 +2274,7 @@
         <v>5</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V20">
         <v>-1</v>
@@ -2343,7 +2295,7 @@
         <v>5</v>
       </c>
       <c r="AB20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC20">
         <v>7</v>
@@ -2396,10 +2348,10 @@
         <v>6</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R21">
         <v>8</v>
@@ -2411,16 +2363,16 @@
         <v>8</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V21">
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y21">
         <v>8</v>
@@ -2432,7 +2384,7 @@
         <v>8</v>
       </c>
       <c r="AB21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC21">
         <v>7</v>
@@ -2485,10 +2437,10 @@
         <v>5</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R22">
         <v>5</v>
@@ -2500,7 +2452,7 @@
         <v>5</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V22">
         <v>-1</v>
@@ -2574,10 +2526,10 @@
         <v>6</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R23">
         <v>8</v>
@@ -2589,16 +2541,16 @@
         <v>6</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V23">
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y23">
         <v>8</v>
@@ -2610,7 +2562,7 @@
         <v>7</v>
       </c>
       <c r="AB23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC23">
         <v>7</v>
@@ -2663,10 +2615,10 @@
         <v>6</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R24">
         <v>8</v>
@@ -2678,16 +2630,16 @@
         <v>6</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V24">
         <v>-1</v>
       </c>
       <c r="W24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y24">
         <v>8</v>
@@ -2699,7 +2651,7 @@
         <v>7</v>
       </c>
       <c r="AB24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC24">
         <v>7</v>
@@ -2752,10 +2704,10 @@
         <v>6</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R25">
         <v>8</v>
@@ -2767,16 +2719,16 @@
         <v>6</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V25">
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y25">
         <v>8</v>
@@ -2788,7 +2740,7 @@
         <v>7</v>
       </c>
       <c r="AB25">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC25">
         <v>7</v>
@@ -2841,10 +2793,10 @@
         <v>8</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R26">
         <v>8</v>
@@ -2856,7 +2808,7 @@
         <v>9</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V26">
         <v>-1</v>
@@ -2930,10 +2882,10 @@
         <v>6</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R27">
         <v>9</v>
@@ -2945,16 +2897,16 @@
         <v>9</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V27">
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y27">
         <v>9</v>
@@ -2966,7 +2918,7 @@
         <v>9</v>
       </c>
       <c r="AB27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC27">
         <v>8</v>
@@ -3019,10 +2971,10 @@
         <v>6</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R28">
         <v>8</v>
@@ -3034,7 +2986,7 @@
         <v>6</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V28">
         <v>-1</v>
@@ -3043,7 +2995,7 @@
         <v>7</v>
       </c>
       <c r="X28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y28">
         <v>8</v>
@@ -3055,7 +3007,7 @@
         <v>8</v>
       </c>
       <c r="AB28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC28">
         <v>8</v>
@@ -3108,10 +3060,10 @@
         <v>8</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R29">
         <v>8</v>
@@ -3123,7 +3075,7 @@
         <v>8</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V29">
         <v>-1</v>
@@ -3132,7 +3084,7 @@
         <v>8</v>
       </c>
       <c r="X29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y29">
         <v>8</v>
@@ -3144,7 +3096,7 @@
         <v>7</v>
       </c>
       <c r="AB29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC29">
         <v>9</v>
@@ -3197,10 +3149,10 @@
         <v>9</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R30">
         <v>10</v>
@@ -3212,7 +3164,7 @@
         <v>10</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V30">
         <v>-1</v>
@@ -3233,7 +3185,7 @@
         <v>10</v>
       </c>
       <c r="AB30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC30">
         <v>9</v>
@@ -3286,10 +3238,10 @@
         <v>8</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R31">
         <v>10</v>
@@ -3301,16 +3253,16 @@
         <v>8</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V31">
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y31">
         <v>10</v>
@@ -3322,7 +3274,7 @@
         <v>9</v>
       </c>
       <c r="AB31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC31">
         <v>9</v>
@@ -3375,10 +3327,10 @@
         <v>9</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R32">
         <v>10</v>
@@ -3390,7 +3342,7 @@
         <v>9</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V32">
         <v>-1</v>
@@ -3464,10 +3416,10 @@
         <v>5</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R33">
         <v>7</v>
@@ -3479,13 +3431,13 @@
         <v>5</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V33">
         <v>-1</v>
       </c>
       <c r="W33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X33">
         <v>7</v>
@@ -3500,7 +3452,7 @@
         <v>5</v>
       </c>
       <c r="AB33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC33">
         <v>7</v>
@@ -3553,10 +3505,10 @@
         <v>6</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R34">
         <v>7</v>
@@ -3568,16 +3520,16 @@
         <v>6</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V34">
         <v>-1</v>
       </c>
       <c r="W34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y34">
         <v>7</v>
@@ -3589,7 +3541,7 @@
         <v>6</v>
       </c>
       <c r="AB34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC34">
         <v>7</v>
@@ -3642,10 +3594,10 @@
         <v>6</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R35">
         <v>9</v>
@@ -3657,13 +3609,13 @@
         <v>8</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V35">
         <v>-1</v>
       </c>
       <c r="W35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X35">
         <v>8</v>
@@ -3731,10 +3683,10 @@
         <v>8</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R36">
         <v>8</v>
@@ -3746,7 +3698,7 @@
         <v>6</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V36">
         <v>-1</v>
@@ -3767,7 +3719,7 @@
         <v>7</v>
       </c>
       <c r="AB36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC36">
         <v>9</v>
@@ -3820,10 +3772,10 @@
         <v>5</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R37">
         <v>6</v>
@@ -3835,13 +3787,13 @@
         <v>6</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V37">
         <v>-1</v>
       </c>
       <c r="W37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X37">
         <v>6</v>
@@ -3856,7 +3808,7 @@
         <v>6</v>
       </c>
       <c r="AB37">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC37">
         <v>6</v>
@@ -3909,10 +3861,10 @@
         <v>9</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R38">
         <v>10</v>
@@ -3924,7 +3876,7 @@
         <v>10</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V38">
         <v>-1</v>
@@ -3998,10 +3950,10 @@
         <v>6</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R39">
         <v>10</v>
@@ -4013,16 +3965,16 @@
         <v>6</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V39">
         <v>-1</v>
       </c>
       <c r="W39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X39">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y39">
         <v>10</v>
@@ -4087,10 +4039,10 @@
         <v>6</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R40">
         <v>8</v>
@@ -4102,16 +4054,16 @@
         <v>8</v>
       </c>
       <c r="U40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V40">
         <v>-1</v>
       </c>
       <c r="W40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X40">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y40">
         <v>8</v>
@@ -4123,7 +4075,7 @@
         <v>7</v>
       </c>
       <c r="AB40">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC40">
         <v>7</v>
@@ -4176,10 +4128,10 @@
         <v>7</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R41">
         <v>7</v>
@@ -4191,13 +4143,13 @@
         <v>6</v>
       </c>
       <c r="U41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V41">
         <v>-1</v>
       </c>
       <c r="W41">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X41">
         <v>8</v>
@@ -4212,7 +4164,7 @@
         <v>8</v>
       </c>
       <c r="AB41">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC41">
         <v>8</v>
@@ -4265,10 +4217,10 @@
         <v>6</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R42">
         <v>5</v>
@@ -4280,13 +4232,13 @@
         <v>7</v>
       </c>
       <c r="U42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V42">
         <v>-1</v>
       </c>
       <c r="W42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X42">
         <v>6</v>
@@ -4301,7 +4253,7 @@
         <v>6</v>
       </c>
       <c r="AB42">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC42">
         <v>6</v>
@@ -4491,7 +4443,7 @@
         <v>100</v>
       </c>
       <c r="U4">
-        <v>97.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="V4">
         <v>100</v>
@@ -4544,7 +4496,7 @@
         <v>82.5</v>
       </c>
       <c r="P5">
-        <v>98.59999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="Q5">
         <v>100</v>
@@ -4559,7 +4511,7 @@
         <v>83.3</v>
       </c>
       <c r="U5">
-        <v>85.7</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="V5">
         <v>82.5</v>
@@ -4612,7 +4564,7 @@
         <v>100</v>
       </c>
       <c r="P6">
-        <v>95.7</v>
+        <v>95.5</v>
       </c>
       <c r="Q6">
         <v>100</v>
@@ -4627,7 +4579,7 @@
         <v>100</v>
       </c>
       <c r="U6">
-        <v>95.2</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V6">
         <v>100</v>
@@ -4683,7 +4635,7 @@
         <v>100</v>
       </c>
       <c r="Q7">
-        <v>98</v>
+        <v>96.3</v>
       </c>
       <c r="R7">
         <v>100</v>
@@ -4695,7 +4647,7 @@
         <v>100</v>
       </c>
       <c r="U7">
-        <v>95.2</v>
+        <v>95.3</v>
       </c>
       <c r="V7">
         <v>100</v>
@@ -4748,10 +4700,10 @@
         <v>85</v>
       </c>
       <c r="P8">
-        <v>94.3</v>
+        <v>93.8</v>
       </c>
       <c r="Q8">
-        <v>94</v>
+        <v>93.8</v>
       </c>
       <c r="R8">
         <v>100</v>
@@ -4763,7 +4715,7 @@
         <v>91.7</v>
       </c>
       <c r="U8">
-        <v>90.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="V8">
         <v>85</v>
@@ -4816,10 +4768,10 @@
         <v>77.5</v>
       </c>
       <c r="P9">
-        <v>81.40000000000001</v>
+        <v>50.9</v>
       </c>
       <c r="Q9">
-        <v>84</v>
+        <v>57.5</v>
       </c>
       <c r="R9">
         <v>18.1</v>
@@ -4831,7 +4783,7 @@
         <v>54.2</v>
       </c>
       <c r="U9">
-        <v>64.3</v>
+        <v>42.2</v>
       </c>
       <c r="V9">
         <v>77.5</v>
@@ -4884,10 +4836,10 @@
         <v>77.5</v>
       </c>
       <c r="P10">
-        <v>97.09999999999999</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="Q10">
-        <v>94</v>
+        <v>91.3</v>
       </c>
       <c r="R10">
         <v>100</v>
@@ -4899,7 +4851,7 @@
         <v>100</v>
       </c>
       <c r="U10">
-        <v>85.7</v>
+        <v>87.5</v>
       </c>
       <c r="V10">
         <v>77.5</v>
@@ -4952,7 +4904,7 @@
         <v>100</v>
       </c>
       <c r="P11">
-        <v>97.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="Q11">
         <v>100</v>
@@ -4967,7 +4919,7 @@
         <v>100</v>
       </c>
       <c r="U11">
-        <v>95.2</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V11">
         <v>100</v>
@@ -5020,10 +4972,10 @@
         <v>85</v>
       </c>
       <c r="P12">
-        <v>94.3</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Q12">
-        <v>94</v>
+        <v>88.8</v>
       </c>
       <c r="R12">
         <v>94.40000000000001</v>
@@ -5035,7 +4987,7 @@
         <v>60.4</v>
       </c>
       <c r="U12">
-        <v>85.7</v>
+        <v>82.8</v>
       </c>
       <c r="V12">
         <v>85</v>
@@ -5088,10 +5040,10 @@
         <v>75</v>
       </c>
       <c r="P13">
-        <v>85.7</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="Q13">
-        <v>92</v>
+        <v>91.3</v>
       </c>
       <c r="R13">
         <v>93.09999999999999</v>
@@ -5103,7 +5055,7 @@
         <v>89.59999999999999</v>
       </c>
       <c r="U13">
-        <v>81</v>
+        <v>82.8</v>
       </c>
       <c r="V13">
         <v>75</v>
@@ -5156,10 +5108,10 @@
         <v>97.5</v>
       </c>
       <c r="P14">
-        <v>95.7</v>
+        <v>95.5</v>
       </c>
       <c r="Q14">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="R14">
         <v>100</v>
@@ -5171,7 +5123,7 @@
         <v>100</v>
       </c>
       <c r="U14">
-        <v>90.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="V14">
         <v>97.5</v>
@@ -5224,7 +5176,7 @@
         <v>100</v>
       </c>
       <c r="P15">
-        <v>98.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -5239,7 +5191,7 @@
         <v>100</v>
       </c>
       <c r="U15">
-        <v>97.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="V15">
         <v>100</v>
@@ -5292,10 +5244,10 @@
         <v>85</v>
       </c>
       <c r="P16">
-        <v>97.09999999999999</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="Q16">
-        <v>94</v>
+        <v>93.8</v>
       </c>
       <c r="R16">
         <v>100</v>
@@ -5307,7 +5259,7 @@
         <v>87.5</v>
       </c>
       <c r="U16">
-        <v>90.5</v>
+        <v>82.8</v>
       </c>
       <c r="V16">
         <v>85</v>
@@ -5360,10 +5312,10 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="Q17">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="R17">
         <v>100</v>
@@ -5375,7 +5327,7 @@
         <v>93.8</v>
       </c>
       <c r="U17">
-        <v>88.09999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="V17">
         <v>100</v>
@@ -5428,10 +5380,10 @@
         <v>82.5</v>
       </c>
       <c r="P18">
-        <v>94.3</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="Q18">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="R18">
         <v>100</v>
@@ -5443,7 +5395,7 @@
         <v>68.8</v>
       </c>
       <c r="U18">
-        <v>88.09999999999999</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="V18">
         <v>82.5</v>
@@ -5496,10 +5448,10 @@
         <v>87.5</v>
       </c>
       <c r="P19">
-        <v>94.3</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Q19">
-        <v>98</v>
+        <v>96.3</v>
       </c>
       <c r="R19">
         <v>100</v>
@@ -5511,7 +5463,7 @@
         <v>68.8</v>
       </c>
       <c r="U19">
-        <v>81</v>
+        <v>82.8</v>
       </c>
       <c r="V19">
         <v>87.5</v>
@@ -5564,10 +5516,10 @@
         <v>92.5</v>
       </c>
       <c r="P20">
-        <v>97.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="Q20">
-        <v>98</v>
+        <v>96.3</v>
       </c>
       <c r="R20">
         <v>66.7</v>
@@ -5579,7 +5531,7 @@
         <v>100</v>
       </c>
       <c r="U20">
-        <v>95.2</v>
+        <v>95.3</v>
       </c>
       <c r="V20">
         <v>92.5</v>
@@ -5632,10 +5584,10 @@
         <v>92.5</v>
       </c>
       <c r="P21">
-        <v>98.59999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="Q21">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="R21">
         <v>100</v>
@@ -5647,7 +5599,7 @@
         <v>91.7</v>
       </c>
       <c r="U21">
-        <v>95.2</v>
+        <v>92.2</v>
       </c>
       <c r="V21">
         <v>92.5</v>
@@ -5700,10 +5652,10 @@
         <v>90</v>
       </c>
       <c r="P22">
-        <v>94.3</v>
+        <v>90.2</v>
       </c>
       <c r="Q22">
-        <v>94</v>
+        <v>88.8</v>
       </c>
       <c r="R22">
         <v>66.7</v>
@@ -5715,7 +5667,7 @@
         <v>60.4</v>
       </c>
       <c r="U22">
-        <v>85.7</v>
+        <v>79.7</v>
       </c>
       <c r="V22">
         <v>90</v>
@@ -5768,10 +5720,10 @@
         <v>97.5</v>
       </c>
       <c r="P23">
-        <v>94.3</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="Q23">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="R23">
         <v>100</v>
@@ -5783,7 +5735,7 @@
         <v>100</v>
       </c>
       <c r="U23">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V23">
         <v>97.5</v>
@@ -5836,10 +5788,10 @@
         <v>95</v>
       </c>
       <c r="P24">
-        <v>94.3</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="Q24">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="R24">
         <v>100</v>
@@ -5851,7 +5803,7 @@
         <v>100</v>
       </c>
       <c r="U24">
-        <v>95.2</v>
+        <v>93.8</v>
       </c>
       <c r="V24">
         <v>95</v>
@@ -5904,10 +5856,10 @@
         <v>87.5</v>
       </c>
       <c r="P25">
-        <v>95.7</v>
+        <v>95.5</v>
       </c>
       <c r="Q25">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="R25">
         <v>100</v>
@@ -5919,7 +5871,7 @@
         <v>93.8</v>
       </c>
       <c r="U25">
-        <v>92.90000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="V25">
         <v>87.5</v>
@@ -5972,7 +5924,7 @@
         <v>100</v>
       </c>
       <c r="P26">
-        <v>100</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="Q26">
         <v>100</v>
@@ -5987,7 +5939,7 @@
         <v>100</v>
       </c>
       <c r="U26">
-        <v>92.90000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="V26">
         <v>100</v>
@@ -6040,10 +5992,10 @@
         <v>95</v>
       </c>
       <c r="P27">
-        <v>98.59999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="Q27">
-        <v>98</v>
+        <v>97.5</v>
       </c>
       <c r="R27">
         <v>100</v>
@@ -6055,7 +6007,7 @@
         <v>100</v>
       </c>
       <c r="U27">
-        <v>97.59999999999999</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V27">
         <v>95</v>
@@ -6108,7 +6060,7 @@
         <v>97.5</v>
       </c>
       <c r="P28">
-        <v>98.59999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="Q28">
         <v>100</v>
@@ -6123,7 +6075,7 @@
         <v>100</v>
       </c>
       <c r="U28">
-        <v>95.2</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V28">
         <v>97.5</v>
@@ -6176,7 +6128,7 @@
         <v>97.5</v>
       </c>
       <c r="P29">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="Q29">
         <v>100</v>
@@ -6191,7 +6143,7 @@
         <v>95.8</v>
       </c>
       <c r="U29">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V29">
         <v>97.5</v>
@@ -6247,7 +6199,7 @@
         <v>100</v>
       </c>
       <c r="Q30">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="R30">
         <v>100</v>
@@ -6259,7 +6211,7 @@
         <v>100</v>
       </c>
       <c r="U30">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="V30">
         <v>100</v>
@@ -6327,7 +6279,7 @@
         <v>100</v>
       </c>
       <c r="U31">
-        <v>95.2</v>
+        <v>95.3</v>
       </c>
       <c r="V31">
         <v>97.5</v>
@@ -6380,7 +6332,7 @@
         <v>100</v>
       </c>
       <c r="P32">
-        <v>98.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="Q32">
         <v>100</v>
@@ -6395,7 +6347,7 @@
         <v>100</v>
       </c>
       <c r="U32">
-        <v>92.90000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="V32">
         <v>100</v>
@@ -6448,10 +6400,10 @@
         <v>97.5</v>
       </c>
       <c r="P33">
-        <v>94.3</v>
+        <v>93.8</v>
       </c>
       <c r="Q33">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="R33">
         <v>100</v>
@@ -6463,7 +6415,7 @@
         <v>75</v>
       </c>
       <c r="U33">
-        <v>95.2</v>
+        <v>82.8</v>
       </c>
       <c r="V33">
         <v>97.5</v>
@@ -6516,10 +6468,10 @@
         <v>97.5</v>
       </c>
       <c r="P34">
-        <v>100</v>
+        <v>97.3</v>
       </c>
       <c r="Q34">
-        <v>98</v>
+        <v>96.3</v>
       </c>
       <c r="R34">
         <v>100</v>
@@ -6531,7 +6483,7 @@
         <v>93.8</v>
       </c>
       <c r="U34">
-        <v>95.2</v>
+        <v>95.3</v>
       </c>
       <c r="V34">
         <v>97.5</v>
@@ -6584,10 +6536,10 @@
         <v>87.5</v>
       </c>
       <c r="P35">
-        <v>97.09999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="Q35">
-        <v>92</v>
+        <v>93.8</v>
       </c>
       <c r="R35">
         <v>100</v>
@@ -6599,7 +6551,7 @@
         <v>85.40000000000001</v>
       </c>
       <c r="U35">
-        <v>92.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="V35">
         <v>87.5</v>
@@ -6655,7 +6607,7 @@
         <v>100</v>
       </c>
       <c r="Q36">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="R36">
         <v>100</v>
@@ -6667,7 +6619,7 @@
         <v>100</v>
       </c>
       <c r="U36">
-        <v>90.5</v>
+        <v>92.2</v>
       </c>
       <c r="V36">
         <v>97.5</v>
@@ -6720,10 +6672,10 @@
         <v>92.5</v>
       </c>
       <c r="P37">
-        <v>98.59999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="Q37">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="R37">
         <v>100</v>
@@ -6735,7 +6687,7 @@
         <v>91.7</v>
       </c>
       <c r="U37">
-        <v>78.59999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="V37">
         <v>92.5</v>
@@ -6788,7 +6740,7 @@
         <v>100</v>
       </c>
       <c r="P38">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="Q38">
         <v>100</v>
@@ -6856,7 +6808,7 @@
         <v>100</v>
       </c>
       <c r="P39">
-        <v>98.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="Q39">
         <v>100</v>
@@ -6924,10 +6876,10 @@
         <v>100</v>
       </c>
       <c r="P40">
-        <v>95.7</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="Q40">
-        <v>98</v>
+        <v>96.3</v>
       </c>
       <c r="R40">
         <v>100</v>
@@ -6939,7 +6891,7 @@
         <v>95.8</v>
       </c>
       <c r="U40">
-        <v>92.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="V40">
         <v>100</v>
@@ -6992,10 +6944,10 @@
         <v>100</v>
       </c>
       <c r="P41">
-        <v>100</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="Q41">
-        <v>94</v>
+        <v>93.8</v>
       </c>
       <c r="R41">
         <v>100</v>
@@ -7007,7 +6959,7 @@
         <v>100</v>
       </c>
       <c r="U41">
-        <v>97.59999999999999</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V41">
         <v>100</v>
@@ -7060,10 +7012,10 @@
         <v>95</v>
       </c>
       <c r="P42">
-        <v>95.7</v>
+        <v>95.5</v>
       </c>
       <c r="Q42">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="R42">
         <v>94.40000000000001</v>
@@ -7075,7 +7027,7 @@
         <v>100</v>
       </c>
       <c r="U42">
-        <v>92.90000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="V42">
         <v>95</v>
@@ -7135,7 +7087,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
@@ -7144,19 +7096,19 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="F2" s="2">
-        <v>56.4</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G2" s="2">
-        <v>43.6</v>
+        <v>17.9</v>
       </c>
       <c r="H2">
-        <v>6.5</v>
+        <v>7.3</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -7167,7 +7119,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>65</v>
@@ -7199,7 +7151,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>66</v>
@@ -7208,19 +7160,19 @@
         <v>39</v>
       </c>
       <c r="D4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4" s="2">
-        <v>82.09999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G4" s="2">
-        <v>17.9</v>
+        <v>15.4</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7263,7 +7215,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>68</v>
@@ -7272,19 +7224,19 @@
         <v>39</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" s="2">
-        <v>84.59999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="G6" s="2">
-        <v>15.4</v>
+        <v>12.8</v>
       </c>
       <c r="H6">
-        <v>7.6</v>
+        <v>6.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7295,7 +7247,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>69</v>
@@ -7304,19 +7256,19 @@
         <v>39</v>
       </c>
       <c r="D7">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F7" s="2">
-        <v>92.3</v>
+        <v>87.2</v>
       </c>
       <c r="G7" s="2">
-        <v>7.7</v>
+        <v>12.8</v>
       </c>
       <c r="H7">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7327,7 +7279,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>70</v>
@@ -7336,19 +7288,19 @@
         <v>39</v>
       </c>
       <c r="D8">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" s="2">
-        <v>94.90000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="G8" s="2">
-        <v>5.1</v>
+        <v>7.7</v>
       </c>
       <c r="H8">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7398,7 +7350,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7436,16 +7388,16 @@
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7459,16 +7411,16 @@
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -7476,22 +7428,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920150</v>
+        <v>22330051920159</v>
       </c>
       <c r="B4" t="s">
         <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7499,19 +7451,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920155</v>
+        <v>22330051920159</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="E5" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
         <v>64</v>
@@ -7522,22 +7474,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920381</v>
+        <v>22330051920386</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7545,22 +7497,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920163</v>
+        <v>22330051920386</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7568,22 +7520,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920299</v>
+        <v>22330051920150</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7591,116 +7543,24 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920164</v>
+        <v>22330051920172</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920170</v>
-      </c>
-      <c r="B10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C10" t="s">
-        <v>92</v>
-      </c>
-      <c r="D10" t="s">
-        <v>102</v>
-      </c>
-      <c r="E10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>64</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920172</v>
-      </c>
-      <c r="B11" t="s">
-        <v>83</v>
-      </c>
-      <c r="C11" t="s">
-        <v>93</v>
-      </c>
-      <c r="D11" t="s">
-        <v>103</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
-        <v>64</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920175</v>
-      </c>
-      <c r="B12" t="s">
-        <v>84</v>
-      </c>
-      <c r="C12" t="s">
-        <v>75</v>
-      </c>
-      <c r="D12" t="s">
-        <v>104</v>
-      </c>
-      <c r="E12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>64</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920287</v>
-      </c>
-      <c r="B13" t="s">
-        <v>85</v>
-      </c>
-      <c r="C13" t="s">
-        <v>94</v>
-      </c>
-      <c r="D13" t="s">
-        <v>105</v>
-      </c>
-      <c r="E13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" t="s">
-        <v>64</v>
-      </c>
-      <c r="G13">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2APM - Estadisticos 20222.xlsx
+++ b/grupos/2APM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="93">
   <si>
     <t>Materia</t>
   </si>
@@ -254,10 +254,13 @@
     <t>RAMIREZ</t>
   </si>
   <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
     <t>BAEZ</t>
   </si>
   <si>
-    <t>ROJAS</t>
+    <t>CALOCA</t>
   </si>
   <si>
     <t>ORTEGA</t>
@@ -269,10 +272,13 @@
     <t>LUNA</t>
   </si>
   <si>
+    <t>ANGUIANO</t>
+  </si>
+  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>ANGUIANO</t>
+    <t>TEXCAHUA</t>
   </si>
   <si>
     <t>JESUS EMMANUEL</t>
@@ -284,10 +290,13 @@
     <t>GUSTAVO</t>
   </si>
   <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
     <t>EDUARDO EMER</t>
   </si>
   <si>
-    <t>LUIS ANGEL</t>
+    <t>ARLETH MARELY</t>
   </si>
 </sst>
 </file>
@@ -853,7 +862,7 @@
         <v>10</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W4">
         <v>10</v>
@@ -942,7 +951,7 @@
         <v>5</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W5">
         <v>8</v>
@@ -1031,7 +1040,7 @@
         <v>8</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W6">
         <v>8</v>
@@ -1120,7 +1129,7 @@
         <v>5</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W7">
         <v>7</v>
@@ -1209,7 +1218,7 @@
         <v>6</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W8">
         <v>6</v>
@@ -1230,7 +1239,7 @@
         <v>9</v>
       </c>
       <c r="AC8">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1298,7 +1307,7 @@
         <v>5</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W9">
         <v>5</v>
@@ -1387,7 +1396,7 @@
         <v>6</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W10">
         <v>6</v>
@@ -1476,7 +1485,7 @@
         <v>10</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W11">
         <v>9</v>
@@ -1565,7 +1574,7 @@
         <v>5</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W12">
         <v>5</v>
@@ -1654,7 +1663,7 @@
         <v>5</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W13">
         <v>5</v>
@@ -1743,7 +1752,7 @@
         <v>5</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W14">
         <v>7</v>
@@ -1832,7 +1841,7 @@
         <v>5</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W15">
         <v>8</v>
@@ -1921,7 +1930,7 @@
         <v>5</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W16">
         <v>6</v>
@@ -2010,7 +2019,7 @@
         <v>5</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>7</v>
@@ -2099,7 +2108,7 @@
         <v>5</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W18">
         <v>6</v>
@@ -2188,7 +2197,7 @@
         <v>5</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W19">
         <v>6</v>
@@ -2277,7 +2286,7 @@
         <v>5</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="W20">
         <v>5</v>
@@ -2298,7 +2307,7 @@
         <v>6</v>
       </c>
       <c r="AC20">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2366,7 +2375,7 @@
         <v>8</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W21">
         <v>8</v>
@@ -2455,7 +2464,7 @@
         <v>5</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W22">
         <v>5</v>
@@ -2544,7 +2553,7 @@
         <v>5</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W23">
         <v>6</v>
@@ -2565,7 +2574,7 @@
         <v>8</v>
       </c>
       <c r="AC23">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2633,7 +2642,7 @@
         <v>5</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W24">
         <v>6</v>
@@ -2722,7 +2731,7 @@
         <v>5</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W25">
         <v>6</v>
@@ -2743,7 +2752,7 @@
         <v>7</v>
       </c>
       <c r="AC25">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2811,7 +2820,7 @@
         <v>10</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W26">
         <v>8</v>
@@ -2900,7 +2909,7 @@
         <v>8</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W27">
         <v>8</v>
@@ -2921,7 +2930,7 @@
         <v>9</v>
       </c>
       <c r="AC27">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -2989,7 +2998,7 @@
         <v>6</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W28">
         <v>7</v>
@@ -3010,7 +3019,7 @@
         <v>9</v>
       </c>
       <c r="AC28">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3078,7 +3087,7 @@
         <v>5</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W29">
         <v>8</v>
@@ -3167,7 +3176,7 @@
         <v>8</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W30">
         <v>8</v>
@@ -3256,7 +3265,7 @@
         <v>5</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W31">
         <v>8</v>
@@ -3345,7 +3354,7 @@
         <v>9</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W32">
         <v>9</v>
@@ -3434,7 +3443,7 @@
         <v>5</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W33">
         <v>6</v>
@@ -3455,7 +3464,7 @@
         <v>6</v>
       </c>
       <c r="AC33">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:29">
@@ -3523,7 +3532,7 @@
         <v>5</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W34">
         <v>6</v>
@@ -3612,7 +3621,7 @@
         <v>9</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W35">
         <v>8</v>
@@ -3701,7 +3710,7 @@
         <v>8</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W36">
         <v>8</v>
@@ -3722,7 +3731,7 @@
         <v>9</v>
       </c>
       <c r="AC36">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:29">
@@ -3790,7 +3799,7 @@
         <v>5</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W37">
         <v>6</v>
@@ -3811,7 +3820,7 @@
         <v>5</v>
       </c>
       <c r="AC37">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:29">
@@ -3879,7 +3888,7 @@
         <v>10</v>
       </c>
       <c r="V38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W38">
         <v>9</v>
@@ -3968,7 +3977,7 @@
         <v>9</v>
       </c>
       <c r="V39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W39">
         <v>6</v>
@@ -4057,7 +4066,7 @@
         <v>5</v>
       </c>
       <c r="V40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W40">
         <v>6</v>
@@ -4146,7 +4155,7 @@
         <v>5</v>
       </c>
       <c r="V41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W41">
         <v>8</v>
@@ -4235,7 +4244,7 @@
         <v>5</v>
       </c>
       <c r="V42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W42">
         <v>6</v>
@@ -4514,7 +4523,7 @@
         <v>85.90000000000001</v>
       </c>
       <c r="V5">
-        <v>82.5</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -4582,7 +4591,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="V6">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -4718,7 +4727,7 @@
         <v>85.90000000000001</v>
       </c>
       <c r="V8">
-        <v>85</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -4786,7 +4795,7 @@
         <v>42.2</v>
       </c>
       <c r="V9">
-        <v>77.5</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -4854,7 +4863,7 @@
         <v>87.5</v>
       </c>
       <c r="V10">
-        <v>77.5</v>
+        <v>81.3</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -4990,7 +4999,7 @@
         <v>82.8</v>
       </c>
       <c r="V12">
-        <v>85</v>
+        <v>76.59999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -5058,7 +5067,7 @@
         <v>82.8</v>
       </c>
       <c r="V13">
-        <v>75</v>
+        <v>73.40000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -5126,7 +5135,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="V14">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -5194,7 +5203,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="V15">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -5262,7 +5271,7 @@
         <v>82.8</v>
       </c>
       <c r="V16">
-        <v>85</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -5330,7 +5339,7 @@
         <v>87.5</v>
       </c>
       <c r="V17">
-        <v>100</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -5398,7 +5407,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="V18">
-        <v>82.5</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -5534,7 +5543,7 @@
         <v>95.3</v>
       </c>
       <c r="V20">
-        <v>92.5</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -5602,7 +5611,7 @@
         <v>92.2</v>
       </c>
       <c r="V21">
-        <v>92.5</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -5670,7 +5679,7 @@
         <v>79.7</v>
       </c>
       <c r="V22">
-        <v>90</v>
+        <v>82.8</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -5738,7 +5747,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="V23">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -5806,7 +5815,7 @@
         <v>93.8</v>
       </c>
       <c r="V24">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -6010,7 +6019,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="V27">
-        <v>95</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -6078,7 +6087,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="V28">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -6146,7 +6155,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="V29">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -6282,7 +6291,7 @@
         <v>95.3</v>
       </c>
       <c r="V31">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -6418,7 +6427,7 @@
         <v>82.8</v>
       </c>
       <c r="V33">
-        <v>97.5</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -6486,7 +6495,7 @@
         <v>95.3</v>
       </c>
       <c r="V34">
-        <v>97.5</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="35" spans="1:22">
@@ -6554,7 +6563,7 @@
         <v>93.8</v>
       </c>
       <c r="V35">
-        <v>87.5</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="36" spans="1:22">
@@ -6622,7 +6631,7 @@
         <v>92.2</v>
       </c>
       <c r="V36">
-        <v>97.5</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:22">
@@ -6690,7 +6699,7 @@
         <v>79.7</v>
       </c>
       <c r="V37">
-        <v>92.5</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="38" spans="1:22">
@@ -6894,7 +6903,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="V40">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="41" spans="1:22">
@@ -6962,7 +6971,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="V41">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="42" spans="1:22">
@@ -7030,7 +7039,7 @@
         <v>87.5</v>
       </c>
       <c r="V42">
-        <v>95</v>
+        <v>95.3</v>
       </c>
     </row>
   </sheetData>
@@ -7096,19 +7105,19 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F2" s="2">
-        <v>82.09999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="G2" s="2">
-        <v>17.9</v>
+        <v>25.6</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -7350,7 +7359,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7388,10 +7397,10 @@
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
@@ -7411,10 +7420,10 @@
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
@@ -7434,10 +7443,10 @@
         <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -7457,10 +7466,10 @@
         <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
@@ -7480,10 +7489,10 @@
         <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -7503,10 +7512,10 @@
         <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -7520,22 +7529,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920150</v>
+        <v>22330051920172</v>
       </c>
       <c r="B8" t="s">
         <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7546,21 +7555,67 @@
         <v>22330051920172</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
         <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>22330051920150</v>
+      </c>
+      <c r="B10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C10" t="s">
+        <v>85</v>
+      </c>
+      <c r="D10" t="s">
+        <v>91</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>67</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>22330051920381</v>
+      </c>
+      <c r="B11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" t="s">
+        <v>86</v>
+      </c>
+      <c r="D11" t="s">
+        <v>92</v>
+      </c>
+      <c r="E11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" t="s">
+        <v>64</v>
+      </c>
+      <c r="G11">
         <v>5</v>
       </c>
     </row>
